--- a/keyword.xlsx
+++ b/keyword.xlsx
@@ -11,6 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="months" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="sites" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="intents" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="customer_triggers" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -3049,4 +3050,251 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C19"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="55" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>keyword</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>type</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>note</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>Keywords that trigger the customer dataset instead of balance spec</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>customer</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>trigger</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>client</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>trigger</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>account</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>trigger</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>buyer</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>trigger</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>who</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>trigger</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="inlineStr">
+        <is>
+          <t>company</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>trigger</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>co.,ltd</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>trigger</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="inlineStr">
+        <is>
+          <t>co., ltd</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>trigger</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>ltd.</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>trigger</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="inlineStr">
+        <is>
+          <t>top customer</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>trigger</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>best customer</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>trigger</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="inlineStr">
+        <is>
+          <t>customer revenue</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>trigger</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>customer list</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>trigger</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="3" t="inlineStr">
+        <is>
+          <t>how many customer</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>trigger</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>customer count</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>trigger</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="3" t="inlineStr">
+        <is>
+          <t>customer trend</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>trigger</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="3" t="inlineStr">
+        <is>
+          <t>customer compare</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>trigger</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/keyword.xlsx
+++ b/keyword.xlsx
@@ -12,6 +12,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="sites" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="intents" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="customer_triggers" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="categories" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -462,12 +463,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C115"/>
+  <dimension ref="A1:C135"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
-    <col width="35" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="40" customWidth="1" min="2" max="2"/>
+    <col width="55" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -490,7 +491,7 @@
     <row r="2">
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>keyword = what user types, item_name = exact name in data file</t>
+          <t>item_name must match exactly with Item Detail in pnl.json</t>
         </is>
       </c>
     </row>
@@ -502,7 +503,7 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>Revenue</t>
+          <t>Revenue Total</t>
         </is>
       </c>
     </row>
@@ -514,7 +515,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>Revenue</t>
+          <t>Revenue Total</t>
         </is>
       </c>
     </row>
@@ -526,7 +527,7 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>Revenue</t>
+          <t>Revenue Total</t>
         </is>
       </c>
     </row>
@@ -538,7 +539,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>Revenue</t>
+          <t>Revenue Total</t>
         </is>
       </c>
     </row>
@@ -557,91 +558,91 @@
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>cost</t>
+          <t>material</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Cost Total</t>
+          <t>Material and Service</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>total cost</t>
+          <t>subcontract</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>Cost Total</t>
+          <t>Material and Service</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>cost total</t>
+          <t>subcontractor</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>Cost Total</t>
+          <t>Material and Service</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>subcontract</t>
+          <t>sub cost</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>Subcontractor Cost</t>
+          <t>Material and Service</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>subcontractor</t>
+          <t>material and service</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>Subcontractor Cost</t>
+          <t>Material and Service</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>sub cost</t>
+          <t>cost adjust</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>Subcontractor Cost</t>
+          <t>Cost (Adjust)</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>salary</t>
+          <t>adjustment</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>Salary</t>
+          <t>Cost (Adjust)</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>wage</t>
+          <t>salary</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
@@ -653,7 +654,7 @@
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>base pay</t>
+          <t>wage</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -665,19 +666,19 @@
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>overtime</t>
+          <t>base pay</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>Over Time</t>
+          <t>Salary</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>over time</t>
+          <t>overtime</t>
         </is>
       </c>
       <c r="B18" s="3" t="inlineStr">
@@ -689,7 +690,7 @@
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>ot</t>
+          <t>over time</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -701,31 +702,31 @@
     <row r="20">
       <c r="A20" s="3" t="inlineStr">
         <is>
-          <t>bonus</t>
+          <t>ot</t>
         </is>
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>Bonus</t>
+          <t>Over Time</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>social security</t>
+          <t>bonus</t>
         </is>
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>Social security</t>
+          <t>Bonus</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="3" t="inlineStr">
         <is>
-          <t>ss</t>
+          <t>social security</t>
         </is>
       </c>
       <c r="B22" s="3" t="inlineStr">
@@ -737,7 +738,7 @@
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>sso</t>
+          <t>ss</t>
         </is>
       </c>
       <c r="B23" s="3" t="inlineStr">
@@ -749,19 +750,19 @@
     <row r="24">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t>welfare</t>
+          <t>sso</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>Welfare</t>
+          <t>Social security</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>benefit</t>
+          <t>welfare</t>
         </is>
       </c>
       <c r="B25" s="3" t="inlineStr">
@@ -773,19 +774,19 @@
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t>provident</t>
+          <t>benefit</t>
         </is>
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>Provident Fund</t>
+          <t>Welfare</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>provident fund</t>
+          <t>provident</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
@@ -797,7 +798,7 @@
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>pvd</t>
+          <t>provident fund</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
@@ -809,19 +810,19 @@
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>workmen</t>
+          <t>pvd</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>Workmen's compensation</t>
+          <t>Provident Fund</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>compensation</t>
+          <t>workmen</t>
         </is>
       </c>
       <c r="B30" s="3" t="inlineStr">
@@ -833,19 +834,19 @@
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>severance</t>
+          <t>compensation</t>
         </is>
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>Severance Pay / Retirement Fee</t>
+          <t>Workmen's compensation</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>retirement</t>
+          <t>severance</t>
         </is>
       </c>
       <c r="B32" s="3" t="inlineStr">
@@ -857,67 +858,67 @@
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>allowance</t>
+          <t>retirement</t>
         </is>
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>Allowance</t>
+          <t>Severance Pay / Retirement Fee</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>warehouse supply</t>
+          <t>allowance</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>Warehouse Supply</t>
+          <t>Allowance</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>wh supply</t>
+          <t>consumable</t>
         </is>
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>Warehouse Supply</t>
+          <t>Consumable Supply</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>outsource</t>
+          <t>consumable supply</t>
         </is>
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>Outsource Labor Fee</t>
+          <t>Consumable Supply</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>outsource labor</t>
+          <t>supply</t>
         </is>
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>Outsource Labor Fee</t>
+          <t>Consumable Supply</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>labor fee</t>
+          <t>outsource</t>
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr">
@@ -929,924 +930,1164 @@
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>warehouse rental</t>
+          <t>outsource labor</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>Warehouse Rental</t>
+          <t>Outsource Labor Fee</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t>wh rental</t>
+          <t>labor fee</t>
         </is>
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>Warehouse Rental</t>
+          <t>Outsource Labor Fee</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t>rental other</t>
+          <t>cost total</t>
         </is>
       </c>
       <c r="B41" s="3" t="inlineStr">
         <is>
-          <t>Rental Other</t>
+          <t>Cost Total</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>rental equipment</t>
+          <t>total cost</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>Rental Equipments</t>
+          <t>Cost Total</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t>equipment rental</t>
+          <t>variable cost</t>
         </is>
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>Rental Equipments</t>
+          <t>Variable Cost Total</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
         <is>
-          <t>repair</t>
+          <t>variable total</t>
         </is>
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>Repair and Maintenance</t>
+          <t>Variable Cost Total</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="3" t="inlineStr">
         <is>
-          <t>maintenance</t>
+          <t>land rental</t>
         </is>
       </c>
       <c r="B45" s="3" t="inlineStr">
         <is>
-          <t>Repair and Maintenance</t>
+          <t>Land Rental</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t>r&amp;m</t>
+          <t>land rent</t>
         </is>
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>Repair and Maintenance</t>
+          <t>Land Rental</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="3" t="inlineStr">
         <is>
-          <t>electric</t>
+          <t>rental other</t>
         </is>
       </c>
       <c r="B47" s="3" t="inlineStr">
         <is>
-          <t>Electric&amp;Water Supply</t>
+          <t>Rental Other</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="3" t="inlineStr">
         <is>
-          <t>water</t>
+          <t>rental equipment</t>
         </is>
       </c>
       <c r="B48" s="3" t="inlineStr">
         <is>
-          <t>Electric&amp;Water Supply</t>
+          <t>Rental Equipments</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="3" t="inlineStr">
         <is>
-          <t>utility</t>
+          <t>equipment rental</t>
         </is>
       </c>
       <c r="B49" s="3" t="inlineStr">
         <is>
-          <t>Electric&amp;Water Supply</t>
+          <t>Rental Equipments</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="3" t="inlineStr">
         <is>
-          <t>utilities</t>
+          <t>rental office</t>
         </is>
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t>Electric&amp;Water Supply</t>
+          <t>Rental Office</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="3" t="inlineStr">
         <is>
-          <t>depreciation</t>
+          <t>office rental</t>
         </is>
       </c>
       <c r="B51" s="3" t="inlineStr">
         <is>
-          <t>Depreciation</t>
+          <t>Rental Office</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="3" t="inlineStr">
         <is>
-          <t>dep</t>
+          <t>repair direct</t>
         </is>
       </c>
       <c r="B52" s="3" t="inlineStr">
         <is>
-          <t>Depreciation</t>
+          <t>Repair and Maintenance (Direct)</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="3" t="inlineStr">
         <is>
-          <t>rental office</t>
+          <t>maintenance direct</t>
         </is>
       </c>
       <c r="B53" s="3" t="inlineStr">
         <is>
-          <t>Rental Office</t>
+          <t>Repair and Maintenance (Direct)</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="3" t="inlineStr">
         <is>
-          <t>office rental</t>
+          <t>repair</t>
         </is>
       </c>
       <c r="B54" s="3" t="inlineStr">
         <is>
-          <t>Rental Office</t>
+          <t>Repair and Maintenance (Expense)</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="3" t="inlineStr">
         <is>
-          <t>conference</t>
+          <t>maintenance</t>
         </is>
       </c>
       <c r="B55" s="3" t="inlineStr">
         <is>
-          <t>Conference</t>
+          <t>Repair and Maintenance (Expense)</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="3" t="inlineStr">
         <is>
-          <t>meeting</t>
+          <t>r&amp;m</t>
         </is>
       </c>
       <c r="B56" s="3" t="inlineStr">
         <is>
-          <t>Conference</t>
+          <t>Repair and Maintenance (Expense)</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="3" t="inlineStr">
         <is>
-          <t>entertainment</t>
+          <t>electric</t>
         </is>
       </c>
       <c r="B57" s="3" t="inlineStr">
         <is>
-          <t>Entertainment</t>
+          <t>Electric&amp;Water Supply</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="3" t="inlineStr">
         <is>
-          <t>transport</t>
+          <t>water</t>
         </is>
       </c>
       <c r="B58" s="3" t="inlineStr">
         <is>
-          <t>Transportation</t>
+          <t>Electric&amp;Water Supply</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="3" t="inlineStr">
         <is>
-          <t>transportation</t>
+          <t>utility</t>
         </is>
       </c>
       <c r="B59" s="3" t="inlineStr">
         <is>
-          <t>Transportation</t>
+          <t>Electric&amp;Water Supply</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="3" t="inlineStr">
         <is>
-          <t>travel</t>
+          <t>utilities</t>
         </is>
       </c>
       <c r="B60" s="3" t="inlineStr">
         <is>
-          <t>Transportation</t>
+          <t>Electric&amp;Water Supply</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="3" t="inlineStr">
         <is>
-          <t>telephone</t>
+          <t>depreciation</t>
         </is>
       </c>
       <c r="B61" s="3" t="inlineStr">
         <is>
-          <t>Telephone</t>
+          <t>Depreciation</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="3" t="inlineStr">
         <is>
-          <t>phone</t>
+          <t>dep</t>
         </is>
       </c>
       <c r="B62" s="3" t="inlineStr">
         <is>
-          <t>Telephone</t>
+          <t>Depreciation</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="3" t="inlineStr">
         <is>
-          <t>mobile</t>
+          <t>fixed cost</t>
         </is>
       </c>
       <c r="B63" s="3" t="inlineStr">
         <is>
-          <t>Mobile Phone</t>
+          <t>Fixed Cost Total</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="3" t="inlineStr">
         <is>
-          <t>mobile phone</t>
+          <t>fix cost</t>
         </is>
       </c>
       <c r="B64" s="3" t="inlineStr">
         <is>
-          <t>Mobile Phone</t>
+          <t>Fixed Cost Total</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="3" t="inlineStr">
         <is>
-          <t>lease circuit</t>
+          <t>fixed total</t>
         </is>
       </c>
       <c r="B65" s="3" t="inlineStr">
         <is>
-          <t>Lease Circuit</t>
+          <t>Fixed Cost Total</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="3" t="inlineStr">
         <is>
-          <t>circuit</t>
+          <t>fix total</t>
         </is>
       </c>
       <c r="B66" s="3" t="inlineStr">
         <is>
-          <t>Lease Circuit</t>
+          <t>Fixed Cost Total</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="3" t="inlineStr">
         <is>
-          <t>internet</t>
+          <t>gross profit</t>
         </is>
       </c>
       <c r="B67" s="3" t="inlineStr">
         <is>
-          <t>Lease Circuit</t>
+          <t>Gross Profit</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="3" t="inlineStr">
         <is>
-          <t>cargo</t>
+          <t>gp</t>
         </is>
       </c>
       <c r="B68" s="3" t="inlineStr">
         <is>
-          <t>Cargo Master</t>
+          <t>Gross Profit</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="3" t="inlineStr">
         <is>
-          <t>cargo master</t>
+          <t>profit</t>
         </is>
       </c>
       <c r="B69" s="3" t="inlineStr">
         <is>
-          <t>Cargo Master</t>
+          <t>Gross Profit</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="3" t="inlineStr">
         <is>
-          <t>office supply</t>
+          <t>operating profit</t>
         </is>
       </c>
       <c r="B70" s="3" t="inlineStr">
         <is>
-          <t>Office Supply</t>
+          <t>Operating Profit</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="3" t="inlineStr">
         <is>
-          <t>stationery</t>
+          <t>op</t>
         </is>
       </c>
       <c r="B71" s="3" t="inlineStr">
         <is>
-          <t>Office Supply</t>
+          <t>Operating Profit</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="3" t="inlineStr">
         <is>
-          <t>insurance</t>
+          <t>net profit</t>
         </is>
       </c>
       <c r="B72" s="3" t="inlineStr">
         <is>
-          <t>Insurance</t>
+          <t>Operating Profit</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="3" t="inlineStr">
         <is>
-          <t>security</t>
+          <t>expense</t>
         </is>
       </c>
       <c r="B73" s="3" t="inlineStr">
         <is>
-          <t>Security</t>
+          <t>Expense Total</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="3" t="inlineStr">
         <is>
-          <t>guard</t>
+          <t>total expense</t>
         </is>
       </c>
       <c r="B74" s="3" t="inlineStr">
         <is>
-          <t>Security</t>
+          <t>Expense Total</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="3" t="inlineStr">
         <is>
-          <t>cleaning</t>
+          <t>conference</t>
         </is>
       </c>
       <c r="B75" s="3" t="inlineStr">
         <is>
-          <t>Cleaning Expense</t>
+          <t>Conference</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="3" t="inlineStr">
         <is>
-          <t>clean</t>
+          <t>meeting</t>
         </is>
       </c>
       <c r="B76" s="3" t="inlineStr">
         <is>
-          <t>Cleaning Expense</t>
+          <t>Conference</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="3" t="inlineStr">
         <is>
-          <t>signboard</t>
+          <t>entertainment</t>
         </is>
       </c>
       <c r="B77" s="3" t="inlineStr">
         <is>
-          <t>Signboard Tax</t>
+          <t>Entertainment</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="3" t="inlineStr">
         <is>
-          <t>land tax</t>
+          <t>transport</t>
         </is>
       </c>
       <c r="B78" s="3" t="inlineStr">
         <is>
-          <t>Land &amp; Building TAX</t>
+          <t>Transportation</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="3" t="inlineStr">
         <is>
-          <t>building tax</t>
+          <t>transportation</t>
         </is>
       </c>
       <c r="B79" s="3" t="inlineStr">
         <is>
-          <t>Land &amp; Building TAX</t>
+          <t>Transportation</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="3" t="inlineStr">
         <is>
-          <t>common expense</t>
+          <t>travel</t>
         </is>
       </c>
       <c r="B80" s="3" t="inlineStr">
         <is>
-          <t>Common expense</t>
+          <t>Transportation</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="3" t="inlineStr">
         <is>
-          <t>service office</t>
+          <t>telephone</t>
         </is>
       </c>
       <c r="B81" s="3" t="inlineStr">
         <is>
-          <t>Service Office</t>
+          <t>Telephone</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="3" t="inlineStr">
         <is>
-          <t>office equipment</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="B82" s="3" t="inlineStr">
         <is>
-          <t>Office Equipment</t>
+          <t>Telephone</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="3" t="inlineStr">
         <is>
-          <t>facility</t>
+          <t>mobile</t>
         </is>
       </c>
       <c r="B83" s="3" t="inlineStr">
         <is>
-          <t>Facility Expense</t>
+          <t>Mobile Phone</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="3" t="inlineStr">
         <is>
-          <t>facility expense</t>
+          <t>mobile phone</t>
         </is>
       </c>
       <c r="B84" s="3" t="inlineStr">
         <is>
-          <t>Facility Expense</t>
+          <t>Mobile Phone</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="3" t="inlineStr">
         <is>
-          <t>staff amenity</t>
+          <t>lease circuit</t>
         </is>
       </c>
       <c r="B85" s="3" t="inlineStr">
         <is>
-          <t>Staff Amenity</t>
+          <t>Lease Circuit</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="3" t="inlineStr">
         <is>
-          <t>amenity</t>
+          <t>circuit</t>
         </is>
       </c>
       <c r="B86" s="3" t="inlineStr">
         <is>
-          <t>Staff Amenity</t>
+          <t>Lease Circuit</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="3" t="inlineStr">
         <is>
-          <t>personnel</t>
+          <t>internet</t>
         </is>
       </c>
       <c r="B87" s="3" t="inlineStr">
         <is>
-          <t>Personnel Expense</t>
+          <t>Lease Circuit</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="3" t="inlineStr">
         <is>
-          <t>personnel expense</t>
+          <t>office supply</t>
         </is>
       </c>
       <c r="B88" s="3" t="inlineStr">
         <is>
-          <t>Personnel Expense</t>
+          <t>Office Supply</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="3" t="inlineStr">
         <is>
-          <t>claim</t>
+          <t>stationery</t>
         </is>
       </c>
       <c r="B89" s="3" t="inlineStr">
         <is>
-          <t>CLAIM FROM CUSTOMER</t>
+          <t>Office Supply</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="3" t="inlineStr">
         <is>
-          <t>customer claim</t>
+          <t>insurance</t>
         </is>
       </c>
       <c r="B90" s="3" t="inlineStr">
         <is>
-          <t>CLAIM FROM CUSTOMER</t>
+          <t>Insurance</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="3" t="inlineStr">
         <is>
-          <t>profit</t>
+          <t>security</t>
         </is>
       </c>
       <c r="B91" s="3" t="inlineStr">
         <is>
-          <t>Gross Profit</t>
+          <t>Security</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="3" t="inlineStr">
         <is>
-          <t>gross profit</t>
+          <t>guard</t>
         </is>
       </c>
       <c r="B92" s="3" t="inlineStr">
         <is>
-          <t>Gross Profit</t>
+          <t>Security</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="3" t="inlineStr">
         <is>
-          <t>gp</t>
+          <t>cleaning</t>
         </is>
       </c>
       <c r="B93" s="3" t="inlineStr">
         <is>
-          <t>Gross Profit</t>
+          <t>Cleaning Expense</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="3" t="inlineStr">
         <is>
-          <t>operating profit</t>
+          <t>clean</t>
         </is>
       </c>
       <c r="B94" s="3" t="inlineStr">
         <is>
-          <t>Operating Profit</t>
+          <t>Cleaning Expense</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="3" t="inlineStr">
         <is>
-          <t>op</t>
+          <t>signboard</t>
         </is>
       </c>
       <c r="B95" s="3" t="inlineStr">
         <is>
-          <t>Operating Profit</t>
+          <t>Signboard Tax</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="3" t="inlineStr">
         <is>
-          <t>net profit</t>
+          <t>land tax</t>
         </is>
       </c>
       <c r="B96" s="3" t="inlineStr">
         <is>
-          <t>Operating Profit</t>
+          <t>Land &amp; Building TAX</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="3" t="inlineStr">
         <is>
-          <t>expense</t>
+          <t>building tax</t>
         </is>
       </c>
       <c r="B97" s="3" t="inlineStr">
         <is>
-          <t>Expense Total</t>
+          <t>Land &amp; Building TAX</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="3" t="inlineStr">
         <is>
-          <t>total expense</t>
+          <t>common expense</t>
         </is>
       </c>
       <c r="B98" s="3" t="inlineStr">
         <is>
-          <t>Expense Total</t>
+          <t>Common expense</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="3" t="inlineStr">
         <is>
-          <t>expense total</t>
+          <t>service office</t>
         </is>
       </c>
       <c r="B99" s="3" t="inlineStr">
         <is>
-          <t>Expense Total</t>
+          <t>Service Office</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="3" t="inlineStr">
         <is>
-          <t>staff</t>
+          <t>office equipment</t>
         </is>
       </c>
       <c r="B100" s="3" t="inlineStr">
         <is>
-          <t>Number of staff</t>
+          <t>Office Equipment</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="3" t="inlineStr">
         <is>
-          <t>headcount</t>
+          <t>facility</t>
         </is>
       </c>
       <c r="B101" s="3" t="inlineStr">
         <is>
-          <t>Number of staff</t>
+          <t>Facility Expense</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="3" t="inlineStr">
         <is>
-          <t>employee</t>
+          <t>facility expense</t>
         </is>
       </c>
       <c r="B102" s="3" t="inlineStr">
         <is>
-          <t>Number of staff</t>
+          <t>Facility Expense</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="3" t="inlineStr">
         <is>
-          <t>hc</t>
+          <t>staff amenity</t>
         </is>
       </c>
       <c r="B103" s="3" t="inlineStr">
         <is>
-          <t>Number of staff</t>
+          <t>Staff Amenity</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="3" t="inlineStr">
         <is>
-          <t>variable</t>
+          <t>amenity</t>
         </is>
       </c>
       <c r="B104" s="3" t="inlineStr">
         <is>
-          <t>Variable</t>
+          <t>Staff Amenity</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="3" t="inlineStr">
         <is>
-          <t>variable cost</t>
+          <t>personnel</t>
         </is>
       </c>
       <c r="B105" s="3" t="inlineStr">
         <is>
-          <t>Variable</t>
+          <t>Personnel Expense</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="3" t="inlineStr">
         <is>
-          <t>fix</t>
+          <t>personnel expense</t>
         </is>
       </c>
       <c r="B106" s="3" t="inlineStr">
         <is>
-          <t>Fix</t>
+          <t>Personnel Expense</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="3" t="inlineStr">
         <is>
-          <t>fixed</t>
+          <t>claim</t>
         </is>
       </c>
       <c r="B107" s="3" t="inlineStr">
         <is>
-          <t>Fix</t>
+          <t>CLAIM FROM CUSTOMER</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="3" t="inlineStr">
         <is>
-          <t>fix cost</t>
+          <t>customer claim</t>
         </is>
       </c>
       <c r="B108" s="3" t="inlineStr">
         <is>
-          <t>Fix</t>
+          <t>CLAIM FROM CUSTOMER</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="3" t="inlineStr">
         <is>
-          <t>fixed cost</t>
+          <t>staff</t>
         </is>
       </c>
       <c r="B109" s="3" t="inlineStr">
         <is>
-          <t>Fix</t>
+          <t>Number of staff</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="3" t="inlineStr">
         <is>
-          <t>adjust</t>
+          <t>headcount</t>
         </is>
       </c>
       <c r="B110" s="3" t="inlineStr">
         <is>
-          <t>Cost (Adjust)</t>
+          <t>Number of staff</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="3" t="inlineStr">
         <is>
-          <t>cost adjust</t>
+          <t>employee</t>
         </is>
       </c>
       <c r="B111" s="3" t="inlineStr">
         <is>
-          <t>Cost (Adjust)</t>
+          <t>Number of staff</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="3" t="inlineStr">
         <is>
-          <t>adjustment</t>
+          <t>hc</t>
         </is>
       </c>
       <c r="B112" s="3" t="inlineStr">
         <is>
-          <t>Cost (Adjust)</t>
+          <t>Number of staff</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="3" t="inlineStr">
         <is>
-          <t>rent</t>
+          <t>number of staff</t>
         </is>
       </c>
       <c r="B113" s="3" t="inlineStr">
         <is>
-          <t>Warehouse Rental</t>
+          <t>Number of staff</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="3" t="inlineStr">
         <is>
-          <t>rental</t>
+          <t>marginal profit</t>
         </is>
       </c>
       <c r="B114" s="3" t="inlineStr">
         <is>
-          <t>Warehouse Rental</t>
+          <t>Marginal Profit</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="3" t="inlineStr">
         <is>
-          <t>supply</t>
+          <t>marginal</t>
         </is>
       </c>
       <c r="B115" s="3" t="inlineStr">
         <is>
-          <t>Warehouse Supply</t>
+          <t>Marginal Profit</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="3" t="inlineStr">
+        <is>
+          <t>revenue per head</t>
+        </is>
+      </c>
+      <c r="B116" s="3" t="inlineStr">
+        <is>
+          <t>Revenue per Head</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="3" t="inlineStr">
+        <is>
+          <t>rev per head</t>
+        </is>
+      </c>
+      <c r="B117" s="3" t="inlineStr">
+        <is>
+          <t>Revenue per Head</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="3" t="inlineStr">
+        <is>
+          <t>software</t>
+        </is>
+      </c>
+      <c r="B118" s="3" t="inlineStr">
+        <is>
+          <t>Software License</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="3" t="inlineStr">
+        <is>
+          <t>license</t>
+        </is>
+      </c>
+      <c r="B119" s="3" t="inlineStr">
+        <is>
+          <t>Software License</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="3" t="inlineStr">
+        <is>
+          <t>gp ratio</t>
+        </is>
+      </c>
+      <c r="B120" s="3" t="inlineStr">
+        <is>
+          <t>Gross Profit Ratio</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="3" t="inlineStr">
+        <is>
+          <t>gross profit ratio</t>
+        </is>
+      </c>
+      <c r="B121" s="3" t="inlineStr">
+        <is>
+          <t>Gross Profit Ratio</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="3" t="inlineStr">
+        <is>
+          <t>gp%</t>
+        </is>
+      </c>
+      <c r="B122" s="3" t="inlineStr">
+        <is>
+          <t>Gross Profit Ratio</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="3" t="inlineStr">
+        <is>
+          <t>op ratio</t>
+        </is>
+      </c>
+      <c r="B123" s="3" t="inlineStr">
+        <is>
+          <t>Operating Profit Ratio</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="3" t="inlineStr">
+        <is>
+          <t>operating profit ratio</t>
+        </is>
+      </c>
+      <c r="B124" s="3" t="inlineStr">
+        <is>
+          <t>Operating Profit Ratio</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="3" t="inlineStr">
+        <is>
+          <t>variable cost ratio</t>
+        </is>
+      </c>
+      <c r="B125" s="3" t="inlineStr">
+        <is>
+          <t>Variable Cost Ratio</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="3" t="inlineStr">
+        <is>
+          <t>fixed cost ratio</t>
+        </is>
+      </c>
+      <c r="B126" s="3" t="inlineStr">
+        <is>
+          <t>Fixed Cost Ratio</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="3" t="inlineStr">
+        <is>
+          <t>fixed cost efficiency</t>
+        </is>
+      </c>
+      <c r="B127" s="3" t="inlineStr">
+        <is>
+          <t>Fixed Cost Efficiency</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="3" t="inlineStr">
+        <is>
+          <t>labor ratio</t>
+        </is>
+      </c>
+      <c r="B128" s="3" t="inlineStr">
+        <is>
+          <t>Direct Labor Ratio</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="3" t="inlineStr">
+        <is>
+          <t>direct labor ratio</t>
+        </is>
+      </c>
+      <c r="B129" s="3" t="inlineStr">
+        <is>
+          <t>Direct Labor Ratio</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="3" t="inlineStr">
+        <is>
+          <t>material ratio</t>
+        </is>
+      </c>
+      <c r="B130" s="3" t="inlineStr">
+        <is>
+          <t>Direct Material Ratio</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="3" t="inlineStr">
+        <is>
+          <t>direct material ratio</t>
+        </is>
+      </c>
+      <c r="B131" s="3" t="inlineStr">
+        <is>
+          <t>Direct Material Ratio</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="3" t="inlineStr">
+        <is>
+          <t>outsource ratio</t>
+        </is>
+      </c>
+      <c r="B132" s="3" t="inlineStr">
+        <is>
+          <t>Outsource Labor Ratio</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="3" t="inlineStr">
+        <is>
+          <t>outsource labor ratio</t>
+        </is>
+      </c>
+      <c r="B133" s="3" t="inlineStr">
+        <is>
+          <t>Outsource Labor Ratio</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="3" t="inlineStr">
+        <is>
+          <t>marginal profit ratio</t>
+        </is>
+      </c>
+      <c r="B134" s="3" t="inlineStr">
+        <is>
+          <t>Marginal Profit Ratio</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="3" t="inlineStr">
+        <is>
+          <t>marginal ratio</t>
+        </is>
+      </c>
+      <c r="B135" s="3" t="inlineStr">
+        <is>
+          <t>Marginal Profit Ratio</t>
         </is>
       </c>
     </row>
@@ -1861,7 +2102,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C38"/>
+  <dimension ref="A1:C39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -1889,7 +2130,7 @@
     <row r="2">
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>pattern: YYYY = year only, MM = month only, YYYY-MM = exact month</t>
+          <t>YYYY=year only, MM=month only, YYYY-MM=exact month</t>
         </is>
       </c>
     </row>
@@ -2184,144 +2425,156 @@
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>2018</t>
+          <t>q1</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>2018</t>
+          <t>Q1</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>2019</t>
+          <t>q2</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>2019</t>
+          <t>Q2</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>2020</t>
+          <t>q3</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>2020</t>
+          <t>Q3</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>2021</t>
+          <t>q4</t>
         </is>
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>2021</t>
+          <t>Q4</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>2018</t>
         </is>
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>2018</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>2019</t>
         </is>
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>2019</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2020</t>
         </is>
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2020</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2021</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2021</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>q1</t>
+          <t>2022</t>
         </is>
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>Q1</t>
+          <t>2022</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>q2</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>Q2</t>
+          <t>2023</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>q3</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>Q3</t>
+          <t>2024</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>q4</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>Q4</t>
+          <t>2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="3" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="B39" s="3" t="inlineStr">
+        <is>
+          <t>2026</t>
         </is>
       </c>
     </row>
@@ -2336,7 +2589,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C21"/>
+  <dimension ref="A1:C51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -2364,223 +2617,223 @@
     <row r="2">
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>site_code must match exactly with column header in data files</t>
+          <t>site_code must match data exactly (case-sensitive)</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>ppd</t>
+          <t>acw</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>PPD</t>
+          <t>ACW</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>bpa</t>
+          <t>all site</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>BPA</t>
+          <t>All Site</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>bpb</t>
+          <t>bn20</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>BPB</t>
+          <t>BN20</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>bpc</t>
+          <t>bp1</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>BPC</t>
+          <t>BP1</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>bpd</t>
+          <t>bpa</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>BPD</t>
+          <t>BPA</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>bp1</t>
+          <t>bpb</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>BP1</t>
+          <t>BPB</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>wgr</t>
+          <t>bpc</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>WGR</t>
+          <t>BPC</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>tbn1</t>
+          <t>bpd</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>TBN1</t>
+          <t>BPD</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>tbn2</t>
+          <t>cbr01</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>TBN2</t>
+          <t>CBR01</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>hmw</t>
+          <t>cbr02</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>HMW</t>
+          <t>CBR02</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>neg</t>
+          <t>cbr03</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>NeG</t>
+          <t>CBR03</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>p304</t>
+          <t>cbr04</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>P304</t>
+          <t>CBR04</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>acw</t>
+          <t>cbr05</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>ACW</t>
+          <t>CBR05</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>ssw</t>
+          <t>ccs01</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>SSW</t>
+          <t>CCS01</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>uaf</t>
+          <t>ccs02</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>UAF</t>
+          <t>CCS02</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>stf</t>
+          <t>ccs03</t>
         </is>
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>STF</t>
+          <t>CCS03</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>st9</t>
+          <t>hmw</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>ST9</t>
+          <t>HMW</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="inlineStr">
         <is>
-          <t>st11</t>
+          <t>neg</t>
         </is>
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>ST11</t>
+          <t>NeG</t>
         </is>
       </c>
     </row>
@@ -2593,6 +2846,366 @@
       <c r="B21" s="3" t="inlineStr">
         <is>
           <t>OTHER</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="3" t="inlineStr">
+        <is>
+          <t>otr01</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>OTR01</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="3" t="inlineStr">
+        <is>
+          <t>otr02</t>
+        </is>
+      </c>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>OTR02</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="3" t="inlineStr">
+        <is>
+          <t>p304</t>
+        </is>
+      </c>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>P304</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="3" t="inlineStr">
+        <is>
+          <t>pjr01</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>PJR01</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="3" t="inlineStr">
+        <is>
+          <t>ppd</t>
+        </is>
+      </c>
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>PPD</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="3" t="inlineStr">
+        <is>
+          <t>ryn01</t>
+        </is>
+      </c>
+      <c r="B27" s="3" t="inlineStr">
+        <is>
+          <t>RYN01</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="3" t="inlineStr">
+        <is>
+          <t>ryn02</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="inlineStr">
+        <is>
+          <t>RYN02</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="3" t="inlineStr">
+        <is>
+          <t>ryn03</t>
+        </is>
+      </c>
+      <c r="B29" s="3" t="inlineStr">
+        <is>
+          <t>RYN03</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="3" t="inlineStr">
+        <is>
+          <t>ryn04</t>
+        </is>
+      </c>
+      <c r="B30" s="3" t="inlineStr">
+        <is>
+          <t>RYN04</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="3" t="inlineStr">
+        <is>
+          <t>sdct</t>
+        </is>
+      </c>
+      <c r="B31" s="3" t="inlineStr">
+        <is>
+          <t>SDCT</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="3" t="inlineStr">
+        <is>
+          <t>smk01</t>
+        </is>
+      </c>
+      <c r="B32" s="3" t="inlineStr">
+        <is>
+          <t>SMK01</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="3" t="inlineStr">
+        <is>
+          <t>smk02</t>
+        </is>
+      </c>
+      <c r="B33" s="3" t="inlineStr">
+        <is>
+          <t>SMK02</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="3" t="inlineStr">
+        <is>
+          <t>smk03</t>
+        </is>
+      </c>
+      <c r="B34" s="3" t="inlineStr">
+        <is>
+          <t>SMK03</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="3" t="inlineStr">
+        <is>
+          <t>smk04</t>
+        </is>
+      </c>
+      <c r="B35" s="3" t="inlineStr">
+        <is>
+          <t>SMK04</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="3" t="inlineStr">
+        <is>
+          <t>smk05</t>
+        </is>
+      </c>
+      <c r="B36" s="3" t="inlineStr">
+        <is>
+          <t>SMK05</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="3" t="inlineStr">
+        <is>
+          <t>smk06</t>
+        </is>
+      </c>
+      <c r="B37" s="3" t="inlineStr">
+        <is>
+          <t>SMK06</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="3" t="inlineStr">
+        <is>
+          <t>smk07</t>
+        </is>
+      </c>
+      <c r="B38" s="3" t="inlineStr">
+        <is>
+          <t>SMK07</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="3" t="inlineStr">
+        <is>
+          <t>ssw</t>
+        </is>
+      </c>
+      <c r="B39" s="3" t="inlineStr">
+        <is>
+          <t>SSW</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="3" t="inlineStr">
+        <is>
+          <t>st11</t>
+        </is>
+      </c>
+      <c r="B40" s="3" t="inlineStr">
+        <is>
+          <t>ST11</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="3" t="inlineStr">
+        <is>
+          <t>st9</t>
+        </is>
+      </c>
+      <c r="B41" s="3" t="inlineStr">
+        <is>
+          <t>ST9</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="3" t="inlineStr">
+        <is>
+          <t>stf</t>
+        </is>
+      </c>
+      <c r="B42" s="3" t="inlineStr">
+        <is>
+          <t>STF</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="3" t="inlineStr">
+        <is>
+          <t>tac</t>
+        </is>
+      </c>
+      <c r="B43" s="3" t="inlineStr">
+        <is>
+          <t>TAC</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="3" t="inlineStr">
+        <is>
+          <t>tbn1</t>
+        </is>
+      </c>
+      <c r="B44" s="3" t="inlineStr">
+        <is>
+          <t>TBN1</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="3" t="inlineStr">
+        <is>
+          <t>tbn2</t>
+        </is>
+      </c>
+      <c r="B45" s="3" t="inlineStr">
+        <is>
+          <t>TBN2</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="3" t="inlineStr">
+        <is>
+          <t>uaf</t>
+        </is>
+      </c>
+      <c r="B46" s="3" t="inlineStr">
+        <is>
+          <t>UAF</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="3" t="inlineStr">
+        <is>
+          <t>wgr</t>
+        </is>
+      </c>
+      <c r="B47" s="3" t="inlineStr">
+        <is>
+          <t>WGR</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="3" t="inlineStr">
+        <is>
+          <t>zc</t>
+        </is>
+      </c>
+      <c r="B48" s="3" t="inlineStr">
+        <is>
+          <t>ZC</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="3" t="inlineStr">
+        <is>
+          <t>all site</t>
+        </is>
+      </c>
+      <c r="B49" s="3" t="inlineStr">
+        <is>
+          <t>All Site</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="3" t="inlineStr">
+        <is>
+          <t>all sites</t>
+        </is>
+      </c>
+      <c r="B50" s="3" t="inlineStr">
+        <is>
+          <t>All Site</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="3" t="inlineStr">
+        <is>
+          <t>total</t>
+        </is>
+      </c>
+      <c r="B51" s="3" t="inlineStr">
+        <is>
+          <t>All Site</t>
         </is>
       </c>
     </row>
@@ -2607,7 +3220,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C36"/>
+  <dimension ref="A1:C38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
@@ -2635,7 +3248,7 @@
     <row r="2">
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>intent types: compare, trend, summary, top, bottom, help, list</t>
+          <t>intent types: compare, trend, summary, top, bottom, help, list, count</t>
         </is>
       </c>
     </row>
@@ -2762,19 +3375,19 @@
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>summary</t>
+          <t>yearly</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>summary</t>
+          <t>trend</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>overview</t>
+          <t>summary</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -2786,7 +3399,7 @@
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>overall</t>
+          <t>overview</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
@@ -2798,7 +3411,7 @@
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>total</t>
+          <t>overall</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -3002,31 +3615,31 @@
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>chart</t>
+          <t>how many</t>
         </is>
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>chart</t>
+          <t>count</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>graph</t>
+          <t>count</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>chart</t>
+          <t>count</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>plot</t>
+          <t>chart</t>
         </is>
       </c>
       <c r="B35" s="3" t="inlineStr">
@@ -3038,10 +3651,34 @@
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
         <is>
+          <t>graph</t>
+        </is>
+      </c>
+      <c r="B36" s="3" t="inlineStr">
+        <is>
+          <t>chart</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="3" t="inlineStr">
+        <is>
+          <t>plot</t>
+        </is>
+      </c>
+      <c r="B37" s="3" t="inlineStr">
+        <is>
+          <t>chart</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="3" t="inlineStr">
+        <is>
           <t>visual</t>
         </is>
       </c>
-      <c r="B36" s="3" t="inlineStr">
+      <c r="B38" s="3" t="inlineStr">
         <is>
           <t>chart</t>
         </is>
@@ -3086,7 +3723,7 @@
     <row r="2">
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Keywords that trigger the customer dataset instead of balance spec</t>
+          <t>Keywords that route query to customer dataset</t>
         </is>
       </c>
     </row>
@@ -3291,6 +3928,241 @@
       <c r="B19" s="3" t="inlineStr">
         <is>
           <t>trigger</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C18"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="25" customWidth="1" min="1" max="1"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="55" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>keyword</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>category</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>note</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>category must match Item column in P&amp;L data exactly</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>variable</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>Variable Cost</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>variable cost</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>Variable Cost</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>fixed</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>Fixed Cost</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>fixed cost</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>Fixed Cost</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>fix cost</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>Fixed Cost</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="inlineStr">
+        <is>
+          <t>fix</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>Fixed Cost</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>expense</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="inlineStr">
+        <is>
+          <t>expenses</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>kpi</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>KPI</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="inlineStr">
+        <is>
+          <t>ratio</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>KPI</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>indicator</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>KPI</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="inlineStr">
+        <is>
+          <t>p&amp;l</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>P&amp;L Statement</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>pnl</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>P&amp;L Statement</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="3" t="inlineStr">
+        <is>
+          <t>profit loss</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>P&amp;L Statement</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>profit and loss</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>P&amp;L Statement</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="3" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>Other</t>
         </is>
       </c>
     </row>

--- a/keyword.xlsx
+++ b/keyword.xlsx
@@ -102,7 +102,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
@@ -110,6 +110,8 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -512,5378 +514,4741 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>── Revenue Total ──</t>
-        </is>
-      </c>
-      <c r="B3" s="3" t="inlineStr"/>
-      <c r="C3" s="3" t="inlineStr"/>
+          <t>── Allowance ──</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="n"/>
+      <c r="C3" s="3" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="4" t="inlineStr">
         <is>
-          <t>revenue</t>
+          <t>allowance</t>
         </is>
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>Revenue Total</t>
-        </is>
-      </c>
+          <t>Allowance</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="n"/>
     </row>
     <row r="5">
-      <c r="A5" s="4" t="inlineStr">
-        <is>
-          <t>revenues</t>
-        </is>
-      </c>
-      <c r="B5" s="4" t="inlineStr">
-        <is>
-          <t>Revenue Total</t>
-        </is>
-      </c>
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>── Bonus ──</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="n"/>
+      <c r="C5" s="5" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>income</t>
+          <t>bonus</t>
         </is>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>Revenue Total</t>
-        </is>
-      </c>
+          <t>Bonus</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="4" t="inlineStr">
-        <is>
-          <t>sales</t>
-        </is>
-      </c>
-      <c r="B7" s="4" t="inlineStr">
-        <is>
-          <t>Revenue Total</t>
-        </is>
-      </c>
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>── CLAIM FROM CUSTOMER ──</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="n"/>
+      <c r="C7" s="5" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>rev</t>
+          <t>claim from</t>
         </is>
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>Revenue Total</t>
-        </is>
-      </c>
+          <t>CLAIM FROM CUSTOMER</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>total revenue</t>
+          <t>claim from customer</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>Revenue Total</t>
-        </is>
-      </c>
+          <t>CLAIM FROM CUSTOMER</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>revenue total</t>
+          <t>claimfrom</t>
         </is>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>Revenue Total</t>
-        </is>
-      </c>
+          <t>CLAIM FROM CUSTOMER</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>turnover</t>
+          <t>claimfromcustomer</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>Revenue Total</t>
-        </is>
-      </c>
+          <t>CLAIM FROM CUSTOMER</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t>top line</t>
+          <t>customer from claim</t>
         </is>
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>Revenue Total</t>
-        </is>
-      </c>
+          <t>CLAIM FROM CUSTOMER</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>topline</t>
+          <t>customerfromclaim</t>
         </is>
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>Revenue Total</t>
-        </is>
-      </c>
+          <t>CLAIM FROM CUSTOMER</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
         <is>
-          <t>billing</t>
+          <t>from customer</t>
         </is>
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>Revenue Total</t>
-        </is>
-      </c>
+          <t>CLAIM FROM CUSTOMER</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>invoiced</t>
+          <t>fromcustomer</t>
         </is>
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>Revenue Total</t>
-        </is>
-      </c>
+          <t>CLAIM FROM CUSTOMER</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="4" t="inlineStr">
-        <is>
-          <t>earned</t>
-        </is>
-      </c>
-      <c r="B16" s="4" t="inlineStr">
-        <is>
-          <t>Revenue Total</t>
-        </is>
-      </c>
+      <c r="A16" s="3" t="inlineStr">
+        <is>
+          <t>── Cleaning Expense ──</t>
+        </is>
+      </c>
+      <c r="B16" s="4" t="n"/>
+      <c r="C16" s="5" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>how much we earn</t>
+          <t>cleaning expense</t>
         </is>
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>Revenue Total</t>
-        </is>
-      </c>
+          <t>Cleaning Expense</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
         <is>
-          <t>how much we made</t>
+          <t>cleaningexpense</t>
         </is>
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>Revenue Total</t>
-        </is>
-      </c>
+          <t>Cleaning Expense</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>money coming in</t>
+          <t>expense cleaning</t>
         </is>
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>Revenue Total</t>
-        </is>
-      </c>
+          <t>Cleaning Expense</t>
+        </is>
+      </c>
+      <c r="C19" s="5" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
         <is>
-          <t>money in</t>
+          <t>expensecleaning</t>
         </is>
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>Revenue Total</t>
-        </is>
-      </c>
+          <t>Cleaning Expense</t>
+        </is>
+      </c>
+      <c r="C20" s="5" t="n"/>
     </row>
     <row r="21">
-      <c r="A21" s="4" t="inlineStr">
-        <is>
-          <t>รายได้</t>
-        </is>
-      </c>
-      <c r="B21" s="4" t="inlineStr">
-        <is>
-          <t>Revenue Total</t>
-        </is>
-      </c>
+      <c r="A21" s="3" t="inlineStr">
+        <is>
+          <t>── Common expense ──</t>
+        </is>
+      </c>
+      <c r="B21" s="4" t="n"/>
+      <c r="C21" s="5" t="n"/>
     </row>
     <row r="22">
-      <c r="A22" s="3" t="inlineStr">
-        <is>
-          <t>── Material and Service ──</t>
-        </is>
-      </c>
-      <c r="B22" s="3" t="inlineStr"/>
-      <c r="C22" s="3" t="inlineStr"/>
+      <c r="A22" s="6" t="inlineStr">
+        <is>
+          <t>common expense</t>
+        </is>
+      </c>
+      <c r="B22" s="6" t="inlineStr">
+        <is>
+          <t>Common expense</t>
+        </is>
+      </c>
+      <c r="C22" s="3" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="4" t="inlineStr">
         <is>
-          <t>material</t>
+          <t>commonexpense</t>
         </is>
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>Material and Service</t>
-        </is>
-      </c>
+          <t>Common expense</t>
+        </is>
+      </c>
+      <c r="C23" s="5" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="4" t="inlineStr">
         <is>
-          <t>material and service</t>
+          <t>expense common</t>
         </is>
       </c>
       <c r="B24" s="4" t="inlineStr">
         <is>
-          <t>Material and Service</t>
-        </is>
-      </c>
+          <t>Common expense</t>
+        </is>
+      </c>
+      <c r="C24" s="5" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="4" t="inlineStr">
         <is>
-          <t>material &amp; service</t>
+          <t>expensecommon</t>
         </is>
       </c>
       <c r="B25" s="4" t="inlineStr">
         <is>
-          <t>Material and Service</t>
-        </is>
-      </c>
+          <t>Common expense</t>
+        </is>
+      </c>
+      <c r="C25" s="5" t="n"/>
     </row>
     <row r="26">
-      <c r="A26" s="4" t="inlineStr">
-        <is>
-          <t>materials</t>
-        </is>
-      </c>
-      <c r="B26" s="4" t="inlineStr">
-        <is>
-          <t>Material and Service</t>
-        </is>
-      </c>
+      <c r="A26" s="3" t="inlineStr">
+        <is>
+          <t>── Conference ──</t>
+        </is>
+      </c>
+      <c r="B26" s="4" t="n"/>
+      <c r="C26" s="5" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="4" t="inlineStr">
         <is>
-          <t>subcontract</t>
+          <t>conference</t>
         </is>
       </c>
       <c r="B27" s="4" t="inlineStr">
         <is>
-          <t>Material and Service</t>
-        </is>
-      </c>
+          <t>Conference</t>
+        </is>
+      </c>
+      <c r="C27" s="5" t="n"/>
     </row>
     <row r="28">
-      <c r="A28" s="4" t="inlineStr">
-        <is>
-          <t>subcontractor</t>
-        </is>
-      </c>
-      <c r="B28" s="4" t="inlineStr">
-        <is>
-          <t>Material and Service</t>
-        </is>
-      </c>
+      <c r="A28" s="3" t="inlineStr">
+        <is>
+          <t>── Consumable Supply ──</t>
+        </is>
+      </c>
+      <c r="B28" s="4" t="n"/>
+      <c r="C28" s="5" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="4" t="inlineStr">
         <is>
-          <t>sub cost</t>
+          <t>consumable supply</t>
         </is>
       </c>
       <c r="B29" s="4" t="inlineStr">
         <is>
-          <t>Material and Service</t>
-        </is>
-      </c>
+          <t>Consumable Supply</t>
+        </is>
+      </c>
+      <c r="C29" s="5" t="n"/>
     </row>
     <row r="30">
       <c r="A30" s="4" t="inlineStr">
         <is>
-          <t>sub-contract</t>
+          <t>consumablesupply</t>
         </is>
       </c>
       <c r="B30" s="4" t="inlineStr">
         <is>
-          <t>Material and Service</t>
-        </is>
-      </c>
+          <t>Consumable Supply</t>
+        </is>
+      </c>
+      <c r="C30" s="5" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="4" t="inlineStr">
         <is>
-          <t>vendor cost</t>
+          <t>supply consumable</t>
         </is>
       </c>
       <c r="B31" s="4" t="inlineStr">
         <is>
-          <t>Material and Service</t>
-        </is>
-      </c>
+          <t>Consumable Supply</t>
+        </is>
+      </c>
+      <c r="C31" s="5" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="4" t="inlineStr">
         <is>
-          <t>supplier cost</t>
+          <t>supplyconsumable</t>
         </is>
       </c>
       <c r="B32" s="4" t="inlineStr">
         <is>
-          <t>Material and Service</t>
-        </is>
-      </c>
+          <t>Consumable Supply</t>
+        </is>
+      </c>
+      <c r="C32" s="5" t="n"/>
     </row>
     <row r="33">
-      <c r="A33" s="4" t="inlineStr">
-        <is>
-          <t>outsource material</t>
-        </is>
-      </c>
-      <c r="B33" s="4" t="inlineStr">
-        <is>
-          <t>Material and Service</t>
-        </is>
-      </c>
+      <c r="A33" s="3" t="inlineStr">
+        <is>
+          <t>── Cost (Adjust) ──</t>
+        </is>
+      </c>
+      <c r="B33" s="4" t="n"/>
+      <c r="C33" s="5" t="n"/>
     </row>
     <row r="34">
       <c r="A34" s="4" t="inlineStr">
         <is>
-          <t>direct material</t>
+          <t>adjust cost</t>
         </is>
       </c>
       <c r="B34" s="4" t="inlineStr">
         <is>
-          <t>Material and Service</t>
-        </is>
-      </c>
+          <t>Cost (Adjust)</t>
+        </is>
+      </c>
+      <c r="C34" s="5" t="n"/>
     </row>
     <row r="35">
       <c r="A35" s="4" t="inlineStr">
         <is>
-          <t>raw material</t>
+          <t>adjustcost</t>
         </is>
       </c>
       <c r="B35" s="4" t="inlineStr">
         <is>
-          <t>Material and Service</t>
-        </is>
-      </c>
+          <t>Cost (Adjust)</t>
+        </is>
+      </c>
+      <c r="C35" s="5" t="n"/>
     </row>
     <row r="36">
       <c r="A36" s="4" t="inlineStr">
         <is>
-          <t>material cost</t>
+          <t>cost (adjust)</t>
         </is>
       </c>
       <c r="B36" s="4" t="inlineStr">
         <is>
-          <t>Material and Service</t>
-        </is>
-      </c>
+          <t>Cost (Adjust)</t>
+        </is>
+      </c>
+      <c r="C36" s="5" t="n"/>
     </row>
     <row r="37">
       <c r="A37" s="4" t="inlineStr">
         <is>
-          <t>วัสดุ</t>
+          <t>cost adjust</t>
         </is>
       </c>
       <c r="B37" s="4" t="inlineStr">
         <is>
-          <t>Material and Service</t>
-        </is>
-      </c>
+          <t>Cost (Adjust)</t>
+        </is>
+      </c>
+      <c r="C37" s="5" t="n"/>
     </row>
     <row r="38">
-      <c r="A38" s="3" t="inlineStr">
-        <is>
-          <t>── Salary ──</t>
-        </is>
-      </c>
-      <c r="B38" s="3" t="inlineStr"/>
-      <c r="C38" s="3" t="inlineStr"/>
+      <c r="A38" s="6" t="inlineStr">
+        <is>
+          <t>costadjust</t>
+        </is>
+      </c>
+      <c r="B38" s="6" t="inlineStr">
+        <is>
+          <t>Cost (Adjust)</t>
+        </is>
+      </c>
+      <c r="C38" s="3" t="n"/>
     </row>
     <row r="39">
-      <c r="A39" s="4" t="inlineStr">
-        <is>
-          <t>salary</t>
-        </is>
-      </c>
-      <c r="B39" s="4" t="inlineStr">
-        <is>
-          <t>Salary</t>
-        </is>
-      </c>
+      <c r="A39" s="3" t="inlineStr">
+        <is>
+          <t>── Cost Total ──</t>
+        </is>
+      </c>
+      <c r="B39" s="4" t="n"/>
+      <c r="C39" s="5" t="n"/>
     </row>
     <row r="40">
       <c r="A40" s="4" t="inlineStr">
         <is>
-          <t>salaries</t>
+          <t>cost total</t>
         </is>
       </c>
       <c r="B40" s="4" t="inlineStr">
         <is>
-          <t>Salary</t>
-        </is>
-      </c>
+          <t>Cost Total</t>
+        </is>
+      </c>
+      <c r="C40" s="5" t="n"/>
     </row>
     <row r="41">
       <c r="A41" s="4" t="inlineStr">
         <is>
-          <t>wage</t>
+          <t>costtotal</t>
         </is>
       </c>
       <c r="B41" s="4" t="inlineStr">
         <is>
-          <t>Salary</t>
-        </is>
-      </c>
+          <t>Cost Total</t>
+        </is>
+      </c>
+      <c r="C41" s="5" t="n"/>
     </row>
     <row r="42">
-      <c r="A42" s="4" t="inlineStr">
-        <is>
-          <t>wages</t>
+      <c r="A42" s="6" t="inlineStr">
+        <is>
+          <t>total cost</t>
         </is>
       </c>
       <c r="B42" s="4" t="inlineStr">
         <is>
-          <t>Salary</t>
-        </is>
-      </c>
+          <t>Cost Total</t>
+        </is>
+      </c>
+      <c r="C42" s="5" t="n"/>
     </row>
     <row r="43">
-      <c r="A43" s="4" t="inlineStr">
-        <is>
-          <t>base pay</t>
+      <c r="A43" s="6" t="inlineStr">
+        <is>
+          <t>totalcost</t>
         </is>
       </c>
       <c r="B43" s="4" t="inlineStr">
         <is>
-          <t>Salary</t>
-        </is>
-      </c>
+          <t>Cost Total</t>
+        </is>
+      </c>
+      <c r="C43" s="5" t="n"/>
     </row>
     <row r="44">
-      <c r="A44" s="4" t="inlineStr">
-        <is>
-          <t>base salary</t>
-        </is>
-      </c>
-      <c r="B44" s="4" t="inlineStr">
-        <is>
-          <t>Salary</t>
-        </is>
-      </c>
+      <c r="A44" s="3" t="inlineStr">
+        <is>
+          <t>── Depreciation ──</t>
+        </is>
+      </c>
+      <c r="B44" s="4" t="n"/>
+      <c r="C44" s="5" t="n"/>
     </row>
     <row r="45">
-      <c r="A45" s="4" t="inlineStr">
-        <is>
-          <t>payroll</t>
+      <c r="A45" s="6" t="inlineStr">
+        <is>
+          <t>depreciation</t>
         </is>
       </c>
       <c r="B45" s="4" t="inlineStr">
         <is>
-          <t>Salary</t>
-        </is>
-      </c>
+          <t>Depreciation</t>
+        </is>
+      </c>
+      <c r="C45" s="5" t="n"/>
     </row>
     <row r="46">
-      <c r="A46" s="4" t="inlineStr">
-        <is>
-          <t>monthly pay</t>
-        </is>
-      </c>
-      <c r="B46" s="4" t="inlineStr">
-        <is>
-          <t>Salary</t>
-        </is>
-      </c>
+      <c r="A46" s="3" t="inlineStr">
+        <is>
+          <t>── Direct Labor Ratio ──</t>
+        </is>
+      </c>
+      <c r="B46" s="4" t="n"/>
+      <c r="C46" s="5" t="n"/>
     </row>
     <row r="47">
       <c r="A47" s="4" t="inlineStr">
         <is>
-          <t>employee pay</t>
+          <t>direct labor</t>
         </is>
       </c>
       <c r="B47" s="4" t="inlineStr">
         <is>
-          <t>Salary</t>
-        </is>
-      </c>
+          <t>Direct Labor Ratio</t>
+        </is>
+      </c>
+      <c r="C47" s="5" t="n"/>
     </row>
     <row r="48">
       <c r="A48" s="4" t="inlineStr">
         <is>
-          <t>staff salary</t>
+          <t>direct labor ratio</t>
         </is>
       </c>
       <c r="B48" s="4" t="inlineStr">
         <is>
-          <t>Salary</t>
-        </is>
-      </c>
+          <t>Direct Labor Ratio</t>
+        </is>
+      </c>
+      <c r="C48" s="5" t="n"/>
     </row>
     <row r="49">
       <c r="A49" s="4" t="inlineStr">
         <is>
-          <t>staff pay</t>
+          <t>directlabor</t>
         </is>
       </c>
       <c r="B49" s="4" t="inlineStr">
         <is>
-          <t>Salary</t>
-        </is>
-      </c>
+          <t>Direct Labor Ratio</t>
+        </is>
+      </c>
+      <c r="C49" s="5" t="n"/>
     </row>
     <row r="50">
       <c r="A50" s="4" t="inlineStr">
         <is>
-          <t>compensation</t>
+          <t>directlaborratio</t>
         </is>
       </c>
       <c r="B50" s="4" t="inlineStr">
         <is>
-          <t>Salary</t>
-        </is>
-      </c>
+          <t>Direct Labor Ratio</t>
+        </is>
+      </c>
+      <c r="C50" s="5" t="n"/>
     </row>
     <row r="51">
-      <c r="A51" s="4" t="inlineStr">
-        <is>
-          <t>remuneration</t>
+      <c r="A51" s="6" t="inlineStr">
+        <is>
+          <t>labor ratio</t>
         </is>
       </c>
       <c r="B51" s="4" t="inlineStr">
         <is>
-          <t>Salary</t>
-        </is>
-      </c>
+          <t>Direct Labor Ratio</t>
+        </is>
+      </c>
+      <c r="C51" s="5" t="n"/>
     </row>
     <row r="52">
       <c r="A52" s="4" t="inlineStr">
         <is>
-          <t>basic salary</t>
+          <t>laborratio</t>
         </is>
       </c>
       <c r="B52" s="4" t="inlineStr">
         <is>
-          <t>Salary</t>
-        </is>
-      </c>
+          <t>Direct Labor Ratio</t>
+        </is>
+      </c>
+      <c r="C52" s="5" t="n"/>
     </row>
     <row r="53">
       <c r="A53" s="4" t="inlineStr">
         <is>
-          <t>basic pay</t>
+          <t>ratio labor direct</t>
         </is>
       </c>
       <c r="B53" s="4" t="inlineStr">
         <is>
-          <t>Salary</t>
-        </is>
-      </c>
+          <t>Direct Labor Ratio</t>
+        </is>
+      </c>
+      <c r="C53" s="5" t="n"/>
     </row>
     <row r="54">
-      <c r="A54" s="4" t="inlineStr">
-        <is>
-          <t>เงินเดือน</t>
+      <c r="A54" s="6" t="inlineStr">
+        <is>
+          <t>ratiolabordirect</t>
         </is>
       </c>
       <c r="B54" s="4" t="inlineStr">
         <is>
-          <t>Salary</t>
-        </is>
-      </c>
+          <t>Direct Labor Ratio</t>
+        </is>
+      </c>
+      <c r="C54" s="5" t="n"/>
     </row>
     <row r="55">
       <c r="A55" s="3" t="inlineStr">
         <is>
-          <t>── Over Time ──</t>
-        </is>
-      </c>
-      <c r="B55" s="3" t="inlineStr"/>
-      <c r="C55" s="3" t="inlineStr"/>
+          <t>── Direct Material Ratio ──</t>
+        </is>
+      </c>
+      <c r="B55" s="6" t="n"/>
+      <c r="C55" s="3" t="n"/>
     </row>
     <row r="56">
       <c r="A56" s="4" t="inlineStr">
         <is>
-          <t>overtime</t>
+          <t>direct material</t>
         </is>
       </c>
       <c r="B56" s="4" t="inlineStr">
         <is>
-          <t>Over Time</t>
-        </is>
-      </c>
+          <t>Direct Material Ratio</t>
+        </is>
+      </c>
+      <c r="C56" s="5" t="n"/>
     </row>
     <row r="57">
       <c r="A57" s="4" t="inlineStr">
         <is>
-          <t>over time</t>
+          <t>direct material ratio</t>
         </is>
       </c>
       <c r="B57" s="4" t="inlineStr">
         <is>
-          <t>Over Time</t>
-        </is>
-      </c>
+          <t>Direct Material Ratio</t>
+        </is>
+      </c>
+      <c r="C57" s="5" t="n"/>
     </row>
     <row r="58">
       <c r="A58" s="4" t="inlineStr">
         <is>
-          <t>ot</t>
+          <t>directmaterial</t>
         </is>
       </c>
       <c r="B58" s="4" t="inlineStr">
         <is>
-          <t>Over Time</t>
-        </is>
-      </c>
+          <t>Direct Material Ratio</t>
+        </is>
+      </c>
+      <c r="C58" s="5" t="n"/>
     </row>
     <row r="59">
       <c r="A59" s="4" t="inlineStr">
         <is>
-          <t>ot cost</t>
+          <t>directmaterialratio</t>
         </is>
       </c>
       <c r="B59" s="4" t="inlineStr">
         <is>
-          <t>Over Time</t>
-        </is>
-      </c>
+          <t>Direct Material Ratio</t>
+        </is>
+      </c>
+      <c r="C59" s="5" t="n"/>
     </row>
     <row r="60">
-      <c r="A60" s="4" t="inlineStr">
-        <is>
-          <t>overtime cost</t>
+      <c r="A60" s="6" t="inlineStr">
+        <is>
+          <t>material ratio</t>
         </is>
       </c>
       <c r="B60" s="4" t="inlineStr">
         <is>
-          <t>Over Time</t>
-        </is>
-      </c>
+          <t>Direct Material Ratio</t>
+        </is>
+      </c>
+      <c r="C60" s="5" t="n"/>
     </row>
     <row r="61">
       <c r="A61" s="4" t="inlineStr">
         <is>
-          <t>overtime pay</t>
+          <t>materialratio</t>
         </is>
       </c>
       <c r="B61" s="4" t="inlineStr">
         <is>
-          <t>Over Time</t>
-        </is>
-      </c>
+          <t>Direct Material Ratio</t>
+        </is>
+      </c>
+      <c r="C61" s="5" t="n"/>
     </row>
     <row r="62">
       <c r="A62" s="4" t="inlineStr">
         <is>
-          <t>extra hours</t>
+          <t>ratio material direct</t>
         </is>
       </c>
       <c r="B62" s="4" t="inlineStr">
         <is>
-          <t>Over Time</t>
-        </is>
-      </c>
+          <t>Direct Material Ratio</t>
+        </is>
+      </c>
+      <c r="C62" s="5" t="n"/>
     </row>
     <row r="63">
-      <c r="A63" s="4" t="inlineStr">
-        <is>
-          <t>overtime expense</t>
+      <c r="A63" s="6" t="inlineStr">
+        <is>
+          <t>ratiomaterialdirect</t>
         </is>
       </c>
       <c r="B63" s="4" t="inlineStr">
         <is>
-          <t>Over Time</t>
-        </is>
-      </c>
+          <t>Direct Material Ratio</t>
+        </is>
+      </c>
+      <c r="C63" s="5" t="n"/>
     </row>
     <row r="64">
-      <c r="A64" s="4" t="inlineStr">
-        <is>
-          <t>overtime payment</t>
-        </is>
-      </c>
-      <c r="B64" s="4" t="inlineStr">
-        <is>
-          <t>Over Time</t>
-        </is>
-      </c>
+      <c r="A64" s="3" t="inlineStr">
+        <is>
+          <t>── Electric&amp;Water Supply ──</t>
+        </is>
+      </c>
+      <c r="B64" s="4" t="n"/>
+      <c r="C64" s="5" t="n"/>
     </row>
     <row r="65">
       <c r="A65" s="4" t="inlineStr">
         <is>
-          <t>ค่าล่วงเวลา</t>
+          <t>electric water</t>
         </is>
       </c>
       <c r="B65" s="4" t="inlineStr">
         <is>
-          <t>Over Time</t>
-        </is>
-      </c>
+          <t>Electric&amp;Water Supply</t>
+        </is>
+      </c>
+      <c r="C65" s="5" t="n"/>
     </row>
     <row r="66">
       <c r="A66" s="4" t="inlineStr">
         <is>
-          <t>โอที</t>
+          <t>electric water supply</t>
         </is>
       </c>
       <c r="B66" s="4" t="inlineStr">
         <is>
-          <t>Over Time</t>
-        </is>
-      </c>
+          <t>Electric&amp;Water Supply</t>
+        </is>
+      </c>
+      <c r="C66" s="5" t="n"/>
     </row>
     <row r="67">
-      <c r="A67" s="3" t="inlineStr">
-        <is>
-          <t>── Bonus ──</t>
-        </is>
-      </c>
-      <c r="B67" s="3" t="inlineStr"/>
-      <c r="C67" s="3" t="inlineStr"/>
+      <c r="A67" s="6" t="inlineStr">
+        <is>
+          <t>electric&amp;water supply</t>
+        </is>
+      </c>
+      <c r="B67" s="6" t="inlineStr">
+        <is>
+          <t>Electric&amp;Water Supply</t>
+        </is>
+      </c>
+      <c r="C67" s="3" t="n"/>
     </row>
     <row r="68">
       <c r="A68" s="4" t="inlineStr">
         <is>
-          <t>bonus</t>
+          <t>electricwater</t>
         </is>
       </c>
       <c r="B68" s="4" t="inlineStr">
         <is>
-          <t>Bonus</t>
-        </is>
-      </c>
+          <t>Electric&amp;Water Supply</t>
+        </is>
+      </c>
+      <c r="C68" s="5" t="n"/>
     </row>
     <row r="69">
       <c r="A69" s="4" t="inlineStr">
         <is>
-          <t>bonuses</t>
+          <t>electricwatersupply</t>
         </is>
       </c>
       <c r="B69" s="4" t="inlineStr">
         <is>
-          <t>Bonus</t>
-        </is>
-      </c>
+          <t>Electric&amp;Water Supply</t>
+        </is>
+      </c>
+      <c r="C69" s="5" t="n"/>
     </row>
     <row r="70">
-      <c r="A70" s="4" t="inlineStr">
-        <is>
-          <t>incentive</t>
+      <c r="A70" s="6" t="inlineStr">
+        <is>
+          <t>supply water electric</t>
         </is>
       </c>
       <c r="B70" s="4" t="inlineStr">
         <is>
-          <t>Bonus</t>
-        </is>
-      </c>
+          <t>Electric&amp;Water Supply</t>
+        </is>
+      </c>
+      <c r="C70" s="5" t="n"/>
     </row>
     <row r="71">
       <c r="A71" s="4" t="inlineStr">
         <is>
-          <t>incentives</t>
+          <t>supplywaterelectric</t>
         </is>
       </c>
       <c r="B71" s="4" t="inlineStr">
         <is>
-          <t>Bonus</t>
-        </is>
-      </c>
+          <t>Electric&amp;Water Supply</t>
+        </is>
+      </c>
+      <c r="C71" s="5" t="n"/>
     </row>
     <row r="72">
-      <c r="A72" s="4" t="inlineStr">
-        <is>
-          <t>performance bonus</t>
+      <c r="A72" s="6" t="inlineStr">
+        <is>
+          <t>water supply</t>
         </is>
       </c>
       <c r="B72" s="4" t="inlineStr">
         <is>
-          <t>Bonus</t>
-        </is>
-      </c>
+          <t>Electric&amp;Water Supply</t>
+        </is>
+      </c>
+      <c r="C72" s="5" t="n"/>
     </row>
     <row r="73">
-      <c r="A73" s="4" t="inlineStr">
-        <is>
-          <t>annual bonus</t>
+      <c r="A73" s="6" t="inlineStr">
+        <is>
+          <t>watersupply</t>
         </is>
       </c>
       <c r="B73" s="4" t="inlineStr">
         <is>
-          <t>Bonus</t>
-        </is>
-      </c>
+          <t>Electric&amp;Water Supply</t>
+        </is>
+      </c>
+      <c r="C73" s="5" t="n"/>
     </row>
     <row r="74">
-      <c r="A74" s="4" t="inlineStr">
-        <is>
-          <t>year-end bonus</t>
-        </is>
-      </c>
-      <c r="B74" s="4" t="inlineStr">
-        <is>
-          <t>Bonus</t>
-        </is>
-      </c>
+      <c r="A74" s="3" t="inlineStr">
+        <is>
+          <t>── Entertainment ──</t>
+        </is>
+      </c>
+      <c r="B74" s="4" t="n"/>
+      <c r="C74" s="5" t="n"/>
     </row>
     <row r="75">
-      <c r="A75" s="4" t="inlineStr">
-        <is>
-          <t>yearend bonus</t>
+      <c r="A75" s="6" t="inlineStr">
+        <is>
+          <t>entertainment</t>
         </is>
       </c>
       <c r="B75" s="4" t="inlineStr">
         <is>
-          <t>Bonus</t>
-        </is>
-      </c>
+          <t>Entertainment</t>
+        </is>
+      </c>
+      <c r="C75" s="5" t="n"/>
     </row>
     <row r="76">
-      <c r="A76" s="4" t="inlineStr">
-        <is>
-          <t>โบนัส</t>
-        </is>
-      </c>
-      <c r="B76" s="4" t="inlineStr">
-        <is>
-          <t>Bonus</t>
-        </is>
-      </c>
+      <c r="A76" s="3" t="inlineStr">
+        <is>
+          <t>── Expense (Adjust) ──</t>
+        </is>
+      </c>
+      <c r="B76" s="4" t="n"/>
+      <c r="C76" s="5" t="n"/>
     </row>
     <row r="77">
-      <c r="A77" s="3" t="inlineStr">
-        <is>
-          <t>── Social security ──</t>
-        </is>
-      </c>
-      <c r="B77" s="3" t="inlineStr"/>
-      <c r="C77" s="3" t="inlineStr"/>
+      <c r="A77" s="6" t="inlineStr">
+        <is>
+          <t>adjust expense</t>
+        </is>
+      </c>
+      <c r="B77" s="6" t="inlineStr">
+        <is>
+          <t>Expense (Adjust)</t>
+        </is>
+      </c>
+      <c r="C77" s="3" t="n"/>
     </row>
     <row r="78">
-      <c r="A78" s="4" t="inlineStr">
-        <is>
-          <t>social security</t>
+      <c r="A78" s="6" t="inlineStr">
+        <is>
+          <t>adjustexpense</t>
         </is>
       </c>
       <c r="B78" s="4" t="inlineStr">
         <is>
-          <t>Social security</t>
-        </is>
-      </c>
+          <t>Expense (Adjust)</t>
+        </is>
+      </c>
+      <c r="C78" s="5" t="n"/>
     </row>
     <row r="79">
       <c r="A79" s="4" t="inlineStr">
         <is>
-          <t>ss</t>
+          <t>expense (adjust)</t>
         </is>
       </c>
       <c r="B79" s="4" t="inlineStr">
         <is>
-          <t>Social security</t>
-        </is>
-      </c>
+          <t>Expense (Adjust)</t>
+        </is>
+      </c>
+      <c r="C79" s="5" t="n"/>
     </row>
     <row r="80">
       <c r="A80" s="4" t="inlineStr">
         <is>
-          <t>sso</t>
+          <t>expense adjust</t>
         </is>
       </c>
       <c r="B80" s="4" t="inlineStr">
         <is>
-          <t>Social security</t>
-        </is>
-      </c>
+          <t>Expense (Adjust)</t>
+        </is>
+      </c>
+      <c r="C80" s="5" t="n"/>
     </row>
     <row r="81">
-      <c r="A81" s="4" t="inlineStr">
-        <is>
-          <t>social insurance</t>
+      <c r="A81" s="6" t="inlineStr">
+        <is>
+          <t>expenseadjust</t>
         </is>
       </c>
       <c r="B81" s="4" t="inlineStr">
         <is>
-          <t>Social security</t>
-        </is>
-      </c>
+          <t>Expense (Adjust)</t>
+        </is>
+      </c>
+      <c r="C81" s="5" t="n"/>
     </row>
     <row r="82">
-      <c r="A82" s="4" t="inlineStr">
-        <is>
-          <t>social contribution</t>
-        </is>
-      </c>
-      <c r="B82" s="4" t="inlineStr">
-        <is>
-          <t>Social security</t>
-        </is>
-      </c>
+      <c r="A82" s="3" t="inlineStr">
+        <is>
+          <t>── Expense Total ──</t>
+        </is>
+      </c>
+      <c r="B82" s="4" t="n"/>
+      <c r="C82" s="5" t="n"/>
     </row>
     <row r="83">
-      <c r="A83" s="4" t="inlineStr">
-        <is>
-          <t>social fund</t>
+      <c r="A83" s="6" t="inlineStr">
+        <is>
+          <t>expense total</t>
         </is>
       </c>
       <c r="B83" s="4" t="inlineStr">
         <is>
-          <t>Social security</t>
-        </is>
-      </c>
+          <t>Expense Total</t>
+        </is>
+      </c>
+      <c r="C83" s="5" t="n"/>
     </row>
     <row r="84">
       <c r="A84" s="4" t="inlineStr">
         <is>
-          <t>ประกันสังคม</t>
+          <t>expensetotal</t>
         </is>
       </c>
       <c r="B84" s="4" t="inlineStr">
         <is>
-          <t>Social security</t>
-        </is>
-      </c>
+          <t>Expense Total</t>
+        </is>
+      </c>
+      <c r="C84" s="5" t="n"/>
     </row>
     <row r="85">
-      <c r="A85" s="3" t="inlineStr">
-        <is>
-          <t>── Welfare ──</t>
-        </is>
-      </c>
-      <c r="B85" s="3" t="inlineStr"/>
-      <c r="C85" s="3" t="inlineStr"/>
+      <c r="A85" s="6" t="inlineStr">
+        <is>
+          <t>total expense</t>
+        </is>
+      </c>
+      <c r="B85" s="6" t="inlineStr">
+        <is>
+          <t>Expense Total</t>
+        </is>
+      </c>
+      <c r="C85" s="3" t="n"/>
     </row>
     <row r="86">
-      <c r="A86" s="4" t="inlineStr">
-        <is>
-          <t>welfare</t>
+      <c r="A86" s="6" t="inlineStr">
+        <is>
+          <t>totalexpense</t>
         </is>
       </c>
       <c r="B86" s="4" t="inlineStr">
         <is>
-          <t>Welfare</t>
-        </is>
-      </c>
+          <t>Expense Total</t>
+        </is>
+      </c>
+      <c r="C86" s="5" t="n"/>
     </row>
     <row r="87">
-      <c r="A87" s="4" t="inlineStr">
-        <is>
-          <t>benefit</t>
-        </is>
-      </c>
-      <c r="B87" s="4" t="inlineStr">
-        <is>
-          <t>Welfare</t>
-        </is>
-      </c>
+      <c r="A87" s="3" t="inlineStr">
+        <is>
+          <t>── Facility Expense ──</t>
+        </is>
+      </c>
+      <c r="B87" s="4" t="n"/>
+      <c r="C87" s="5" t="n"/>
     </row>
     <row r="88">
-      <c r="A88" s="4" t="inlineStr">
-        <is>
-          <t>benefits</t>
+      <c r="A88" s="6" t="inlineStr">
+        <is>
+          <t>expense facility</t>
         </is>
       </c>
       <c r="B88" s="4" t="inlineStr">
         <is>
-          <t>Welfare</t>
-        </is>
-      </c>
+          <t>Facility Expense</t>
+        </is>
+      </c>
+      <c r="C88" s="5" t="n"/>
     </row>
     <row r="89">
       <c r="A89" s="4" t="inlineStr">
         <is>
-          <t>employee benefit</t>
+          <t>expensefacility</t>
         </is>
       </c>
       <c r="B89" s="4" t="inlineStr">
         <is>
-          <t>Welfare</t>
-        </is>
-      </c>
+          <t>Facility Expense</t>
+        </is>
+      </c>
+      <c r="C89" s="5" t="n"/>
     </row>
     <row r="90">
       <c r="A90" s="4" t="inlineStr">
         <is>
-          <t>staff benefit</t>
+          <t>facility expense</t>
         </is>
       </c>
       <c r="B90" s="4" t="inlineStr">
         <is>
-          <t>Welfare</t>
-        </is>
-      </c>
+          <t>Facility Expense</t>
+        </is>
+      </c>
+      <c r="C90" s="5" t="n"/>
     </row>
     <row r="91">
-      <c r="A91" s="4" t="inlineStr">
-        <is>
-          <t>employee welfare</t>
+      <c r="A91" s="6" t="inlineStr">
+        <is>
+          <t>facilityexpense</t>
         </is>
       </c>
       <c r="B91" s="4" t="inlineStr">
         <is>
-          <t>Welfare</t>
-        </is>
-      </c>
+          <t>Facility Expense</t>
+        </is>
+      </c>
+      <c r="C91" s="5" t="n"/>
     </row>
     <row r="92">
-      <c r="A92" s="4" t="inlineStr">
-        <is>
-          <t>staff welfare</t>
-        </is>
-      </c>
-      <c r="B92" s="4" t="inlineStr">
-        <is>
-          <t>Welfare</t>
-        </is>
-      </c>
+      <c r="A92" s="3" t="inlineStr">
+        <is>
+          <t>── Fixed Cost Efficiency ──</t>
+        </is>
+      </c>
+      <c r="B92" s="4" t="n"/>
+      <c r="C92" s="5" t="n"/>
     </row>
     <row r="93">
       <c r="A93" s="4" t="inlineStr">
         <is>
-          <t>fringe benefit</t>
+          <t>cost efficiency</t>
         </is>
       </c>
       <c r="B93" s="4" t="inlineStr">
         <is>
-          <t>Welfare</t>
-        </is>
-      </c>
+          <t>Fixed Cost Efficiency</t>
+        </is>
+      </c>
+      <c r="C93" s="5" t="n"/>
     </row>
     <row r="94">
       <c r="A94" s="4" t="inlineStr">
         <is>
-          <t>fringe</t>
+          <t>costefficiency</t>
         </is>
       </c>
       <c r="B94" s="4" t="inlineStr">
         <is>
-          <t>Welfare</t>
-        </is>
-      </c>
+          <t>Fixed Cost Efficiency</t>
+        </is>
+      </c>
+      <c r="C94" s="5" t="n"/>
     </row>
     <row r="95">
-      <c r="A95" s="4" t="inlineStr">
-        <is>
-          <t>สวัสดิการ</t>
+      <c r="A95" s="6" t="inlineStr">
+        <is>
+          <t>efficiency cost fixed</t>
         </is>
       </c>
       <c r="B95" s="4" t="inlineStr">
         <is>
-          <t>Welfare</t>
-        </is>
-      </c>
+          <t>Fixed Cost Efficiency</t>
+        </is>
+      </c>
+      <c r="C95" s="5" t="n"/>
     </row>
     <row r="96">
-      <c r="A96" s="3" t="inlineStr">
-        <is>
-          <t>── Provident Fund ──</t>
-        </is>
-      </c>
-      <c r="B96" s="3" t="inlineStr"/>
-      <c r="C96" s="3" t="inlineStr"/>
+      <c r="A96" s="6" t="inlineStr">
+        <is>
+          <t>efficiencycostfixed</t>
+        </is>
+      </c>
+      <c r="B96" s="6" t="inlineStr">
+        <is>
+          <t>Fixed Cost Efficiency</t>
+        </is>
+      </c>
+      <c r="C96" s="3" t="n"/>
     </row>
     <row r="97">
       <c r="A97" s="4" t="inlineStr">
         <is>
-          <t>provident</t>
+          <t>fixed cost efficiency</t>
         </is>
       </c>
       <c r="B97" s="4" t="inlineStr">
         <is>
-          <t>Provident Fund</t>
-        </is>
-      </c>
+          <t>Fixed Cost Efficiency</t>
+        </is>
+      </c>
+      <c r="C97" s="5" t="n"/>
     </row>
     <row r="98">
       <c r="A98" s="4" t="inlineStr">
         <is>
-          <t>provident fund</t>
+          <t>fixedcostefficiency</t>
         </is>
       </c>
       <c r="B98" s="4" t="inlineStr">
         <is>
-          <t>Provident Fund</t>
-        </is>
-      </c>
+          <t>Fixed Cost Efficiency</t>
+        </is>
+      </c>
+      <c r="C98" s="5" t="n"/>
     </row>
     <row r="99">
-      <c r="A99" s="4" t="inlineStr">
-        <is>
-          <t>pvd</t>
-        </is>
-      </c>
-      <c r="B99" s="4" t="inlineStr">
-        <is>
-          <t>Provident Fund</t>
-        </is>
-      </c>
+      <c r="A99" s="3" t="inlineStr">
+        <is>
+          <t>── Fixed Cost Ratio ──</t>
+        </is>
+      </c>
+      <c r="B99" s="4" t="n"/>
+      <c r="C99" s="5" t="n"/>
     </row>
     <row r="100">
-      <c r="A100" s="4" t="inlineStr">
-        <is>
-          <t>pension</t>
+      <c r="A100" s="6" t="inlineStr">
+        <is>
+          <t>cost ratio</t>
         </is>
       </c>
       <c r="B100" s="4" t="inlineStr">
         <is>
-          <t>Provident Fund</t>
-        </is>
-      </c>
+          <t>Fixed Cost Ratio</t>
+        </is>
+      </c>
+      <c r="C100" s="5" t="n"/>
     </row>
     <row r="101">
       <c r="A101" s="4" t="inlineStr">
         <is>
-          <t>retirement fund</t>
+          <t>costratio</t>
         </is>
       </c>
       <c r="B101" s="4" t="inlineStr">
         <is>
-          <t>Provident Fund</t>
-        </is>
-      </c>
+          <t>Fixed Cost Ratio</t>
+        </is>
+      </c>
+      <c r="C101" s="5" t="n"/>
     </row>
     <row r="102">
       <c r="A102" s="4" t="inlineStr">
         <is>
-          <t>employee fund</t>
+          <t>fixed cost</t>
         </is>
       </c>
       <c r="B102" s="4" t="inlineStr">
         <is>
-          <t>Provident Fund</t>
-        </is>
-      </c>
+          <t>Fixed Cost Ratio</t>
+        </is>
+      </c>
+      <c r="C102" s="5" t="n"/>
     </row>
     <row r="103">
       <c r="A103" s="4" t="inlineStr">
         <is>
-          <t>saving fund</t>
+          <t>fixed cost ratio</t>
         </is>
       </c>
       <c r="B103" s="4" t="inlineStr">
         <is>
-          <t>Provident Fund</t>
-        </is>
-      </c>
+          <t>Fixed Cost Ratio</t>
+        </is>
+      </c>
+      <c r="C103" s="5" t="n"/>
     </row>
     <row r="104">
       <c r="A104" s="4" t="inlineStr">
         <is>
-          <t>กองทุนสำรองเลี้ยงชีพ</t>
+          <t>fixedcost</t>
         </is>
       </c>
       <c r="B104" s="4" t="inlineStr">
         <is>
-          <t>Provident Fund</t>
-        </is>
-      </c>
+          <t>Fixed Cost Ratio</t>
+        </is>
+      </c>
+      <c r="C104" s="5" t="n"/>
     </row>
     <row r="105">
-      <c r="A105" s="3" t="inlineStr">
-        <is>
-          <t>── Workmen's compensation ──</t>
-        </is>
-      </c>
-      <c r="B105" s="3" t="inlineStr"/>
-      <c r="C105" s="3" t="inlineStr"/>
+      <c r="A105" s="6" t="inlineStr">
+        <is>
+          <t>fixedcostratio</t>
+        </is>
+      </c>
+      <c r="B105" s="6" t="inlineStr">
+        <is>
+          <t>Fixed Cost Ratio</t>
+        </is>
+      </c>
+      <c r="C105" s="3" t="n"/>
     </row>
     <row r="106">
-      <c r="A106" s="4" t="inlineStr">
-        <is>
-          <t>workmen</t>
+      <c r="A106" s="6" t="inlineStr">
+        <is>
+          <t>ratio cost fixed</t>
         </is>
       </c>
       <c r="B106" s="4" t="inlineStr">
         <is>
-          <t>Workmen's compensation</t>
-        </is>
-      </c>
+          <t>Fixed Cost Ratio</t>
+        </is>
+      </c>
+      <c r="C106" s="5" t="n"/>
     </row>
     <row r="107">
       <c r="A107" s="4" t="inlineStr">
         <is>
-          <t>workmen's compensation</t>
+          <t>ratiocostfixed</t>
         </is>
       </c>
       <c r="B107" s="4" t="inlineStr">
         <is>
-          <t>Workmen's compensation</t>
-        </is>
-      </c>
+          <t>Fixed Cost Ratio</t>
+        </is>
+      </c>
+      <c r="C107" s="5" t="n"/>
     </row>
     <row r="108">
-      <c r="A108" s="4" t="inlineStr">
-        <is>
-          <t>worker compensation</t>
-        </is>
-      </c>
-      <c r="B108" s="4" t="inlineStr">
-        <is>
-          <t>Workmen's compensation</t>
-        </is>
-      </c>
+      <c r="A108" s="3" t="inlineStr">
+        <is>
+          <t>── Fixed Cost Total ──</t>
+        </is>
+      </c>
+      <c r="B108" s="4" t="n"/>
+      <c r="C108" s="5" t="n"/>
     </row>
     <row r="109">
       <c r="A109" s="4" t="inlineStr">
         <is>
-          <t>work comp</t>
+          <t>fixed cost total</t>
         </is>
       </c>
       <c r="B109" s="4" t="inlineStr">
         <is>
-          <t>Workmen's compensation</t>
-        </is>
-      </c>
+          <t>Fixed Cost Total</t>
+        </is>
+      </c>
+      <c r="C109" s="5" t="n"/>
     </row>
     <row r="110">
       <c r="A110" s="4" t="inlineStr">
         <is>
-          <t>injury compensation</t>
+          <t>fixedcosttotal</t>
         </is>
       </c>
       <c r="B110" s="4" t="inlineStr">
         <is>
-          <t>Workmen's compensation</t>
-        </is>
-      </c>
+          <t>Fixed Cost Total</t>
+        </is>
+      </c>
+      <c r="C110" s="5" t="n"/>
     </row>
     <row r="111">
       <c r="A111" s="4" t="inlineStr">
         <is>
-          <t>work accident</t>
+          <t>total cost fixed</t>
         </is>
       </c>
       <c r="B111" s="4" t="inlineStr">
         <is>
-          <t>Workmen's compensation</t>
-        </is>
-      </c>
+          <t>Fixed Cost Total</t>
+        </is>
+      </c>
+      <c r="C111" s="5" t="n"/>
     </row>
     <row r="112">
-      <c r="A112" s="3" t="inlineStr">
-        <is>
-          <t>── Severance Pay / Retirement Fee ──</t>
-        </is>
-      </c>
-      <c r="B112" s="3" t="inlineStr"/>
-      <c r="C112" s="3" t="inlineStr"/>
+      <c r="A112" s="6" t="inlineStr">
+        <is>
+          <t>totalcostfixed</t>
+        </is>
+      </c>
+      <c r="B112" s="6" t="inlineStr">
+        <is>
+          <t>Fixed Cost Total</t>
+        </is>
+      </c>
+      <c r="C112" s="3" t="n"/>
     </row>
     <row r="113">
-      <c r="A113" s="4" t="inlineStr">
-        <is>
-          <t>severance</t>
-        </is>
-      </c>
-      <c r="B113" s="4" t="inlineStr">
-        <is>
-          <t>Severance Pay / Retirement Fee</t>
-        </is>
-      </c>
+      <c r="A113" s="3" t="inlineStr">
+        <is>
+          <t>── Gross Profit ──</t>
+        </is>
+      </c>
+      <c r="B113" s="4" t="n"/>
+      <c r="C113" s="5" t="n"/>
     </row>
     <row r="114">
       <c r="A114" s="4" t="inlineStr">
         <is>
-          <t>retirement</t>
+          <t>gross profit</t>
         </is>
       </c>
       <c r="B114" s="4" t="inlineStr">
         <is>
-          <t>Severance Pay / Retirement Fee</t>
-        </is>
-      </c>
+          <t>Gross Profit</t>
+        </is>
+      </c>
+      <c r="C114" s="5" t="n"/>
     </row>
     <row r="115">
-      <c r="A115" s="4" t="inlineStr">
-        <is>
-          <t>severance pay</t>
+      <c r="A115" s="6" t="inlineStr">
+        <is>
+          <t>grossprofit</t>
         </is>
       </c>
       <c r="B115" s="4" t="inlineStr">
         <is>
-          <t>Severance Pay / Retirement Fee</t>
-        </is>
-      </c>
+          <t>Gross Profit</t>
+        </is>
+      </c>
+      <c r="C115" s="5" t="n"/>
     </row>
     <row r="116">
       <c r="A116" s="4" t="inlineStr">
         <is>
-          <t>retirement fee</t>
+          <t>profit gross</t>
         </is>
       </c>
       <c r="B116" s="4" t="inlineStr">
         <is>
-          <t>Severance Pay / Retirement Fee</t>
-        </is>
-      </c>
+          <t>Gross Profit</t>
+        </is>
+      </c>
+      <c r="C116" s="5" t="n"/>
     </row>
     <row r="117">
       <c r="A117" s="4" t="inlineStr">
         <is>
-          <t>termination pay</t>
+          <t>profitgross</t>
         </is>
       </c>
       <c r="B117" s="4" t="inlineStr">
         <is>
-          <t>Severance Pay / Retirement Fee</t>
-        </is>
-      </c>
+          <t>Gross Profit</t>
+        </is>
+      </c>
+      <c r="C117" s="5" t="n"/>
     </row>
     <row r="118">
-      <c r="A118" s="4" t="inlineStr">
-        <is>
-          <t>separation pay</t>
-        </is>
-      </c>
-      <c r="B118" s="4" t="inlineStr">
-        <is>
-          <t>Severance Pay / Retirement Fee</t>
-        </is>
-      </c>
+      <c r="A118" s="3" t="inlineStr">
+        <is>
+          <t>── Gross Profit Ratio ──</t>
+        </is>
+      </c>
+      <c r="B118" s="4" t="n"/>
+      <c r="C118" s="5" t="n"/>
     </row>
     <row r="119">
       <c r="A119" s="4" t="inlineStr">
         <is>
-          <t>redundancy</t>
+          <t>gross profit ratio</t>
         </is>
       </c>
       <c r="B119" s="4" t="inlineStr">
         <is>
-          <t>Severance Pay / Retirement Fee</t>
-        </is>
-      </c>
+          <t>Gross Profit Ratio</t>
+        </is>
+      </c>
+      <c r="C119" s="5" t="n"/>
     </row>
     <row r="120">
       <c r="A120" s="4" t="inlineStr">
         <is>
-          <t>ค่าชดเชย</t>
+          <t>grossprofitratio</t>
         </is>
       </c>
       <c r="B120" s="4" t="inlineStr">
         <is>
-          <t>Severance Pay / Retirement Fee</t>
-        </is>
-      </c>
+          <t>Gross Profit Ratio</t>
+        </is>
+      </c>
+      <c r="C120" s="5" t="n"/>
     </row>
     <row r="121">
-      <c r="A121" s="3" t="inlineStr">
-        <is>
-          <t>── Allowance ──</t>
-        </is>
-      </c>
-      <c r="B121" s="3" t="inlineStr"/>
-      <c r="C121" s="3" t="inlineStr"/>
+      <c r="A121" s="6" t="inlineStr">
+        <is>
+          <t>profit ratio</t>
+        </is>
+      </c>
+      <c r="B121" s="6" t="inlineStr">
+        <is>
+          <t>Gross Profit Ratio</t>
+        </is>
+      </c>
+      <c r="C121" s="3" t="n"/>
     </row>
     <row r="122">
       <c r="A122" s="4" t="inlineStr">
         <is>
-          <t>allowance</t>
+          <t>profitratio</t>
         </is>
       </c>
       <c r="B122" s="4" t="inlineStr">
         <is>
-          <t>Allowance</t>
-        </is>
-      </c>
+          <t>Gross Profit Ratio</t>
+        </is>
+      </c>
+      <c r="C122" s="5" t="n"/>
     </row>
     <row r="123">
       <c r="A123" s="4" t="inlineStr">
         <is>
-          <t>allowances</t>
+          <t>ratio profit gross</t>
         </is>
       </c>
       <c r="B123" s="4" t="inlineStr">
         <is>
-          <t>Allowance</t>
-        </is>
-      </c>
+          <t>Gross Profit Ratio</t>
+        </is>
+      </c>
+      <c r="C123" s="5" t="n"/>
     </row>
     <row r="124">
       <c r="A124" s="4" t="inlineStr">
         <is>
-          <t>daily allowance</t>
+          <t>ratioprofitgross</t>
         </is>
       </c>
       <c r="B124" s="4" t="inlineStr">
         <is>
-          <t>Allowance</t>
-        </is>
-      </c>
+          <t>Gross Profit Ratio</t>
+        </is>
+      </c>
+      <c r="C124" s="5" t="n"/>
     </row>
     <row r="125">
-      <c r="A125" s="4" t="inlineStr">
-        <is>
-          <t>meal allowance</t>
-        </is>
-      </c>
-      <c r="B125" s="4" t="inlineStr">
-        <is>
-          <t>Allowance</t>
-        </is>
-      </c>
+      <c r="A125" s="3" t="inlineStr">
+        <is>
+          <t>── Insurance ──</t>
+        </is>
+      </c>
+      <c r="B125" s="4" t="n"/>
+      <c r="C125" s="5" t="n"/>
     </row>
     <row r="126">
       <c r="A126" s="4" t="inlineStr">
         <is>
-          <t>housing allowance</t>
+          <t>insurance</t>
         </is>
       </c>
       <c r="B126" s="4" t="inlineStr">
         <is>
-          <t>Allowance</t>
-        </is>
-      </c>
+          <t>Insurance</t>
+        </is>
+      </c>
+      <c r="C126" s="5" t="n"/>
     </row>
     <row r="127">
-      <c r="A127" s="4" t="inlineStr">
-        <is>
-          <t>travel allowance</t>
-        </is>
-      </c>
-      <c r="B127" s="4" t="inlineStr">
-        <is>
-          <t>Allowance</t>
-        </is>
-      </c>
+      <c r="A127" s="3" t="inlineStr">
+        <is>
+          <t>── Land &amp; Building TAX ──</t>
+        </is>
+      </c>
+      <c r="B127" s="4" t="n"/>
+      <c r="C127" s="5" t="n"/>
     </row>
     <row r="128">
       <c r="A128" s="4" t="inlineStr">
         <is>
-          <t>position allowance</t>
+          <t>building tax</t>
         </is>
       </c>
       <c r="B128" s="4" t="inlineStr">
         <is>
-          <t>Allowance</t>
-        </is>
-      </c>
+          <t>Land &amp; Building TAX</t>
+        </is>
+      </c>
+      <c r="C128" s="5" t="n"/>
     </row>
     <row r="129">
-      <c r="A129" s="4" t="inlineStr">
-        <is>
-          <t>เบี้ยเลี้ยง</t>
+      <c r="A129" s="6" t="inlineStr">
+        <is>
+          <t>buildingtax</t>
         </is>
       </c>
       <c r="B129" s="4" t="inlineStr">
         <is>
-          <t>Allowance</t>
-        </is>
-      </c>
+          <t>Land &amp; Building TAX</t>
+        </is>
+      </c>
+      <c r="C129" s="5" t="n"/>
     </row>
     <row r="130">
-      <c r="A130" s="3" t="inlineStr">
-        <is>
-          <t>── Consumable Supply ──</t>
-        </is>
-      </c>
-      <c r="B130" s="3" t="inlineStr"/>
-      <c r="C130" s="3" t="inlineStr"/>
+      <c r="A130" s="6" t="inlineStr">
+        <is>
+          <t>land &amp; building tax</t>
+        </is>
+      </c>
+      <c r="B130" s="6" t="inlineStr">
+        <is>
+          <t>Land &amp; Building TAX</t>
+        </is>
+      </c>
+      <c r="C130" s="3" t="n"/>
     </row>
     <row r="131">
       <c r="A131" s="4" t="inlineStr">
         <is>
-          <t>consumable</t>
+          <t>land building</t>
         </is>
       </c>
       <c r="B131" s="4" t="inlineStr">
         <is>
-          <t>Consumable Supply</t>
-        </is>
-      </c>
+          <t>Land &amp; Building TAX</t>
+        </is>
+      </c>
+      <c r="C131" s="5" t="n"/>
     </row>
     <row r="132">
       <c r="A132" s="4" t="inlineStr">
         <is>
-          <t>consumable supply</t>
+          <t>land building tax</t>
         </is>
       </c>
       <c r="B132" s="4" t="inlineStr">
         <is>
-          <t>Consumable Supply</t>
-        </is>
-      </c>
+          <t>Land &amp; Building TAX</t>
+        </is>
+      </c>
+      <c r="C132" s="5" t="n"/>
     </row>
     <row r="133">
       <c r="A133" s="4" t="inlineStr">
         <is>
-          <t>consumables</t>
+          <t>landbuilding</t>
         </is>
       </c>
       <c r="B133" s="4" t="inlineStr">
         <is>
-          <t>Consumable Supply</t>
-        </is>
-      </c>
+          <t>Land &amp; Building TAX</t>
+        </is>
+      </c>
+      <c r="C133" s="5" t="n"/>
     </row>
     <row r="134">
       <c r="A134" s="4" t="inlineStr">
         <is>
-          <t>warehouse supply</t>
+          <t>landbuildingtax</t>
         </is>
       </c>
       <c r="B134" s="4" t="inlineStr">
         <is>
-          <t>Consumable Supply</t>
-        </is>
-      </c>
+          <t>Land &amp; Building TAX</t>
+        </is>
+      </c>
+      <c r="C134" s="5" t="n"/>
     </row>
     <row r="135">
-      <c r="A135" s="4" t="inlineStr">
-        <is>
-          <t>wh supply</t>
+      <c r="A135" s="6" t="inlineStr">
+        <is>
+          <t>tax building land</t>
         </is>
       </c>
       <c r="B135" s="4" t="inlineStr">
         <is>
-          <t>Consumable Supply</t>
-        </is>
-      </c>
+          <t>Land &amp; Building TAX</t>
+        </is>
+      </c>
+      <c r="C135" s="5" t="n"/>
     </row>
     <row r="136">
       <c r="A136" s="4" t="inlineStr">
         <is>
-          <t>supplies</t>
+          <t>taxbuildingland</t>
         </is>
       </c>
       <c r="B136" s="4" t="inlineStr">
         <is>
-          <t>Consumable Supply</t>
-        </is>
-      </c>
+          <t>Land &amp; Building TAX</t>
+        </is>
+      </c>
+      <c r="C136" s="5" t="n"/>
     </row>
     <row r="137">
-      <c r="A137" s="4" t="inlineStr">
-        <is>
-          <t>packaging</t>
-        </is>
-      </c>
-      <c r="B137" s="4" t="inlineStr">
-        <is>
-          <t>Consumable Supply</t>
-        </is>
-      </c>
+      <c r="A137" s="3" t="inlineStr">
+        <is>
+          <t>── Land Rental ──</t>
+        </is>
+      </c>
+      <c r="B137" s="4" t="n"/>
+      <c r="C137" s="5" t="n"/>
     </row>
     <row r="138">
-      <c r="A138" s="4" t="inlineStr">
-        <is>
-          <t>packing material</t>
+      <c r="A138" s="6" t="inlineStr">
+        <is>
+          <t>land rental</t>
         </is>
       </c>
       <c r="B138" s="4" t="inlineStr">
         <is>
-          <t>Consumable Supply</t>
-        </is>
-      </c>
+          <t>Land Rental</t>
+        </is>
+      </c>
+      <c r="C138" s="5" t="n"/>
     </row>
     <row r="139">
-      <c r="A139" s="3" t="inlineStr">
-        <is>
-          <t>── Outsource Labor Fee ──</t>
-        </is>
-      </c>
-      <c r="B139" s="3" t="inlineStr"/>
-      <c r="C139" s="3" t="inlineStr"/>
+      <c r="A139" s="6" t="inlineStr">
+        <is>
+          <t>landrental</t>
+        </is>
+      </c>
+      <c r="B139" s="6" t="inlineStr">
+        <is>
+          <t>Land Rental</t>
+        </is>
+      </c>
+      <c r="C139" s="3" t="n"/>
     </row>
     <row r="140">
       <c r="A140" s="4" t="inlineStr">
         <is>
-          <t>outsource</t>
+          <t>rental land</t>
         </is>
       </c>
       <c r="B140" s="4" t="inlineStr">
         <is>
-          <t>Outsource Labor Fee</t>
-        </is>
-      </c>
+          <t>Land Rental</t>
+        </is>
+      </c>
+      <c r="C140" s="5" t="n"/>
     </row>
     <row r="141">
       <c r="A141" s="4" t="inlineStr">
         <is>
-          <t>outsource labor</t>
+          <t>rentalland</t>
         </is>
       </c>
       <c r="B141" s="4" t="inlineStr">
         <is>
-          <t>Outsource Labor Fee</t>
-        </is>
-      </c>
+          <t>Land Rental</t>
+        </is>
+      </c>
+      <c r="C141" s="5" t="n"/>
     </row>
     <row r="142">
-      <c r="A142" s="4" t="inlineStr">
-        <is>
-          <t>labor fee</t>
-        </is>
-      </c>
-      <c r="B142" s="4" t="inlineStr">
-        <is>
-          <t>Outsource Labor Fee</t>
-        </is>
-      </c>
+      <c r="A142" s="3" t="inlineStr">
+        <is>
+          <t>── Lease Circuit ──</t>
+        </is>
+      </c>
+      <c r="B142" s="4" t="n"/>
+      <c r="C142" s="5" t="n"/>
     </row>
     <row r="143">
-      <c r="A143" s="4" t="inlineStr">
-        <is>
-          <t>outsource labor fee</t>
+      <c r="A143" s="6" t="inlineStr">
+        <is>
+          <t>circuit lease</t>
         </is>
       </c>
       <c r="B143" s="4" t="inlineStr">
         <is>
-          <t>Outsource Labor Fee</t>
-        </is>
-      </c>
+          <t>Lease Circuit</t>
+        </is>
+      </c>
+      <c r="C143" s="5" t="n"/>
     </row>
     <row r="144">
-      <c r="A144" s="4" t="inlineStr">
-        <is>
-          <t>outsourced</t>
+      <c r="A144" s="6" t="inlineStr">
+        <is>
+          <t>circuitlease</t>
         </is>
       </c>
       <c r="B144" s="4" t="inlineStr">
         <is>
-          <t>Outsource Labor Fee</t>
-        </is>
-      </c>
+          <t>Lease Circuit</t>
+        </is>
+      </c>
+      <c r="C144" s="5" t="n"/>
     </row>
     <row r="145">
       <c r="A145" s="4" t="inlineStr">
         <is>
-          <t>outsourcing</t>
+          <t>lease circuit</t>
         </is>
       </c>
       <c r="B145" s="4" t="inlineStr">
         <is>
-          <t>Outsource Labor Fee</t>
-        </is>
-      </c>
+          <t>Lease Circuit</t>
+        </is>
+      </c>
+      <c r="C145" s="5" t="n"/>
     </row>
     <row r="146">
       <c r="A146" s="4" t="inlineStr">
         <is>
-          <t>contract labor</t>
+          <t>leasecircuit</t>
         </is>
       </c>
       <c r="B146" s="4" t="inlineStr">
         <is>
-          <t>Outsource Labor Fee</t>
-        </is>
-      </c>
+          <t>Lease Circuit</t>
+        </is>
+      </c>
+      <c r="C146" s="5" t="n"/>
     </row>
     <row r="147">
-      <c r="A147" s="4" t="inlineStr">
-        <is>
-          <t>temp labor</t>
-        </is>
-      </c>
-      <c r="B147" s="4" t="inlineStr">
-        <is>
-          <t>Outsource Labor Fee</t>
-        </is>
-      </c>
+      <c r="A147" s="3" t="inlineStr">
+        <is>
+          <t>── Marginal Profit ──</t>
+        </is>
+      </c>
+      <c r="B147" s="4" t="n"/>
+      <c r="C147" s="5" t="n"/>
     </row>
     <row r="148">
       <c r="A148" s="4" t="inlineStr">
         <is>
-          <t>temporary staff</t>
+          <t>marginal profit</t>
         </is>
       </c>
       <c r="B148" s="4" t="inlineStr">
         <is>
-          <t>Outsource Labor Fee</t>
-        </is>
-      </c>
+          <t>Marginal Profit</t>
+        </is>
+      </c>
+      <c r="C148" s="5" t="n"/>
     </row>
     <row r="149">
-      <c r="A149" s="4" t="inlineStr">
-        <is>
-          <t>temp staff</t>
+      <c r="A149" s="6" t="inlineStr">
+        <is>
+          <t>marginalprofit</t>
         </is>
       </c>
       <c r="B149" s="4" t="inlineStr">
         <is>
-          <t>Outsource Labor Fee</t>
-        </is>
-      </c>
+          <t>Marginal Profit</t>
+        </is>
+      </c>
+      <c r="C149" s="5" t="n"/>
     </row>
     <row r="150">
       <c r="A150" s="4" t="inlineStr">
         <is>
-          <t>agency fee</t>
+          <t>profit marginal</t>
         </is>
       </c>
       <c r="B150" s="4" t="inlineStr">
         <is>
-          <t>Outsource Labor Fee</t>
-        </is>
-      </c>
+          <t>Marginal Profit</t>
+        </is>
+      </c>
+      <c r="C150" s="5" t="n"/>
     </row>
     <row r="151">
       <c r="A151" s="4" t="inlineStr">
         <is>
-          <t>manpower</t>
+          <t>profitmarginal</t>
         </is>
       </c>
       <c r="B151" s="4" t="inlineStr">
         <is>
-          <t>Outsource Labor Fee</t>
-        </is>
-      </c>
+          <t>Marginal Profit</t>
+        </is>
+      </c>
+      <c r="C151" s="5" t="n"/>
     </row>
     <row r="152">
       <c r="A152" s="3" t="inlineStr">
         <is>
-          <t>── Cost (Adjust) ──</t>
-        </is>
-      </c>
-      <c r="B152" s="3" t="inlineStr"/>
-      <c r="C152" s="3" t="inlineStr"/>
+          <t>── Marginal Profit Ratio ──</t>
+        </is>
+      </c>
+      <c r="B152" s="6" t="n"/>
+      <c r="C152" s="3" t="n"/>
     </row>
     <row r="153">
       <c r="A153" s="4" t="inlineStr">
         <is>
-          <t>cost adjust</t>
+          <t>marginal profit ratio</t>
         </is>
       </c>
       <c r="B153" s="4" t="inlineStr">
         <is>
-          <t>Cost (Adjust)</t>
-        </is>
-      </c>
+          <t>Marginal Profit Ratio</t>
+        </is>
+      </c>
+      <c r="C153" s="5" t="n"/>
     </row>
     <row r="154">
-      <c r="A154" s="4" t="inlineStr">
-        <is>
-          <t>adjustment</t>
+      <c r="A154" s="6" t="inlineStr">
+        <is>
+          <t>marginalprofitratio</t>
         </is>
       </c>
       <c r="B154" s="4" t="inlineStr">
         <is>
-          <t>Cost (Adjust)</t>
-        </is>
-      </c>
+          <t>Marginal Profit Ratio</t>
+        </is>
+      </c>
+      <c r="C154" s="5" t="n"/>
     </row>
     <row r="155">
       <c r="A155" s="4" t="inlineStr">
         <is>
-          <t>cost adjustment</t>
+          <t>ratio profit marginal</t>
         </is>
       </c>
       <c r="B155" s="4" t="inlineStr">
         <is>
-          <t>Cost (Adjust)</t>
-        </is>
-      </c>
+          <t>Marginal Profit Ratio</t>
+        </is>
+      </c>
+      <c r="C155" s="5" t="n"/>
     </row>
     <row r="156">
       <c r="A156" s="4" t="inlineStr">
         <is>
-          <t>adjust</t>
+          <t>ratioprofitmarginal</t>
         </is>
       </c>
       <c r="B156" s="4" t="inlineStr">
         <is>
-          <t>Cost (Adjust)</t>
-        </is>
-      </c>
+          <t>Marginal Profit Ratio</t>
+        </is>
+      </c>
+      <c r="C156" s="5" t="n"/>
     </row>
     <row r="157">
       <c r="A157" s="3" t="inlineStr">
         <is>
-          <t>── Cost Total ──</t>
-        </is>
-      </c>
-      <c r="B157" s="3" t="inlineStr"/>
-      <c r="C157" s="3" t="inlineStr"/>
+          <t>── Material and Service ──</t>
+        </is>
+      </c>
+      <c r="B157" s="6" t="n"/>
+      <c r="C157" s="3" t="n"/>
     </row>
     <row r="158">
       <c r="A158" s="4" t="inlineStr">
         <is>
-          <t>cost total</t>
+          <t>and service</t>
         </is>
       </c>
       <c r="B158" s="4" t="inlineStr">
         <is>
-          <t>Cost Total</t>
-        </is>
-      </c>
+          <t>Material and Service</t>
+        </is>
+      </c>
+      <c r="C158" s="5" t="n"/>
     </row>
     <row r="159">
       <c r="A159" s="4" t="inlineStr">
         <is>
-          <t>total cost</t>
+          <t>andservice</t>
         </is>
       </c>
       <c r="B159" s="4" t="inlineStr">
         <is>
-          <t>Cost Total</t>
-        </is>
-      </c>
+          <t>Material and Service</t>
+        </is>
+      </c>
+      <c r="C159" s="5" t="n"/>
     </row>
     <row r="160">
       <c r="A160" s="4" t="inlineStr">
         <is>
-          <t>all cost</t>
+          <t>material and</t>
         </is>
       </c>
       <c r="B160" s="4" t="inlineStr">
         <is>
-          <t>Cost Total</t>
-        </is>
-      </c>
+          <t>Material and Service</t>
+        </is>
+      </c>
+      <c r="C160" s="5" t="n"/>
     </row>
     <row r="161">
       <c r="A161" s="4" t="inlineStr">
         <is>
-          <t>cost sum</t>
+          <t>material and service</t>
         </is>
       </c>
       <c r="B161" s="4" t="inlineStr">
         <is>
-          <t>Cost Total</t>
-        </is>
-      </c>
+          <t>Material and Service</t>
+        </is>
+      </c>
+      <c r="C161" s="5" t="n"/>
     </row>
     <row r="162">
-      <c r="A162" s="3" t="inlineStr">
-        <is>
-          <t>── Variable Cost Total ──</t>
-        </is>
-      </c>
-      <c r="B162" s="3" t="inlineStr"/>
-      <c r="C162" s="3" t="inlineStr"/>
+      <c r="A162" s="6" t="inlineStr">
+        <is>
+          <t>materialand</t>
+        </is>
+      </c>
+      <c r="B162" s="6" t="inlineStr">
+        <is>
+          <t>Material and Service</t>
+        </is>
+      </c>
+      <c r="C162" s="3" t="n"/>
     </row>
     <row r="163">
-      <c r="A163" s="4" t="inlineStr">
-        <is>
-          <t>variable cost total</t>
+      <c r="A163" s="6" t="inlineStr">
+        <is>
+          <t>materialandservice</t>
         </is>
       </c>
       <c r="B163" s="4" t="inlineStr">
         <is>
-          <t>Variable Cost Total</t>
-        </is>
-      </c>
+          <t>Material and Service</t>
+        </is>
+      </c>
+      <c r="C163" s="5" t="n"/>
     </row>
     <row r="164">
       <c r="A164" s="4" t="inlineStr">
         <is>
-          <t>variable total</t>
+          <t>service and material</t>
         </is>
       </c>
       <c r="B164" s="4" t="inlineStr">
         <is>
-          <t>Variable Cost Total</t>
-        </is>
-      </c>
+          <t>Material and Service</t>
+        </is>
+      </c>
+      <c r="C164" s="5" t="n"/>
     </row>
     <row r="165">
       <c r="A165" s="4" t="inlineStr">
         <is>
-          <t>total variable cost</t>
+          <t>serviceandmaterial</t>
         </is>
       </c>
       <c r="B165" s="4" t="inlineStr">
         <is>
-          <t>Variable Cost Total</t>
-        </is>
-      </c>
+          <t>Material and Service</t>
+        </is>
+      </c>
+      <c r="C165" s="5" t="n"/>
     </row>
     <row r="166">
-      <c r="A166" s="4" t="inlineStr">
-        <is>
-          <t>total variable</t>
-        </is>
-      </c>
-      <c r="B166" s="4" t="inlineStr">
-        <is>
-          <t>Variable Cost Total</t>
-        </is>
-      </c>
+      <c r="A166" s="3" t="inlineStr">
+        <is>
+          <t>── Mobile Phone ──</t>
+        </is>
+      </c>
+      <c r="B166" s="4" t="n"/>
+      <c r="C166" s="5" t="n"/>
     </row>
     <row r="167">
       <c r="A167" s="4" t="inlineStr">
         <is>
-          <t>variable cost sum</t>
+          <t>mobile phone</t>
         </is>
       </c>
       <c r="B167" s="4" t="inlineStr">
         <is>
-          <t>Variable Cost Total</t>
-        </is>
-      </c>
+          <t>Mobile Phone</t>
+        </is>
+      </c>
+      <c r="C167" s="5" t="n"/>
     </row>
     <row r="168">
-      <c r="A168" s="3" t="inlineStr">
-        <is>
-          <t>── Fixed Cost Total ──</t>
-        </is>
-      </c>
-      <c r="B168" s="3" t="inlineStr"/>
-      <c r="C168" s="3" t="inlineStr"/>
+      <c r="A168" s="6" t="inlineStr">
+        <is>
+          <t>mobilephone</t>
+        </is>
+      </c>
+      <c r="B168" s="6" t="inlineStr">
+        <is>
+          <t>Mobile Phone</t>
+        </is>
+      </c>
+      <c r="C168" s="3" t="n"/>
     </row>
     <row r="169">
       <c r="A169" s="4" t="inlineStr">
         <is>
-          <t>fixed cost total</t>
+          <t>phone mobile</t>
         </is>
       </c>
       <c r="B169" s="4" t="inlineStr">
         <is>
-          <t>Fixed Cost Total</t>
-        </is>
-      </c>
+          <t>Mobile Phone</t>
+        </is>
+      </c>
+      <c r="C169" s="5" t="n"/>
     </row>
     <row r="170">
       <c r="A170" s="4" t="inlineStr">
         <is>
-          <t>fixed total</t>
+          <t>phonemobile</t>
         </is>
       </c>
       <c r="B170" s="4" t="inlineStr">
         <is>
-          <t>Fixed Cost Total</t>
-        </is>
-      </c>
+          <t>Mobile Phone</t>
+        </is>
+      </c>
+      <c r="C170" s="5" t="n"/>
     </row>
     <row r="171">
-      <c r="A171" s="4" t="inlineStr">
-        <is>
-          <t>total fixed cost</t>
-        </is>
-      </c>
-      <c r="B171" s="4" t="inlineStr">
-        <is>
-          <t>Fixed Cost Total</t>
-        </is>
-      </c>
+      <c r="A171" s="3" t="inlineStr">
+        <is>
+          <t>── Number of staff ──</t>
+        </is>
+      </c>
+      <c r="B171" s="4" t="n"/>
+      <c r="C171" s="5" t="n"/>
     </row>
     <row r="172">
-      <c r="A172" s="4" t="inlineStr">
-        <is>
-          <t>total fixed</t>
+      <c r="A172" s="6" t="inlineStr">
+        <is>
+          <t>number of</t>
         </is>
       </c>
       <c r="B172" s="4" t="inlineStr">
         <is>
-          <t>Fixed Cost Total</t>
-        </is>
-      </c>
+          <t>Number of staff</t>
+        </is>
+      </c>
+      <c r="C172" s="5" t="n"/>
     </row>
     <row r="173">
       <c r="A173" s="4" t="inlineStr">
         <is>
-          <t>fixed cost sum</t>
+          <t>number of staff</t>
         </is>
       </c>
       <c r="B173" s="4" t="inlineStr">
         <is>
-          <t>Fixed Cost Total</t>
-        </is>
-      </c>
+          <t>Number of staff</t>
+        </is>
+      </c>
+      <c r="C173" s="5" t="n"/>
     </row>
     <row r="174">
-      <c r="A174" s="3" t="inlineStr">
-        <is>
-          <t>── Land Rental ──</t>
-        </is>
-      </c>
-      <c r="B174" s="3" t="inlineStr"/>
-      <c r="C174" s="3" t="inlineStr"/>
+      <c r="A174" s="6" t="inlineStr">
+        <is>
+          <t>numberof</t>
+        </is>
+      </c>
+      <c r="B174" s="6" t="inlineStr">
+        <is>
+          <t>Number of staff</t>
+        </is>
+      </c>
+      <c r="C174" s="3" t="n"/>
     </row>
     <row r="175">
       <c r="A175" s="4" t="inlineStr">
         <is>
-          <t>land rental</t>
+          <t>numberofstaff</t>
         </is>
       </c>
       <c r="B175" s="4" t="inlineStr">
         <is>
-          <t>Land Rental</t>
-        </is>
-      </c>
+          <t>Number of staff</t>
+        </is>
+      </c>
+      <c r="C175" s="5" t="n"/>
     </row>
     <row r="176">
-      <c r="A176" s="4" t="inlineStr">
-        <is>
-          <t>land rent</t>
+      <c r="A176" s="6" t="inlineStr">
+        <is>
+          <t>of staff</t>
         </is>
       </c>
       <c r="B176" s="4" t="inlineStr">
         <is>
-          <t>Land Rental</t>
-        </is>
-      </c>
+          <t>Number of staff</t>
+        </is>
+      </c>
+      <c r="C176" s="5" t="n"/>
     </row>
     <row r="177">
-      <c r="A177" s="4" t="inlineStr">
-        <is>
-          <t>land lease</t>
+      <c r="A177" s="6" t="inlineStr">
+        <is>
+          <t>ofstaff</t>
         </is>
       </c>
       <c r="B177" s="4" t="inlineStr">
         <is>
-          <t>Land Rental</t>
-        </is>
-      </c>
+          <t>Number of staff</t>
+        </is>
+      </c>
+      <c r="C177" s="5" t="n"/>
     </row>
     <row r="178">
       <c r="A178" s="4" t="inlineStr">
         <is>
-          <t>ค่าเช่าที่ดิน</t>
+          <t>staff of number</t>
         </is>
       </c>
       <c r="B178" s="4" t="inlineStr">
         <is>
-          <t>Land Rental</t>
-        </is>
-      </c>
+          <t>Number of staff</t>
+        </is>
+      </c>
+      <c r="C178" s="5" t="n"/>
     </row>
     <row r="179">
-      <c r="A179" s="3" t="inlineStr">
-        <is>
-          <t>── Rental Other ──</t>
-        </is>
-      </c>
-      <c r="B179" s="3" t="inlineStr"/>
-      <c r="C179" s="3" t="inlineStr"/>
+      <c r="A179" s="6" t="inlineStr">
+        <is>
+          <t>staffofnumber</t>
+        </is>
+      </c>
+      <c r="B179" s="6" t="inlineStr">
+        <is>
+          <t>Number of staff</t>
+        </is>
+      </c>
+      <c r="C179" s="3" t="n"/>
     </row>
     <row r="180">
-      <c r="A180" s="4" t="inlineStr">
-        <is>
-          <t>rental other</t>
-        </is>
-      </c>
-      <c r="B180" s="4" t="inlineStr">
-        <is>
-          <t>Rental Other</t>
-        </is>
-      </c>
+      <c r="A180" s="3" t="inlineStr">
+        <is>
+          <t>── Office Equipment ──</t>
+        </is>
+      </c>
+      <c r="B180" s="4" t="n"/>
+      <c r="C180" s="5" t="n"/>
     </row>
     <row r="181">
       <c r="A181" s="4" t="inlineStr">
         <is>
-          <t>other rental</t>
+          <t>equipment office</t>
         </is>
       </c>
       <c r="B181" s="4" t="inlineStr">
         <is>
-          <t>Rental Other</t>
-        </is>
-      </c>
+          <t>Office Equipment</t>
+        </is>
+      </c>
+      <c r="C181" s="5" t="n"/>
     </row>
     <row r="182">
       <c r="A182" s="4" t="inlineStr">
         <is>
-          <t>misc rental</t>
+          <t>equipmentoffice</t>
         </is>
       </c>
       <c r="B182" s="4" t="inlineStr">
         <is>
-          <t>Rental Other</t>
-        </is>
-      </c>
+          <t>Office Equipment</t>
+        </is>
+      </c>
+      <c r="C182" s="5" t="n"/>
     </row>
     <row r="183">
-      <c r="A183" s="3" t="inlineStr">
-        <is>
-          <t>── Rental Equipments ──</t>
-        </is>
-      </c>
-      <c r="B183" s="3" t="inlineStr"/>
-      <c r="C183" s="3" t="inlineStr"/>
+      <c r="A183" s="6" t="inlineStr">
+        <is>
+          <t>office equipment</t>
+        </is>
+      </c>
+      <c r="B183" s="6" t="inlineStr">
+        <is>
+          <t>Office Equipment</t>
+        </is>
+      </c>
+      <c r="C183" s="3" t="n"/>
     </row>
     <row r="184">
-      <c r="A184" s="4" t="inlineStr">
-        <is>
-          <t>rental equipment</t>
+      <c r="A184" s="6" t="inlineStr">
+        <is>
+          <t>officeequipment</t>
         </is>
       </c>
       <c r="B184" s="4" t="inlineStr">
         <is>
-          <t>Rental Equipments</t>
-        </is>
-      </c>
+          <t>Office Equipment</t>
+        </is>
+      </c>
+      <c r="C184" s="5" t="n"/>
     </row>
     <row r="185">
-      <c r="A185" s="4" t="inlineStr">
-        <is>
-          <t>equipment rental</t>
-        </is>
-      </c>
-      <c r="B185" s="4" t="inlineStr">
-        <is>
-          <t>Rental Equipments</t>
-        </is>
-      </c>
+      <c r="A185" s="3" t="inlineStr">
+        <is>
+          <t>── Office Supply ──</t>
+        </is>
+      </c>
+      <c r="B185" s="4" t="n"/>
+      <c r="C185" s="5" t="n"/>
     </row>
     <row r="186">
-      <c r="A186" s="4" t="inlineStr">
-        <is>
-          <t>rental equipments</t>
+      <c r="A186" s="6" t="inlineStr">
+        <is>
+          <t>office supply</t>
         </is>
       </c>
       <c r="B186" s="4" t="inlineStr">
         <is>
-          <t>Rental Equipments</t>
-        </is>
-      </c>
+          <t>Office Supply</t>
+        </is>
+      </c>
+      <c r="C186" s="5" t="n"/>
     </row>
     <row r="187">
       <c r="A187" s="4" t="inlineStr">
         <is>
-          <t>machine rental</t>
+          <t>officesupply</t>
         </is>
       </c>
       <c r="B187" s="4" t="inlineStr">
         <is>
-          <t>Rental Equipments</t>
-        </is>
-      </c>
+          <t>Office Supply</t>
+        </is>
+      </c>
+      <c r="C187" s="5" t="n"/>
     </row>
     <row r="188">
       <c r="A188" s="4" t="inlineStr">
         <is>
-          <t>machinery rental</t>
+          <t>supply office</t>
         </is>
       </c>
       <c r="B188" s="4" t="inlineStr">
         <is>
-          <t>Rental Equipments</t>
-        </is>
-      </c>
+          <t>Office Supply</t>
+        </is>
+      </c>
+      <c r="C188" s="5" t="n"/>
     </row>
     <row r="189">
       <c r="A189" s="4" t="inlineStr">
         <is>
-          <t>forklift rental</t>
+          <t>supplyoffice</t>
         </is>
       </c>
       <c r="B189" s="4" t="inlineStr">
         <is>
-          <t>Rental Equipments</t>
-        </is>
-      </c>
+          <t>Office Supply</t>
+        </is>
+      </c>
+      <c r="C189" s="5" t="n"/>
     </row>
     <row r="190">
-      <c r="A190" s="4" t="inlineStr">
-        <is>
-          <t>ค่าเช่าอุปกรณ์</t>
-        </is>
-      </c>
-      <c r="B190" s="4" t="inlineStr">
-        <is>
-          <t>Rental Equipments</t>
-        </is>
-      </c>
+      <c r="A190" s="3" t="inlineStr">
+        <is>
+          <t>── Operating Profit ──</t>
+        </is>
+      </c>
+      <c r="B190" s="4" t="n"/>
+      <c r="C190" s="5" t="n"/>
     </row>
     <row r="191">
-      <c r="A191" s="3" t="inlineStr">
-        <is>
-          <t>── Rental Office ──</t>
-        </is>
-      </c>
-      <c r="B191" s="3" t="inlineStr"/>
-      <c r="C191" s="3" t="inlineStr"/>
+      <c r="A191" s="6" t="inlineStr">
+        <is>
+          <t>operating profit</t>
+        </is>
+      </c>
+      <c r="B191" s="6" t="inlineStr">
+        <is>
+          <t>Operating Profit</t>
+        </is>
+      </c>
+      <c r="C191" s="3" t="n"/>
     </row>
     <row r="192">
       <c r="A192" s="4" t="inlineStr">
         <is>
-          <t>rental office</t>
+          <t>operatingprofit</t>
         </is>
       </c>
       <c r="B192" s="4" t="inlineStr">
         <is>
-          <t>Rental Office</t>
-        </is>
-      </c>
+          <t>Operating Profit</t>
+        </is>
+      </c>
+      <c r="C192" s="5" t="n"/>
     </row>
     <row r="193">
       <c r="A193" s="4" t="inlineStr">
         <is>
-          <t>office rental</t>
+          <t>profit operating</t>
         </is>
       </c>
       <c r="B193" s="4" t="inlineStr">
         <is>
-          <t>Rental Office</t>
-        </is>
-      </c>
+          <t>Operating Profit</t>
+        </is>
+      </c>
+      <c r="C193" s="5" t="n"/>
     </row>
     <row r="194">
       <c r="A194" s="4" t="inlineStr">
         <is>
-          <t>office rent</t>
+          <t>profitoperating</t>
         </is>
       </c>
       <c r="B194" s="4" t="inlineStr">
         <is>
-          <t>Rental Office</t>
-        </is>
-      </c>
+          <t>Operating Profit</t>
+        </is>
+      </c>
+      <c r="C194" s="5" t="n"/>
     </row>
     <row r="195">
-      <c r="A195" s="4" t="inlineStr">
-        <is>
-          <t>office lease</t>
-        </is>
-      </c>
-      <c r="B195" s="4" t="inlineStr">
-        <is>
-          <t>Rental Office</t>
-        </is>
-      </c>
+      <c r="A195" s="3" t="inlineStr">
+        <is>
+          <t>── Operating Profit Ratio ──</t>
+        </is>
+      </c>
+      <c r="B195" s="4" t="n"/>
+      <c r="C195" s="5" t="n"/>
     </row>
     <row r="196">
-      <c r="A196" s="4" t="inlineStr">
-        <is>
-          <t>ค่าเช่าสำนักงาน</t>
+      <c r="A196" s="6" t="inlineStr">
+        <is>
+          <t>operating profit ratio</t>
         </is>
       </c>
       <c r="B196" s="4" t="inlineStr">
         <is>
-          <t>Rental Office</t>
-        </is>
-      </c>
+          <t>Operating Profit Ratio</t>
+        </is>
+      </c>
+      <c r="C196" s="5" t="n"/>
     </row>
     <row r="197">
-      <c r="A197" s="3" t="inlineStr">
-        <is>
-          <t>── Repair and Maintenance (Direct) ──</t>
-        </is>
-      </c>
-      <c r="B197" s="3" t="inlineStr"/>
-      <c r="C197" s="3" t="inlineStr"/>
+      <c r="A197" s="6" t="inlineStr">
+        <is>
+          <t>operatingprofitratio</t>
+        </is>
+      </c>
+      <c r="B197" s="6" t="inlineStr">
+        <is>
+          <t>Operating Profit Ratio</t>
+        </is>
+      </c>
+      <c r="C197" s="3" t="n"/>
     </row>
     <row r="198">
       <c r="A198" s="4" t="inlineStr">
         <is>
-          <t>repair direct</t>
+          <t>ratio profit operating</t>
         </is>
       </c>
       <c r="B198" s="4" t="inlineStr">
         <is>
-          <t>Repair and Maintenance (Direct)</t>
-        </is>
-      </c>
+          <t>Operating Profit Ratio</t>
+        </is>
+      </c>
+      <c r="C198" s="5" t="n"/>
     </row>
     <row r="199">
       <c r="A199" s="4" t="inlineStr">
         <is>
-          <t>maintenance direct</t>
+          <t>ratioprofitoperating</t>
         </is>
       </c>
       <c r="B199" s="4" t="inlineStr">
         <is>
-          <t>Repair and Maintenance (Direct)</t>
-        </is>
-      </c>
+          <t>Operating Profit Ratio</t>
+        </is>
+      </c>
+      <c r="C199" s="5" t="n"/>
     </row>
     <row r="200">
-      <c r="A200" s="4" t="inlineStr">
-        <is>
-          <t>direct repair</t>
-        </is>
-      </c>
-      <c r="B200" s="4" t="inlineStr">
-        <is>
-          <t>Repair and Maintenance (Direct)</t>
-        </is>
-      </c>
+      <c r="A200" s="3" t="inlineStr">
+        <is>
+          <t>── Outsource Labor Fee ──</t>
+        </is>
+      </c>
+      <c r="B200" s="4" t="n"/>
+      <c r="C200" s="5" t="n"/>
     </row>
     <row r="201">
-      <c r="A201" s="4" t="inlineStr">
-        <is>
-          <t>direct maintenance</t>
+      <c r="A201" s="6" t="inlineStr">
+        <is>
+          <t>fee labor outsource</t>
         </is>
       </c>
       <c r="B201" s="4" t="inlineStr">
         <is>
-          <t>Repair and Maintenance (Direct)</t>
-        </is>
-      </c>
+          <t>Outsource Labor Fee</t>
+        </is>
+      </c>
+      <c r="C201" s="5" t="n"/>
     </row>
     <row r="202">
-      <c r="A202" s="3" t="inlineStr">
-        <is>
-          <t>── Repair and Maintenance (Expense) ──</t>
-        </is>
-      </c>
-      <c r="B202" s="3" t="inlineStr"/>
-      <c r="C202" s="3" t="inlineStr"/>
+      <c r="A202" s="6" t="inlineStr">
+        <is>
+          <t>feelaboroutsource</t>
+        </is>
+      </c>
+      <c r="B202" s="6" t="inlineStr">
+        <is>
+          <t>Outsource Labor Fee</t>
+        </is>
+      </c>
+      <c r="C202" s="3" t="n"/>
     </row>
     <row r="203">
       <c r="A203" s="4" t="inlineStr">
         <is>
-          <t>repair</t>
+          <t>labor fee</t>
         </is>
       </c>
       <c r="B203" s="4" t="inlineStr">
         <is>
-          <t>Repair and Maintenance (Expense)</t>
-        </is>
-      </c>
+          <t>Outsource Labor Fee</t>
+        </is>
+      </c>
+      <c r="C203" s="5" t="n"/>
     </row>
     <row r="204">
       <c r="A204" s="4" t="inlineStr">
         <is>
-          <t>maintenance</t>
+          <t>laborfee</t>
         </is>
       </c>
       <c r="B204" s="4" t="inlineStr">
         <is>
-          <t>Repair and Maintenance (Expense)</t>
-        </is>
-      </c>
+          <t>Outsource Labor Fee</t>
+        </is>
+      </c>
+      <c r="C204" s="5" t="n"/>
     </row>
     <row r="205">
       <c r="A205" s="4" t="inlineStr">
         <is>
-          <t>r&amp;m</t>
+          <t>outsource labor</t>
         </is>
       </c>
       <c r="B205" s="4" t="inlineStr">
         <is>
-          <t>Repair and Maintenance (Expense)</t>
-        </is>
-      </c>
+          <t>Outsource Labor Fee</t>
+        </is>
+      </c>
+      <c r="C205" s="5" t="n"/>
     </row>
     <row r="206">
-      <c r="A206" s="4" t="inlineStr">
-        <is>
-          <t>repair and maintenance</t>
+      <c r="A206" s="6" t="inlineStr">
+        <is>
+          <t>outsource labor fee</t>
         </is>
       </c>
       <c r="B206" s="4" t="inlineStr">
         <is>
-          <t>Repair and Maintenance (Expense)</t>
-        </is>
-      </c>
+          <t>Outsource Labor Fee</t>
+        </is>
+      </c>
+      <c r="C206" s="5" t="n"/>
     </row>
     <row r="207">
       <c r="A207" s="4" t="inlineStr">
         <is>
-          <t>fix equipment</t>
+          <t>outsourcelabor</t>
         </is>
       </c>
       <c r="B207" s="4" t="inlineStr">
         <is>
-          <t>Repair and Maintenance (Expense)</t>
-        </is>
-      </c>
+          <t>Outsource Labor Fee</t>
+        </is>
+      </c>
+      <c r="C207" s="5" t="n"/>
     </row>
     <row r="208">
       <c r="A208" s="4" t="inlineStr">
         <is>
-          <t>equipment repair</t>
+          <t>outsourcelaborfee</t>
         </is>
       </c>
       <c r="B208" s="4" t="inlineStr">
         <is>
-          <t>Repair and Maintenance (Expense)</t>
-        </is>
-      </c>
+          <t>Outsource Labor Fee</t>
+        </is>
+      </c>
+      <c r="C208" s="5" t="n"/>
     </row>
     <row r="209">
-      <c r="A209" s="4" t="inlineStr">
-        <is>
-          <t>building maintenance</t>
-        </is>
-      </c>
-      <c r="B209" s="4" t="inlineStr">
-        <is>
-          <t>Repair and Maintenance (Expense)</t>
-        </is>
-      </c>
+      <c r="A209" s="3" t="inlineStr">
+        <is>
+          <t>── Outsource Labor Ratio ──</t>
+        </is>
+      </c>
+      <c r="B209" s="4" t="n"/>
+      <c r="C209" s="5" t="n"/>
     </row>
     <row r="210">
-      <c r="A210" s="4" t="inlineStr">
-        <is>
-          <t>ซ่อมบำรุง</t>
+      <c r="A210" s="6" t="inlineStr">
+        <is>
+          <t>outsource labor ratio</t>
         </is>
       </c>
       <c r="B210" s="4" t="inlineStr">
         <is>
-          <t>Repair and Maintenance (Expense)</t>
-        </is>
-      </c>
+          <t>Outsource Labor Ratio</t>
+        </is>
+      </c>
+      <c r="C210" s="5" t="n"/>
     </row>
     <row r="211">
-      <c r="A211" s="3" t="inlineStr">
-        <is>
-          <t>── Electric&amp;Water Supply ──</t>
-        </is>
-      </c>
-      <c r="B211" s="3" t="inlineStr"/>
-      <c r="C211" s="3" t="inlineStr"/>
+      <c r="A211" s="6" t="inlineStr">
+        <is>
+          <t>outsourcelaborratio</t>
+        </is>
+      </c>
+      <c r="B211" s="6" t="inlineStr">
+        <is>
+          <t>Outsource Labor Ratio</t>
+        </is>
+      </c>
+      <c r="C211" s="3" t="n"/>
     </row>
     <row r="212">
       <c r="A212" s="4" t="inlineStr">
         <is>
-          <t>electric</t>
+          <t>ratio labor outsource</t>
         </is>
       </c>
       <c r="B212" s="4" t="inlineStr">
         <is>
-          <t>Electric&amp;Water Supply</t>
-        </is>
-      </c>
+          <t>Outsource Labor Ratio</t>
+        </is>
+      </c>
+      <c r="C212" s="5" t="n"/>
     </row>
     <row r="213">
       <c r="A213" s="4" t="inlineStr">
         <is>
-          <t>electricity</t>
+          <t>ratiolaboroutsource</t>
         </is>
       </c>
       <c r="B213" s="4" t="inlineStr">
         <is>
-          <t>Electric&amp;Water Supply</t>
-        </is>
-      </c>
+          <t>Outsource Labor Ratio</t>
+        </is>
+      </c>
+      <c r="C213" s="5" t="n"/>
     </row>
     <row r="214">
-      <c r="A214" s="4" t="inlineStr">
-        <is>
-          <t>water</t>
-        </is>
-      </c>
-      <c r="B214" s="4" t="inlineStr">
-        <is>
-          <t>Electric&amp;Water Supply</t>
-        </is>
-      </c>
+      <c r="A214" s="3" t="inlineStr">
+        <is>
+          <t>── Over Time ──</t>
+        </is>
+      </c>
+      <c r="B214" s="4" t="n"/>
+      <c r="C214" s="5" t="n"/>
     </row>
     <row r="215">
       <c r="A215" s="4" t="inlineStr">
         <is>
-          <t>utility</t>
+          <t>over time</t>
         </is>
       </c>
       <c r="B215" s="4" t="inlineStr">
         <is>
-          <t>Electric&amp;Water Supply</t>
-        </is>
-      </c>
+          <t>Over Time</t>
+        </is>
+      </c>
+      <c r="C215" s="5" t="n"/>
     </row>
     <row r="216">
-      <c r="A216" s="4" t="inlineStr">
-        <is>
-          <t>utilities</t>
+      <c r="A216" s="6" t="inlineStr">
+        <is>
+          <t>overtime</t>
         </is>
       </c>
       <c r="B216" s="4" t="inlineStr">
         <is>
-          <t>Electric&amp;Water Supply</t>
-        </is>
-      </c>
+          <t>Over Time</t>
+        </is>
+      </c>
+      <c r="C216" s="5" t="n"/>
     </row>
     <row r="217">
       <c r="A217" s="4" t="inlineStr">
         <is>
-          <t>electric&amp;water</t>
+          <t>time over</t>
         </is>
       </c>
       <c r="B217" s="4" t="inlineStr">
         <is>
-          <t>Electric&amp;Water Supply</t>
-        </is>
-      </c>
+          <t>Over Time</t>
+        </is>
+      </c>
+      <c r="C217" s="5" t="n"/>
     </row>
     <row r="218">
       <c r="A218" s="4" t="inlineStr">
         <is>
-          <t>electric &amp; water</t>
+          <t>timeover</t>
         </is>
       </c>
       <c r="B218" s="4" t="inlineStr">
         <is>
-          <t>Electric&amp;Water Supply</t>
-        </is>
-      </c>
+          <t>Over Time</t>
+        </is>
+      </c>
+      <c r="C218" s="5" t="n"/>
     </row>
     <row r="219">
-      <c r="A219" s="4" t="inlineStr">
-        <is>
-          <t>power</t>
-        </is>
-      </c>
-      <c r="B219" s="4" t="inlineStr">
-        <is>
-          <t>Electric&amp;Water Supply</t>
-        </is>
-      </c>
+      <c r="A219" s="3" t="inlineStr">
+        <is>
+          <t>── Personnel Expense ──</t>
+        </is>
+      </c>
+      <c r="B219" s="4" t="n"/>
+      <c r="C219" s="5" t="n"/>
     </row>
     <row r="220">
       <c r="A220" s="4" t="inlineStr">
         <is>
-          <t>energy cost</t>
+          <t>expense personnel</t>
         </is>
       </c>
       <c r="B220" s="4" t="inlineStr">
         <is>
-          <t>Electric&amp;Water Supply</t>
-        </is>
-      </c>
+          <t>Personnel Expense</t>
+        </is>
+      </c>
+      <c r="C220" s="5" t="n"/>
     </row>
     <row r="221">
-      <c r="A221" s="4" t="inlineStr">
-        <is>
-          <t>water supply</t>
+      <c r="A221" s="6" t="inlineStr">
+        <is>
+          <t>expensepersonnel</t>
         </is>
       </c>
       <c r="B221" s="4" t="inlineStr">
         <is>
-          <t>Electric&amp;Water Supply</t>
-        </is>
-      </c>
+          <t>Personnel Expense</t>
+        </is>
+      </c>
+      <c r="C221" s="5" t="n"/>
     </row>
     <row r="222">
       <c r="A222" s="4" t="inlineStr">
         <is>
-          <t>electric bill</t>
+          <t>personnel expense</t>
         </is>
       </c>
       <c r="B222" s="4" t="inlineStr">
         <is>
-          <t>Electric&amp;Water Supply</t>
-        </is>
-      </c>
+          <t>Personnel Expense</t>
+        </is>
+      </c>
+      <c r="C222" s="5" t="n"/>
     </row>
     <row r="223">
       <c r="A223" s="4" t="inlineStr">
         <is>
-          <t>water bill</t>
+          <t>personnelexpense</t>
         </is>
       </c>
       <c r="B223" s="4" t="inlineStr">
         <is>
-          <t>Electric&amp;Water Supply</t>
-        </is>
-      </c>
+          <t>Personnel Expense</t>
+        </is>
+      </c>
+      <c r="C223" s="5" t="n"/>
     </row>
     <row r="224">
-      <c r="A224" s="4" t="inlineStr">
-        <is>
-          <t>ค่าไฟ</t>
-        </is>
-      </c>
-      <c r="B224" s="4" t="inlineStr">
-        <is>
-          <t>Electric&amp;Water Supply</t>
-        </is>
-      </c>
+      <c r="A224" s="3" t="inlineStr">
+        <is>
+          <t>── Provident Fund ──</t>
+        </is>
+      </c>
+      <c r="B224" s="4" t="n"/>
+      <c r="C224" s="5" t="n"/>
     </row>
     <row r="225">
       <c r="A225" s="4" t="inlineStr">
         <is>
-          <t>ค่าน้ำ</t>
+          <t>fund provident</t>
         </is>
       </c>
       <c r="B225" s="4" t="inlineStr">
         <is>
-          <t>Electric&amp;Water Supply</t>
-        </is>
-      </c>
+          <t>Provident Fund</t>
+        </is>
+      </c>
+      <c r="C225" s="5" t="n"/>
     </row>
     <row r="226">
-      <c r="A226" s="3" t="inlineStr">
-        <is>
-          <t>── Depreciation ──</t>
-        </is>
-      </c>
-      <c r="B226" s="3" t="inlineStr"/>
-      <c r="C226" s="3" t="inlineStr"/>
+      <c r="A226" s="6" t="inlineStr">
+        <is>
+          <t>fundprovident</t>
+        </is>
+      </c>
+      <c r="B226" s="6" t="inlineStr">
+        <is>
+          <t>Provident Fund</t>
+        </is>
+      </c>
+      <c r="C226" s="3" t="n"/>
     </row>
     <row r="227">
       <c r="A227" s="4" t="inlineStr">
         <is>
-          <t>depreciation</t>
+          <t>provident fund</t>
         </is>
       </c>
       <c r="B227" s="4" t="inlineStr">
         <is>
-          <t>Depreciation</t>
-        </is>
-      </c>
+          <t>Provident Fund</t>
+        </is>
+      </c>
+      <c r="C227" s="5" t="n"/>
     </row>
     <row r="228">
-      <c r="A228" s="4" t="inlineStr">
-        <is>
-          <t>dep</t>
+      <c r="A228" s="6" t="inlineStr">
+        <is>
+          <t>providentfund</t>
         </is>
       </c>
       <c r="B228" s="4" t="inlineStr">
         <is>
-          <t>Depreciation</t>
-        </is>
-      </c>
+          <t>Provident Fund</t>
+        </is>
+      </c>
+      <c r="C228" s="5" t="n"/>
     </row>
     <row r="229">
-      <c r="A229" s="4" t="inlineStr">
-        <is>
-          <t>depreciate</t>
-        </is>
-      </c>
-      <c r="B229" s="4" t="inlineStr">
-        <is>
-          <t>Depreciation</t>
-        </is>
-      </c>
+      <c r="A229" s="3" t="inlineStr">
+        <is>
+          <t>── Rental Equipments ──</t>
+        </is>
+      </c>
+      <c r="B229" s="4" t="n"/>
+      <c r="C229" s="5" t="n"/>
     </row>
     <row r="230">
       <c r="A230" s="4" t="inlineStr">
         <is>
-          <t>amortization</t>
+          <t>equipments rental</t>
         </is>
       </c>
       <c r="B230" s="4" t="inlineStr">
         <is>
-          <t>Depreciation</t>
-        </is>
-      </c>
+          <t>Rental Equipments</t>
+        </is>
+      </c>
+      <c r="C230" s="5" t="n"/>
     </row>
     <row r="231">
       <c r="A231" s="4" t="inlineStr">
         <is>
-          <t>asset depreciation</t>
+          <t>equipmentsrental</t>
         </is>
       </c>
       <c r="B231" s="4" t="inlineStr">
         <is>
-          <t>Depreciation</t>
-        </is>
-      </c>
+          <t>Rental Equipments</t>
+        </is>
+      </c>
+      <c r="C231" s="5" t="n"/>
     </row>
     <row r="232">
       <c r="A232" s="4" t="inlineStr">
         <is>
-          <t>book value</t>
+          <t>rental equipments</t>
         </is>
       </c>
       <c r="B232" s="4" t="inlineStr">
         <is>
-          <t>Depreciation</t>
-        </is>
-      </c>
+          <t>Rental Equipments</t>
+        </is>
+      </c>
+      <c r="C232" s="5" t="n"/>
     </row>
     <row r="233">
-      <c r="A233" s="4" t="inlineStr">
-        <is>
-          <t>write off</t>
+      <c r="A233" s="6" t="inlineStr">
+        <is>
+          <t>rentalequipments</t>
         </is>
       </c>
       <c r="B233" s="4" t="inlineStr">
         <is>
-          <t>Depreciation</t>
-        </is>
-      </c>
+          <t>Rental Equipments</t>
+        </is>
+      </c>
+      <c r="C233" s="5" t="n"/>
     </row>
     <row r="234">
-      <c r="A234" s="4" t="inlineStr">
-        <is>
-          <t>ค่าเสื่อมราคา</t>
-        </is>
-      </c>
-      <c r="B234" s="4" t="inlineStr">
-        <is>
-          <t>Depreciation</t>
-        </is>
-      </c>
+      <c r="A234" s="3" t="inlineStr">
+        <is>
+          <t>── Rental Office ──</t>
+        </is>
+      </c>
+      <c r="B234" s="4" t="n"/>
+      <c r="C234" s="5" t="n"/>
     </row>
     <row r="235">
-      <c r="A235" s="3" t="inlineStr">
-        <is>
-          <t>── Gross Profit ──</t>
-        </is>
-      </c>
-      <c r="B235" s="3" t="inlineStr"/>
-      <c r="C235" s="3" t="inlineStr"/>
+      <c r="A235" s="6" t="inlineStr">
+        <is>
+          <t>office rental</t>
+        </is>
+      </c>
+      <c r="B235" s="6" t="inlineStr">
+        <is>
+          <t>Rental Office</t>
+        </is>
+      </c>
+      <c r="C235" s="3" t="n"/>
     </row>
     <row r="236">
       <c r="A236" s="4" t="inlineStr">
         <is>
-          <t>gross profit</t>
+          <t>officerental</t>
         </is>
       </c>
       <c r="B236" s="4" t="inlineStr">
         <is>
-          <t>Gross Profit</t>
-        </is>
-      </c>
+          <t>Rental Office</t>
+        </is>
+      </c>
+      <c r="C236" s="5" t="n"/>
     </row>
     <row r="237">
       <c r="A237" s="4" t="inlineStr">
         <is>
-          <t>gp</t>
+          <t>rental office</t>
         </is>
       </c>
       <c r="B237" s="4" t="inlineStr">
         <is>
-          <t>Gross Profit</t>
-        </is>
-      </c>
+          <t>Rental Office</t>
+        </is>
+      </c>
+      <c r="C237" s="5" t="n"/>
     </row>
     <row r="238">
-      <c r="A238" s="4" t="inlineStr">
-        <is>
-          <t>profit</t>
+      <c r="A238" s="6" t="inlineStr">
+        <is>
+          <t>rentaloffice</t>
         </is>
       </c>
       <c r="B238" s="4" t="inlineStr">
         <is>
-          <t>Gross Profit</t>
-        </is>
-      </c>
+          <t>Rental Office</t>
+        </is>
+      </c>
+      <c r="C238" s="5" t="n"/>
     </row>
     <row r="239">
-      <c r="A239" s="4" t="inlineStr">
-        <is>
-          <t>gross margin</t>
-        </is>
-      </c>
-      <c r="B239" s="4" t="inlineStr">
-        <is>
-          <t>Gross Profit</t>
-        </is>
-      </c>
+      <c r="A239" s="3" t="inlineStr">
+        <is>
+          <t>── Rental Other ──</t>
+        </is>
+      </c>
+      <c r="B239" s="4" t="n"/>
+      <c r="C239" s="5" t="n"/>
     </row>
     <row r="240">
       <c r="A240" s="4" t="inlineStr">
         <is>
-          <t>gross income</t>
+          <t>other rental</t>
         </is>
       </c>
       <c r="B240" s="4" t="inlineStr">
         <is>
-          <t>Gross Profit</t>
-        </is>
-      </c>
+          <t>Rental Other</t>
+        </is>
+      </c>
+      <c r="C240" s="5" t="n"/>
     </row>
     <row r="241">
       <c r="A241" s="4" t="inlineStr">
         <is>
-          <t>margin</t>
+          <t>otherrental</t>
         </is>
       </c>
       <c r="B241" s="4" t="inlineStr">
         <is>
-          <t>Gross Profit</t>
-        </is>
-      </c>
+          <t>Rental Other</t>
+        </is>
+      </c>
+      <c r="C241" s="5" t="n"/>
     </row>
     <row r="242">
-      <c r="A242" s="4" t="inlineStr">
-        <is>
-          <t>profitability</t>
+      <c r="A242" s="6" t="inlineStr">
+        <is>
+          <t>rental other</t>
         </is>
       </c>
       <c r="B242" s="4" t="inlineStr">
         <is>
-          <t>Gross Profit</t>
-        </is>
-      </c>
+          <t>Rental Other</t>
+        </is>
+      </c>
+      <c r="C242" s="5" t="n"/>
     </row>
     <row r="243">
-      <c r="A243" s="4" t="inlineStr">
-        <is>
-          <t>กำไรขั้นต้น</t>
+      <c r="A243" s="6" t="inlineStr">
+        <is>
+          <t>rentalother</t>
         </is>
       </c>
       <c r="B243" s="4" t="inlineStr">
         <is>
-          <t>Gross Profit</t>
-        </is>
-      </c>
+          <t>Rental Other</t>
+        </is>
+      </c>
+      <c r="C243" s="5" t="n"/>
     </row>
     <row r="244">
       <c r="A244" s="3" t="inlineStr">
         <is>
-          <t>── Marginal Profit ──</t>
-        </is>
-      </c>
-      <c r="B244" s="3" t="inlineStr"/>
-      <c r="C244" s="3" t="inlineStr"/>
+          <t>── Repair and Maintenance (Direct) ──</t>
+        </is>
+      </c>
+      <c r="B244" s="6" t="n"/>
+      <c r="C244" s="3" t="n"/>
     </row>
     <row r="245">
       <c r="A245" s="4" t="inlineStr">
         <is>
-          <t>marginal profit</t>
+          <t>and maintenance</t>
         </is>
       </c>
       <c r="B245" s="4" t="inlineStr">
         <is>
-          <t>Marginal Profit</t>
-        </is>
-      </c>
+          <t>Repair and Maintenance (Direct)</t>
+        </is>
+      </c>
+      <c r="C245" s="5" t="n"/>
     </row>
     <row r="246">
       <c r="A246" s="4" t="inlineStr">
         <is>
-          <t>marginal</t>
+          <t>andmaintenance</t>
         </is>
       </c>
       <c r="B246" s="4" t="inlineStr">
         <is>
-          <t>Marginal Profit</t>
-        </is>
-      </c>
+          <t>Repair and Maintenance (Direct)</t>
+        </is>
+      </c>
+      <c r="C246" s="5" t="n"/>
     </row>
     <row r="247">
-      <c r="A247" s="4" t="inlineStr">
-        <is>
-          <t>contribution margin</t>
+      <c r="A247" s="6" t="inlineStr">
+        <is>
+          <t>direct maintenance and repair</t>
         </is>
       </c>
       <c r="B247" s="4" t="inlineStr">
         <is>
-          <t>Marginal Profit</t>
-        </is>
-      </c>
+          <t>Repair and Maintenance (Direct)</t>
+        </is>
+      </c>
+      <c r="C247" s="5" t="n"/>
     </row>
     <row r="248">
-      <c r="A248" s="4" t="inlineStr">
-        <is>
-          <t>contribution</t>
+      <c r="A248" s="6" t="inlineStr">
+        <is>
+          <t>directmaintenanceandrepair</t>
         </is>
       </c>
       <c r="B248" s="4" t="inlineStr">
         <is>
-          <t>Marginal Profit</t>
-        </is>
-      </c>
+          <t>Repair and Maintenance (Direct)</t>
+        </is>
+      </c>
+      <c r="C248" s="5" t="n"/>
     </row>
     <row r="249">
-      <c r="A249" s="3" t="inlineStr">
-        <is>
-          <t>── Operating Profit ──</t>
-        </is>
-      </c>
-      <c r="B249" s="3" t="inlineStr"/>
-      <c r="C249" s="3" t="inlineStr"/>
+      <c r="A249" s="6" t="inlineStr">
+        <is>
+          <t>maintenance direct</t>
+        </is>
+      </c>
+      <c r="B249" s="6" t="inlineStr">
+        <is>
+          <t>Repair and Maintenance (Direct)</t>
+        </is>
+      </c>
+      <c r="C249" s="3" t="n"/>
     </row>
     <row r="250">
       <c r="A250" s="4" t="inlineStr">
         <is>
-          <t>operating profit</t>
+          <t>maintenancedirect</t>
         </is>
       </c>
       <c r="B250" s="4" t="inlineStr">
         <is>
-          <t>Operating Profit</t>
-        </is>
-      </c>
+          <t>Repair and Maintenance (Direct)</t>
+        </is>
+      </c>
+      <c r="C250" s="5" t="n"/>
     </row>
     <row r="251">
       <c r="A251" s="4" t="inlineStr">
         <is>
-          <t>op</t>
+          <t>repair and</t>
         </is>
       </c>
       <c r="B251" s="4" t="inlineStr">
         <is>
-          <t>Operating Profit</t>
-        </is>
-      </c>
+          <t>Repair and Maintenance (Direct)</t>
+        </is>
+      </c>
+      <c r="C251" s="5" t="n"/>
     </row>
     <row r="252">
       <c r="A252" s="4" t="inlineStr">
         <is>
-          <t>net profit</t>
+          <t>repair and maintenance (direct)</t>
         </is>
       </c>
       <c r="B252" s="4" t="inlineStr">
         <is>
-          <t>Operating Profit</t>
-        </is>
-      </c>
+          <t>Repair and Maintenance (Direct)</t>
+        </is>
+      </c>
+      <c r="C252" s="5" t="n"/>
     </row>
     <row r="253">
-      <c r="A253" s="4" t="inlineStr">
-        <is>
-          <t>net income</t>
+      <c r="A253" s="6" t="inlineStr">
+        <is>
+          <t>repair and maintenance direct</t>
         </is>
       </c>
       <c r="B253" s="4" t="inlineStr">
         <is>
-          <t>Operating Profit</t>
-        </is>
-      </c>
+          <t>Repair and Maintenance (Direct)</t>
+        </is>
+      </c>
+      <c r="C253" s="5" t="n"/>
     </row>
     <row r="254">
       <c r="A254" s="4" t="inlineStr">
         <is>
-          <t>bottom line</t>
+          <t>repairand</t>
         </is>
       </c>
       <c r="B254" s="4" t="inlineStr">
         <is>
-          <t>Operating Profit</t>
-        </is>
-      </c>
+          <t>Repair and Maintenance (Direct)</t>
+        </is>
+      </c>
+      <c r="C254" s="5" t="n"/>
     </row>
     <row r="255">
       <c r="A255" s="4" t="inlineStr">
         <is>
-          <t>operating income</t>
+          <t>repairandmaintenancedirect</t>
         </is>
       </c>
       <c r="B255" s="4" t="inlineStr">
         <is>
-          <t>Operating Profit</t>
-        </is>
-      </c>
+          <t>Repair and Maintenance (Direct)</t>
+        </is>
+      </c>
+      <c r="C255" s="5" t="n"/>
     </row>
     <row r="256">
-      <c r="A256" s="4" t="inlineStr">
-        <is>
-          <t>ebit</t>
-        </is>
-      </c>
-      <c r="B256" s="4" t="inlineStr">
-        <is>
-          <t>Operating Profit</t>
-        </is>
-      </c>
+      <c r="A256" s="3" t="inlineStr">
+        <is>
+          <t>── Repair and Maintenance (Expense) ──</t>
+        </is>
+      </c>
+      <c r="B256" s="4" t="n"/>
+      <c r="C256" s="5" t="n"/>
     </row>
     <row r="257">
       <c r="A257" s="4" t="inlineStr">
         <is>
-          <t>กำไรจากการดำเนินงาน</t>
+          <t>expense maintenance and repair</t>
         </is>
       </c>
       <c r="B257" s="4" t="inlineStr">
         <is>
-          <t>Operating Profit</t>
-        </is>
-      </c>
+          <t>Repair and Maintenance (Expense)</t>
+        </is>
+      </c>
+      <c r="C257" s="5" t="n"/>
     </row>
     <row r="258">
-      <c r="A258" s="3" t="inlineStr">
-        <is>
-          <t>── Expense Total ──</t>
-        </is>
-      </c>
-      <c r="B258" s="3" t="inlineStr"/>
-      <c r="C258" s="3" t="inlineStr"/>
+      <c r="A258" s="6" t="inlineStr">
+        <is>
+          <t>expensemaintenanceandrepair</t>
+        </is>
+      </c>
+      <c r="B258" s="6" t="inlineStr">
+        <is>
+          <t>Repair and Maintenance (Expense)</t>
+        </is>
+      </c>
+      <c r="C258" s="3" t="n"/>
     </row>
     <row r="259">
       <c r="A259" s="4" t="inlineStr">
         <is>
-          <t>expense total</t>
+          <t>maintenance expense</t>
         </is>
       </c>
       <c r="B259" s="4" t="inlineStr">
         <is>
-          <t>Expense Total</t>
-        </is>
-      </c>
+          <t>Repair and Maintenance (Expense)</t>
+        </is>
+      </c>
+      <c r="C259" s="5" t="n"/>
     </row>
     <row r="260">
-      <c r="A260" s="4" t="inlineStr">
-        <is>
-          <t>total expense</t>
+      <c r="A260" s="6" t="inlineStr">
+        <is>
+          <t>maintenanceexpense</t>
         </is>
       </c>
       <c r="B260" s="4" t="inlineStr">
         <is>
-          <t>Expense Total</t>
-        </is>
-      </c>
+          <t>Repair and Maintenance (Expense)</t>
+        </is>
+      </c>
+      <c r="C260" s="5" t="n"/>
     </row>
     <row r="261">
       <c r="A261" s="4" t="inlineStr">
         <is>
-          <t>total expenses</t>
+          <t>repair and maintenance (expense)</t>
         </is>
       </c>
       <c r="B261" s="4" t="inlineStr">
         <is>
-          <t>Expense Total</t>
-        </is>
-      </c>
+          <t>Repair and Maintenance (Expense)</t>
+        </is>
+      </c>
+      <c r="C261" s="5" t="n"/>
     </row>
     <row r="262">
       <c r="A262" s="4" t="inlineStr">
         <is>
-          <t>all expenses</t>
+          <t>repair and maintenance expense</t>
         </is>
       </c>
       <c r="B262" s="4" t="inlineStr">
         <is>
-          <t>Expense Total</t>
-        </is>
-      </c>
+          <t>Repair and Maintenance (Expense)</t>
+        </is>
+      </c>
+      <c r="C262" s="5" t="n"/>
     </row>
     <row r="263">
-      <c r="A263" s="3" t="inlineStr">
-        <is>
-          <t>── Conference ──</t>
-        </is>
-      </c>
-      <c r="B263" s="3" t="inlineStr"/>
-      <c r="C263" s="3" t="inlineStr"/>
+      <c r="A263" s="6" t="inlineStr">
+        <is>
+          <t>repairandmaintenanceexpense</t>
+        </is>
+      </c>
+      <c r="B263" s="6" t="inlineStr">
+        <is>
+          <t>Repair and Maintenance (Expense)</t>
+        </is>
+      </c>
+      <c r="C263" s="3" t="n"/>
     </row>
     <row r="264">
-      <c r="A264" s="4" t="inlineStr">
-        <is>
-          <t>conference</t>
-        </is>
-      </c>
-      <c r="B264" s="4" t="inlineStr">
-        <is>
-          <t>Conference</t>
-        </is>
-      </c>
+      <c r="A264" s="3" t="inlineStr">
+        <is>
+          <t>── Revenue Total ──</t>
+        </is>
+      </c>
+      <c r="B264" s="4" t="n"/>
+      <c r="C264" s="5" t="n"/>
     </row>
     <row r="265">
-      <c r="A265" s="4" t="inlineStr">
-        <is>
-          <t>meeting</t>
+      <c r="A265" s="6" t="inlineStr">
+        <is>
+          <t>revenue total</t>
         </is>
       </c>
       <c r="B265" s="4" t="inlineStr">
         <is>
-          <t>Conference</t>
-        </is>
-      </c>
+          <t>Revenue Total</t>
+        </is>
+      </c>
+      <c r="C265" s="5" t="n"/>
     </row>
     <row r="266">
       <c r="A266" s="4" t="inlineStr">
         <is>
-          <t>seminar</t>
+          <t>revenuetotal</t>
         </is>
       </c>
       <c r="B266" s="4" t="inlineStr">
         <is>
-          <t>Conference</t>
-        </is>
-      </c>
+          <t>Revenue Total</t>
+        </is>
+      </c>
+      <c r="C266" s="5" t="n"/>
     </row>
     <row r="267">
       <c r="A267" s="4" t="inlineStr">
         <is>
-          <t>training</t>
+          <t>total revenue</t>
         </is>
       </c>
       <c r="B267" s="4" t="inlineStr">
         <is>
-          <t>Conference</t>
-        </is>
-      </c>
+          <t>Revenue Total</t>
+        </is>
+      </c>
+      <c r="C267" s="5" t="n"/>
     </row>
     <row r="268">
       <c r="A268" s="4" t="inlineStr">
         <is>
-          <t>workshop</t>
+          <t>totalrevenue</t>
         </is>
       </c>
       <c r="B268" s="4" t="inlineStr">
         <is>
-          <t>Conference</t>
-        </is>
-      </c>
+          <t>Revenue Total</t>
+        </is>
+      </c>
+      <c r="C268" s="5" t="n"/>
     </row>
     <row r="269">
-      <c r="A269" s="4" t="inlineStr">
-        <is>
-          <t>ค่าประชุม</t>
-        </is>
-      </c>
-      <c r="B269" s="4" t="inlineStr">
-        <is>
-          <t>Conference</t>
-        </is>
-      </c>
+      <c r="A269" s="3" t="inlineStr">
+        <is>
+          <t>── Revenue per Head ──</t>
+        </is>
+      </c>
+      <c r="B269" s="4" t="n"/>
+      <c r="C269" s="5" t="n"/>
     </row>
     <row r="270">
-      <c r="A270" s="3" t="inlineStr">
-        <is>
-          <t>── Entertainment ──</t>
-        </is>
-      </c>
-      <c r="B270" s="3" t="inlineStr"/>
-      <c r="C270" s="3" t="inlineStr"/>
+      <c r="A270" s="6" t="inlineStr">
+        <is>
+          <t>head per revenue</t>
+        </is>
+      </c>
+      <c r="B270" s="6" t="inlineStr">
+        <is>
+          <t>Revenue per Head</t>
+        </is>
+      </c>
+      <c r="C270" s="3" t="n"/>
     </row>
     <row r="271">
       <c r="A271" s="4" t="inlineStr">
         <is>
-          <t>entertainment</t>
+          <t>headperrevenue</t>
         </is>
       </c>
       <c r="B271" s="4" t="inlineStr">
         <is>
-          <t>Entertainment</t>
-        </is>
-      </c>
+          <t>Revenue per Head</t>
+        </is>
+      </c>
+      <c r="C271" s="5" t="n"/>
     </row>
     <row r="272">
       <c r="A272" s="4" t="inlineStr">
         <is>
-          <t>entertain</t>
+          <t>per head</t>
         </is>
       </c>
       <c r="B272" s="4" t="inlineStr">
         <is>
-          <t>Entertainment</t>
-        </is>
-      </c>
+          <t>Revenue per Head</t>
+        </is>
+      </c>
+      <c r="C272" s="5" t="n"/>
     </row>
     <row r="273">
       <c r="A273" s="4" t="inlineStr">
         <is>
-          <t>hospitality</t>
+          <t>perhead</t>
         </is>
       </c>
       <c r="B273" s="4" t="inlineStr">
         <is>
-          <t>Entertainment</t>
-        </is>
-      </c>
+          <t>Revenue per Head</t>
+        </is>
+      </c>
+      <c r="C273" s="5" t="n"/>
     </row>
     <row r="274">
       <c r="A274" s="4" t="inlineStr">
         <is>
-          <t>ค่ารับรอง</t>
+          <t>revenue per</t>
         </is>
       </c>
       <c r="B274" s="4" t="inlineStr">
         <is>
-          <t>Entertainment</t>
-        </is>
-      </c>
+          <t>Revenue per Head</t>
+        </is>
+      </c>
+      <c r="C274" s="5" t="n"/>
     </row>
     <row r="275">
-      <c r="A275" s="3" t="inlineStr">
-        <is>
-          <t>── Transportation ──</t>
-        </is>
-      </c>
-      <c r="B275" s="3" t="inlineStr"/>
-      <c r="C275" s="3" t="inlineStr"/>
+      <c r="A275" s="6" t="inlineStr">
+        <is>
+          <t>revenue per head</t>
+        </is>
+      </c>
+      <c r="B275" s="6" t="inlineStr">
+        <is>
+          <t>Revenue per Head</t>
+        </is>
+      </c>
+      <c r="C275" s="3" t="n"/>
     </row>
     <row r="276">
       <c r="A276" s="4" t="inlineStr">
         <is>
-          <t>transport</t>
+          <t>revenueper</t>
         </is>
       </c>
       <c r="B276" s="4" t="inlineStr">
         <is>
-          <t>Transportation</t>
-        </is>
-      </c>
+          <t>Revenue per Head</t>
+        </is>
+      </c>
+      <c r="C276" s="5" t="n"/>
     </row>
     <row r="277">
-      <c r="A277" s="4" t="inlineStr">
-        <is>
-          <t>transportation</t>
+      <c r="A277" s="6" t="inlineStr">
+        <is>
+          <t>revenueperhead</t>
         </is>
       </c>
       <c r="B277" s="4" t="inlineStr">
         <is>
-          <t>Transportation</t>
-        </is>
-      </c>
+          <t>Revenue per Head</t>
+        </is>
+      </c>
+      <c r="C277" s="5" t="n"/>
     </row>
     <row r="278">
-      <c r="A278" s="4" t="inlineStr">
-        <is>
-          <t>travel</t>
-        </is>
-      </c>
-      <c r="B278" s="4" t="inlineStr">
-        <is>
-          <t>Transportation</t>
-        </is>
-      </c>
+      <c r="A278" s="3" t="inlineStr">
+        <is>
+          <t>── Salary ──</t>
+        </is>
+      </c>
+      <c r="B278" s="4" t="n"/>
+      <c r="C278" s="5" t="n"/>
     </row>
     <row r="279">
       <c r="A279" s="4" t="inlineStr">
         <is>
-          <t>travel expense</t>
+          <t>salary</t>
         </is>
       </c>
       <c r="B279" s="4" t="inlineStr">
         <is>
-          <t>Transportation</t>
-        </is>
-      </c>
+          <t>Salary</t>
+        </is>
+      </c>
+      <c r="C279" s="5" t="n"/>
     </row>
     <row r="280">
-      <c r="A280" s="4" t="inlineStr">
-        <is>
-          <t>trip</t>
-        </is>
-      </c>
-      <c r="B280" s="4" t="inlineStr">
-        <is>
-          <t>Transportation</t>
-        </is>
-      </c>
+      <c r="A280" s="3" t="inlineStr">
+        <is>
+          <t>── Security ──</t>
+        </is>
+      </c>
+      <c r="B280" s="4" t="n"/>
+      <c r="C280" s="5" t="n"/>
     </row>
     <row r="281">
       <c r="A281" s="4" t="inlineStr">
         <is>
-          <t>business trip</t>
+          <t>security</t>
         </is>
       </c>
       <c r="B281" s="4" t="inlineStr">
         <is>
-          <t>Transportation</t>
-        </is>
-      </c>
+          <t>Security</t>
+        </is>
+      </c>
+      <c r="C281" s="5" t="n"/>
     </row>
     <row r="282">
-      <c r="A282" s="4" t="inlineStr">
-        <is>
-          <t>commute</t>
-        </is>
-      </c>
-      <c r="B282" s="4" t="inlineStr">
-        <is>
-          <t>Transportation</t>
-        </is>
-      </c>
+      <c r="A282" s="3" t="inlineStr">
+        <is>
+          <t>── Service Office ──</t>
+        </is>
+      </c>
+      <c r="B282" s="4" t="n"/>
+      <c r="C282" s="5" t="n"/>
     </row>
     <row r="283">
       <c r="A283" s="4" t="inlineStr">
         <is>
-          <t>logistics expense</t>
+          <t>office service</t>
         </is>
       </c>
       <c r="B283" s="4" t="inlineStr">
         <is>
-          <t>Transportation</t>
-        </is>
-      </c>
+          <t>Service Office</t>
+        </is>
+      </c>
+      <c r="C283" s="5" t="n"/>
     </row>
     <row r="284">
       <c r="A284" s="4" t="inlineStr">
         <is>
-          <t>ค่าเดินทาง</t>
+          <t>officeservice</t>
         </is>
       </c>
       <c r="B284" s="4" t="inlineStr">
         <is>
-          <t>Transportation</t>
-        </is>
-      </c>
+          <t>Service Office</t>
+        </is>
+      </c>
+      <c r="C284" s="5" t="n"/>
     </row>
     <row r="285">
-      <c r="A285" s="3" t="inlineStr">
-        <is>
-          <t>── Telephone ──</t>
-        </is>
-      </c>
-      <c r="B285" s="3" t="inlineStr"/>
-      <c r="C285" s="3" t="inlineStr"/>
+      <c r="A285" s="6" t="inlineStr">
+        <is>
+          <t>service office</t>
+        </is>
+      </c>
+      <c r="B285" s="6" t="inlineStr">
+        <is>
+          <t>Service Office</t>
+        </is>
+      </c>
+      <c r="C285" s="3" t="n"/>
     </row>
     <row r="286">
       <c r="A286" s="4" t="inlineStr">
         <is>
-          <t>telephone</t>
+          <t>serviceoffice</t>
         </is>
       </c>
       <c r="B286" s="4" t="inlineStr">
         <is>
-          <t>Telephone</t>
-        </is>
-      </c>
+          <t>Service Office</t>
+        </is>
+      </c>
+      <c r="C286" s="5" t="n"/>
     </row>
     <row r="287">
-      <c r="A287" s="4" t="inlineStr">
-        <is>
-          <t>phone</t>
-        </is>
-      </c>
-      <c r="B287" s="4" t="inlineStr">
-        <is>
-          <t>Telephone</t>
-        </is>
-      </c>
+      <c r="A287" s="3" t="inlineStr">
+        <is>
+          <t>── Severance Pay / Retirement Fee ──</t>
+        </is>
+      </c>
+      <c r="B287" s="4" t="n"/>
+      <c r="C287" s="5" t="n"/>
     </row>
     <row r="288">
       <c r="A288" s="4" t="inlineStr">
         <is>
-          <t>phone bill</t>
+          <t>fee retirement pay severance</t>
         </is>
       </c>
       <c r="B288" s="4" t="inlineStr">
         <is>
-          <t>Telephone</t>
-        </is>
-      </c>
+          <t>Severance Pay / Retirement Fee</t>
+        </is>
+      </c>
+      <c r="C288" s="5" t="n"/>
     </row>
     <row r="289">
       <c r="A289" s="4" t="inlineStr">
         <is>
-          <t>tel</t>
+          <t>feeretirementpayseverance</t>
         </is>
       </c>
       <c r="B289" s="4" t="inlineStr">
         <is>
-          <t>Telephone</t>
-        </is>
-      </c>
+          <t>Severance Pay / Retirement Fee</t>
+        </is>
+      </c>
+      <c r="C289" s="5" t="n"/>
     </row>
     <row r="290">
       <c r="A290" s="4" t="inlineStr">
         <is>
-          <t>landline</t>
+          <t>pay retirement</t>
         </is>
       </c>
       <c r="B290" s="4" t="inlineStr">
         <is>
-          <t>Telephone</t>
-        </is>
-      </c>
+          <t>Severance Pay / Retirement Fee</t>
+        </is>
+      </c>
+      <c r="C290" s="5" t="n"/>
     </row>
     <row r="291">
       <c r="A291" s="4" t="inlineStr">
         <is>
-          <t>ค่าโทรศัพท์</t>
+          <t>payretirement</t>
         </is>
       </c>
       <c r="B291" s="4" t="inlineStr">
         <is>
-          <t>Telephone</t>
-        </is>
-      </c>
+          <t>Severance Pay / Retirement Fee</t>
+        </is>
+      </c>
+      <c r="C291" s="5" t="n"/>
     </row>
     <row r="292">
-      <c r="A292" s="3" t="inlineStr">
-        <is>
-          <t>── Mobile Phone ──</t>
-        </is>
-      </c>
-      <c r="B292" s="3" t="inlineStr"/>
-      <c r="C292" s="3" t="inlineStr"/>
+      <c r="A292" s="6" t="inlineStr">
+        <is>
+          <t>retirement fee</t>
+        </is>
+      </c>
+      <c r="B292" s="6" t="inlineStr">
+        <is>
+          <t>Severance Pay / Retirement Fee</t>
+        </is>
+      </c>
+      <c r="C292" s="3" t="n"/>
     </row>
     <row r="293">
       <c r="A293" s="4" t="inlineStr">
         <is>
-          <t>mobile</t>
+          <t>retirementfee</t>
         </is>
       </c>
       <c r="B293" s="4" t="inlineStr">
         <is>
-          <t>Mobile Phone</t>
-        </is>
-      </c>
+          <t>Severance Pay / Retirement Fee</t>
+        </is>
+      </c>
+      <c r="C293" s="5" t="n"/>
     </row>
     <row r="294">
-      <c r="A294" s="4" t="inlineStr">
-        <is>
-          <t>mobile phone</t>
+      <c r="A294" s="6" t="inlineStr">
+        <is>
+          <t>severance pay</t>
         </is>
       </c>
       <c r="B294" s="4" t="inlineStr">
         <is>
-          <t>Mobile Phone</t>
-        </is>
-      </c>
+          <t>Severance Pay / Retirement Fee</t>
+        </is>
+      </c>
+      <c r="C294" s="5" t="n"/>
     </row>
     <row r="295">
       <c r="A295" s="4" t="inlineStr">
         <is>
-          <t>cell phone</t>
+          <t>severance pay / retirement fee</t>
         </is>
       </c>
       <c r="B295" s="4" t="inlineStr">
         <is>
-          <t>Mobile Phone</t>
-        </is>
-      </c>
+          <t>Severance Pay / Retirement Fee</t>
+        </is>
+      </c>
+      <c r="C295" s="5" t="n"/>
     </row>
     <row r="296">
-      <c r="A296" s="4" t="inlineStr">
-        <is>
-          <t>cellphone</t>
+      <c r="A296" s="6" t="inlineStr">
+        <is>
+          <t>severance pay retirement fee</t>
         </is>
       </c>
       <c r="B296" s="4" t="inlineStr">
         <is>
-          <t>Mobile Phone</t>
-        </is>
-      </c>
+          <t>Severance Pay / Retirement Fee</t>
+        </is>
+      </c>
+      <c r="C296" s="5" t="n"/>
     </row>
     <row r="297">
-      <c r="A297" s="4" t="inlineStr">
-        <is>
-          <t>smartphone</t>
+      <c r="A297" s="6" t="inlineStr">
+        <is>
+          <t>severancepay</t>
         </is>
       </c>
       <c r="B297" s="4" t="inlineStr">
         <is>
-          <t>Mobile Phone</t>
-        </is>
-      </c>
+          <t>Severance Pay / Retirement Fee</t>
+        </is>
+      </c>
+      <c r="C297" s="5" t="n"/>
     </row>
     <row r="298">
-      <c r="A298" s="4" t="inlineStr">
-        <is>
-          <t>mobile bill</t>
+      <c r="A298" s="6" t="inlineStr">
+        <is>
+          <t>severancepayretirementfee</t>
         </is>
       </c>
       <c r="B298" s="4" t="inlineStr">
         <is>
-          <t>Mobile Phone</t>
-        </is>
-      </c>
+          <t>Severance Pay / Retirement Fee</t>
+        </is>
+      </c>
+      <c r="C298" s="5" t="n"/>
     </row>
     <row r="299">
       <c r="A299" s="3" t="inlineStr">
         <is>
-          <t>── Lease Circuit ──</t>
-        </is>
-      </c>
-      <c r="B299" s="3" t="inlineStr"/>
-      <c r="C299" s="3" t="inlineStr"/>
+          <t>── Signboard Tax ──</t>
+        </is>
+      </c>
+      <c r="B299" s="6" t="n"/>
+      <c r="C299" s="3" t="n"/>
     </row>
     <row r="300">
       <c r="A300" s="4" t="inlineStr">
         <is>
-          <t>lease circuit</t>
+          <t>signboard tax</t>
         </is>
       </c>
       <c r="B300" s="4" t="inlineStr">
         <is>
-          <t>Lease Circuit</t>
-        </is>
-      </c>
+          <t>Signboard Tax</t>
+        </is>
+      </c>
+      <c r="C300" s="5" t="n"/>
     </row>
     <row r="301">
-      <c r="A301" s="4" t="inlineStr">
-        <is>
-          <t>circuit</t>
+      <c r="A301" s="6" t="inlineStr">
+        <is>
+          <t>signboardtax</t>
         </is>
       </c>
       <c r="B301" s="4" t="inlineStr">
         <is>
-          <t>Lease Circuit</t>
-        </is>
-      </c>
+          <t>Signboard Tax</t>
+        </is>
+      </c>
+      <c r="C301" s="5" t="n"/>
     </row>
     <row r="302">
       <c r="A302" s="4" t="inlineStr">
         <is>
-          <t>internet</t>
+          <t>tax signboard</t>
         </is>
       </c>
       <c r="B302" s="4" t="inlineStr">
         <is>
-          <t>Lease Circuit</t>
-        </is>
-      </c>
+          <t>Signboard Tax</t>
+        </is>
+      </c>
+      <c r="C302" s="5" t="n"/>
     </row>
     <row r="303">
-      <c r="A303" s="4" t="inlineStr">
-        <is>
-          <t>network</t>
+      <c r="A303" s="6" t="inlineStr">
+        <is>
+          <t>taxsignboard</t>
         </is>
       </c>
       <c r="B303" s="4" t="inlineStr">
         <is>
-          <t>Lease Circuit</t>
-        </is>
-      </c>
+          <t>Signboard Tax</t>
+        </is>
+      </c>
+      <c r="C303" s="5" t="n"/>
     </row>
     <row r="304">
-      <c r="A304" s="4" t="inlineStr">
-        <is>
-          <t>bandwidth</t>
-        </is>
-      </c>
-      <c r="B304" s="4" t="inlineStr">
-        <is>
-          <t>Lease Circuit</t>
-        </is>
-      </c>
+      <c r="A304" s="3" t="inlineStr">
+        <is>
+          <t>── Social security ──</t>
+        </is>
+      </c>
+      <c r="B304" s="4" t="n"/>
+      <c r="C304" s="5" t="n"/>
     </row>
     <row r="305">
       <c r="A305" s="4" t="inlineStr">
         <is>
-          <t>leased line</t>
+          <t>security social</t>
         </is>
       </c>
       <c r="B305" s="4" t="inlineStr">
         <is>
-          <t>Lease Circuit</t>
-        </is>
-      </c>
+          <t>Social security</t>
+        </is>
+      </c>
+      <c r="C305" s="5" t="n"/>
     </row>
     <row r="306">
-      <c r="A306" s="4" t="inlineStr">
-        <is>
-          <t>data circuit</t>
+      <c r="A306" s="6" t="inlineStr">
+        <is>
+          <t>securitysocial</t>
         </is>
       </c>
       <c r="B306" s="4" t="inlineStr">
         <is>
-          <t>Lease Circuit</t>
-        </is>
-      </c>
+          <t>Social security</t>
+        </is>
+      </c>
+      <c r="C306" s="5" t="n"/>
     </row>
     <row r="307">
       <c r="A307" s="4" t="inlineStr">
         <is>
-          <t>wan</t>
+          <t>social security</t>
         </is>
       </c>
       <c r="B307" s="4" t="inlineStr">
         <is>
-          <t>Lease Circuit</t>
-        </is>
-      </c>
+          <t>Social security</t>
+        </is>
+      </c>
+      <c r="C307" s="5" t="n"/>
     </row>
     <row r="308">
       <c r="A308" s="4" t="inlineStr">
         <is>
-          <t>vpn</t>
+          <t>socialsecurity</t>
         </is>
       </c>
       <c r="B308" s="4" t="inlineStr">
         <is>
-          <t>Lease Circuit</t>
-        </is>
-      </c>
+          <t>Social security</t>
+        </is>
+      </c>
+      <c r="C308" s="5" t="n"/>
     </row>
     <row r="309">
-      <c r="A309" s="4" t="inlineStr">
-        <is>
-          <t>ค่าอินเทอร์เน็ต</t>
-        </is>
-      </c>
-      <c r="B309" s="4" t="inlineStr">
-        <is>
-          <t>Lease Circuit</t>
-        </is>
-      </c>
+      <c r="A309" s="3" t="inlineStr">
+        <is>
+          <t>── Software License ──</t>
+        </is>
+      </c>
+      <c r="B309" s="4" t="n"/>
+      <c r="C309" s="5" t="n"/>
     </row>
     <row r="310">
-      <c r="A310" s="3" t="inlineStr">
-        <is>
-          <t>── Office Supply ──</t>
-        </is>
-      </c>
-      <c r="B310" s="3" t="inlineStr"/>
-      <c r="C310" s="3" t="inlineStr"/>
+      <c r="A310" s="6" t="inlineStr">
+        <is>
+          <t>license software</t>
+        </is>
+      </c>
+      <c r="B310" s="6" t="inlineStr">
+        <is>
+          <t>Software License</t>
+        </is>
+      </c>
+      <c r="C310" s="3" t="n"/>
     </row>
     <row r="311">
-      <c r="A311" s="4" t="inlineStr">
-        <is>
-          <t>office supply</t>
+      <c r="A311" s="6" t="inlineStr">
+        <is>
+          <t>licensesoftware</t>
         </is>
       </c>
       <c r="B311" s="4" t="inlineStr">
         <is>
-          <t>Office Supply</t>
-        </is>
-      </c>
+          <t>Software License</t>
+        </is>
+      </c>
+      <c r="C311" s="5" t="n"/>
     </row>
     <row r="312">
       <c r="A312" s="4" t="inlineStr">
         <is>
-          <t>office supplies</t>
+          <t>software license</t>
         </is>
       </c>
       <c r="B312" s="4" t="inlineStr">
         <is>
-          <t>Office Supply</t>
-        </is>
-      </c>
+          <t>Software License</t>
+        </is>
+      </c>
+      <c r="C312" s="5" t="n"/>
     </row>
     <row r="313">
-      <c r="A313" s="4" t="inlineStr">
-        <is>
-          <t>stationery</t>
+      <c r="A313" s="6" t="inlineStr">
+        <is>
+          <t>softwarelicense</t>
         </is>
       </c>
       <c r="B313" s="4" t="inlineStr">
         <is>
-          <t>Office Supply</t>
-        </is>
-      </c>
+          <t>Software License</t>
+        </is>
+      </c>
+      <c r="C313" s="5" t="n"/>
     </row>
     <row r="314">
-      <c r="A314" s="4" t="inlineStr">
-        <is>
-          <t>stationary</t>
-        </is>
-      </c>
-      <c r="B314" s="4" t="inlineStr">
-        <is>
-          <t>Office Supply</t>
-        </is>
-      </c>
+      <c r="A314" s="3" t="inlineStr">
+        <is>
+          <t>── Staff Amenity ──</t>
+        </is>
+      </c>
+      <c r="B314" s="4" t="n"/>
+      <c r="C314" s="5" t="n"/>
     </row>
     <row r="315">
-      <c r="A315" s="4" t="inlineStr">
-        <is>
-          <t>paper</t>
+      <c r="A315" s="6" t="inlineStr">
+        <is>
+          <t>amenity staff</t>
         </is>
       </c>
       <c r="B315" s="4" t="inlineStr">
         <is>
-          <t>Office Supply</t>
-        </is>
-      </c>
+          <t>Staff Amenity</t>
+        </is>
+      </c>
+      <c r="C315" s="5" t="n"/>
     </row>
     <row r="316">
       <c r="A316" s="4" t="inlineStr">
         <is>
-          <t>printer</t>
+          <t>amenitystaff</t>
         </is>
       </c>
       <c r="B316" s="4" t="inlineStr">
         <is>
-          <t>Office Supply</t>
-        </is>
-      </c>
+          <t>Staff Amenity</t>
+        </is>
+      </c>
+      <c r="C316" s="5" t="n"/>
     </row>
     <row r="317">
       <c r="A317" s="4" t="inlineStr">
         <is>
-          <t>toner</t>
+          <t>staff amenity</t>
         </is>
       </c>
       <c r="B317" s="4" t="inlineStr">
         <is>
-          <t>Office Supply</t>
-        </is>
-      </c>
+          <t>Staff Amenity</t>
+        </is>
+      </c>
+      <c r="C317" s="5" t="n"/>
     </row>
     <row r="318">
       <c r="A318" s="4" t="inlineStr">
         <is>
-          <t>วัสดุสำนักงาน</t>
+          <t>staffamenity</t>
         </is>
       </c>
       <c r="B318" s="4" t="inlineStr">
         <is>
-          <t>Office Supply</t>
-        </is>
-      </c>
+          <t>Staff Amenity</t>
+        </is>
+      </c>
+      <c r="C318" s="5" t="n"/>
     </row>
     <row r="319">
       <c r="A319" s="3" t="inlineStr">
         <is>
-          <t>── Insurance ──</t>
-        </is>
-      </c>
-      <c r="B319" s="3" t="inlineStr"/>
-      <c r="C319" s="3" t="inlineStr"/>
+          <t>── Telephone ──</t>
+        </is>
+      </c>
+      <c r="B319" s="6" t="n"/>
+      <c r="C319" s="3" t="n"/>
     </row>
     <row r="320">
-      <c r="A320" s="4" t="inlineStr">
-        <is>
-          <t>insurance</t>
+      <c r="A320" s="6" t="inlineStr">
+        <is>
+          <t>telephone</t>
         </is>
       </c>
       <c r="B320" s="4" t="inlineStr">
         <is>
-          <t>Insurance</t>
-        </is>
-      </c>
+          <t>Telephone</t>
+        </is>
+      </c>
+      <c r="C320" s="5" t="n"/>
     </row>
     <row r="321">
-      <c r="A321" s="4" t="inlineStr">
-        <is>
-          <t>insure</t>
-        </is>
-      </c>
-      <c r="B321" s="4" t="inlineStr">
-        <is>
-          <t>Insurance</t>
-        </is>
-      </c>
+      <c r="A321" s="3" t="inlineStr">
+        <is>
+          <t>── Transportation ──</t>
+        </is>
+      </c>
+      <c r="B321" s="4" t="n"/>
+      <c r="C321" s="5" t="n"/>
     </row>
     <row r="322">
       <c r="A322" s="4" t="inlineStr">
         <is>
-          <t>premium</t>
+          <t>transportation</t>
         </is>
       </c>
       <c r="B322" s="4" t="inlineStr">
         <is>
-          <t>Insurance</t>
-        </is>
-      </c>
+          <t>Transportation</t>
+        </is>
+      </c>
+      <c r="C322" s="5" t="n"/>
     </row>
     <row r="323">
-      <c r="A323" s="4" t="inlineStr">
-        <is>
-          <t>coverage</t>
-        </is>
-      </c>
-      <c r="B323" s="4" t="inlineStr">
-        <is>
-          <t>Insurance</t>
-        </is>
-      </c>
+      <c r="A323" s="3" t="inlineStr">
+        <is>
+          <t>── Variable Cost Ratio ──</t>
+        </is>
+      </c>
+      <c r="B323" s="4" t="n"/>
+      <c r="C323" s="5" t="n"/>
     </row>
     <row r="324">
       <c r="A324" s="4" t="inlineStr">
         <is>
-          <t>property insurance</t>
+          <t>ratio cost variable</t>
         </is>
       </c>
       <c r="B324" s="4" t="inlineStr">
         <is>
-          <t>Insurance</t>
-        </is>
-      </c>
+          <t>Variable Cost Ratio</t>
+        </is>
+      </c>
+      <c r="C324" s="5" t="n"/>
     </row>
     <row r="325">
-      <c r="A325" s="4" t="inlineStr">
-        <is>
-          <t>fire insurance</t>
+      <c r="A325" s="6" t="inlineStr">
+        <is>
+          <t>ratiocostvariable</t>
         </is>
       </c>
       <c r="B325" s="4" t="inlineStr">
         <is>
-          <t>Insurance</t>
-        </is>
-      </c>
+          <t>Variable Cost Ratio</t>
+        </is>
+      </c>
+      <c r="C325" s="5" t="n"/>
     </row>
     <row r="326">
       <c r="A326" s="4" t="inlineStr">
         <is>
-          <t>liability insurance</t>
+          <t>variable cost ratio</t>
         </is>
       </c>
       <c r="B326" s="4" t="inlineStr">
         <is>
-          <t>Insurance</t>
-        </is>
-      </c>
+          <t>Variable Cost Ratio</t>
+        </is>
+      </c>
+      <c r="C326" s="5" t="n"/>
     </row>
     <row r="327">
       <c r="A327" s="4" t="inlineStr">
         <is>
-          <t>ค่าประกันภัย</t>
+          <t>variablecostratio</t>
         </is>
       </c>
       <c r="B327" s="4" t="inlineStr">
         <is>
-          <t>Insurance</t>
-        </is>
-      </c>
+          <t>Variable Cost Ratio</t>
+        </is>
+      </c>
+      <c r="C327" s="5" t="n"/>
     </row>
     <row r="328">
       <c r="A328" s="3" t="inlineStr">
         <is>
-          <t>── Security ──</t>
-        </is>
-      </c>
-      <c r="B328" s="3" t="inlineStr"/>
-      <c r="C328" s="3" t="inlineStr"/>
+          <t>── Variable Cost Total ──</t>
+        </is>
+      </c>
+      <c r="B328" s="6" t="n"/>
+      <c r="C328" s="3" t="n"/>
     </row>
     <row r="329">
       <c r="A329" s="4" t="inlineStr">
         <is>
-          <t>security</t>
+          <t>total cost variable</t>
         </is>
       </c>
       <c r="B329" s="4" t="inlineStr">
         <is>
-          <t>Security</t>
-        </is>
-      </c>
+          <t>Variable Cost Total</t>
+        </is>
+      </c>
+      <c r="C329" s="5" t="n"/>
     </row>
     <row r="330">
-      <c r="A330" s="4" t="inlineStr">
-        <is>
-          <t>guard</t>
+      <c r="A330" s="6" t="inlineStr">
+        <is>
+          <t>totalcostvariable</t>
         </is>
       </c>
       <c r="B330" s="4" t="inlineStr">
         <is>
-          <t>Security</t>
-        </is>
-      </c>
+          <t>Variable Cost Total</t>
+        </is>
+      </c>
+      <c r="C330" s="5" t="n"/>
     </row>
     <row r="331">
       <c r="A331" s="4" t="inlineStr">
         <is>
-          <t>security guard</t>
+          <t>variable cost</t>
         </is>
       </c>
       <c r="B331" s="4" t="inlineStr">
         <is>
-          <t>Security</t>
-        </is>
-      </c>
+          <t>Variable Cost Total</t>
+        </is>
+      </c>
+      <c r="C331" s="5" t="n"/>
     </row>
     <row r="332">
       <c r="A332" s="4" t="inlineStr">
         <is>
-          <t>cctv</t>
+          <t>variable cost total</t>
         </is>
       </c>
       <c r="B332" s="4" t="inlineStr">
         <is>
-          <t>Security</t>
-        </is>
-      </c>
+          <t>Variable Cost Total</t>
+        </is>
+      </c>
+      <c r="C332" s="5" t="n"/>
     </row>
     <row r="333">
       <c r="A333" s="4" t="inlineStr">
         <is>
-          <t>surveillance</t>
+          <t>variablecost</t>
         </is>
       </c>
       <c r="B333" s="4" t="inlineStr">
         <is>
-          <t>Security</t>
-        </is>
-      </c>
+          <t>Variable Cost Total</t>
+        </is>
+      </c>
+      <c r="C333" s="5" t="n"/>
     </row>
     <row r="334">
       <c r="A334" s="4" t="inlineStr">
         <is>
-          <t>รักษาความปลอดภัย</t>
+          <t>variablecosttotal</t>
         </is>
       </c>
       <c r="B334" s="4" t="inlineStr">
         <is>
-          <t>Security</t>
-        </is>
-      </c>
+          <t>Variable Cost Total</t>
+        </is>
+      </c>
+      <c r="C334" s="5" t="n"/>
     </row>
     <row r="335">
       <c r="A335" s="3" t="inlineStr">
         <is>
-          <t>── Cleaning Expense ──</t>
-        </is>
-      </c>
-      <c r="B335" s="3" t="inlineStr"/>
-      <c r="C335" s="3" t="inlineStr"/>
+          <t>── Welfare ──</t>
+        </is>
+      </c>
+      <c r="B335" s="3" t="n"/>
+      <c r="C335" s="3" t="n"/>
     </row>
     <row r="336">
       <c r="A336" s="4" t="inlineStr">
         <is>
-          <t>cleaning</t>
+          <t>welfare</t>
         </is>
       </c>
       <c r="B336" s="4" t="inlineStr">
         <is>
-          <t>Cleaning Expense</t>
-        </is>
-      </c>
+          <t>Welfare</t>
+        </is>
+      </c>
+      <c r="C336" s="5" t="n"/>
     </row>
     <row r="337">
-      <c r="A337" s="4" t="inlineStr">
-        <is>
-          <t>clean</t>
-        </is>
-      </c>
-      <c r="B337" s="4" t="inlineStr">
-        <is>
-          <t>Cleaning Expense</t>
-        </is>
-      </c>
+      <c r="A337" s="3" t="inlineStr">
+        <is>
+          <t>── Workmen's compensation ──</t>
+        </is>
+      </c>
+      <c r="B337" s="4" t="n"/>
+      <c r="C337" s="5" t="n"/>
     </row>
     <row r="338">
       <c r="A338" s="4" t="inlineStr">
         <is>
-          <t>janitorial</t>
+          <t>compensation s workmen</t>
         </is>
       </c>
       <c r="B338" s="4" t="inlineStr">
         <is>
-          <t>Cleaning Expense</t>
-        </is>
-      </c>
+          <t>Workmen's compensation</t>
+        </is>
+      </c>
+      <c r="C338" s="5" t="n"/>
     </row>
     <row r="339">
-      <c r="A339" s="4" t="inlineStr">
-        <is>
-          <t>housekeeping</t>
+      <c r="A339" s="6" t="inlineStr">
+        <is>
+          <t>compensationsworkmen</t>
         </is>
       </c>
       <c r="B339" s="4" t="inlineStr">
         <is>
-          <t>Cleaning Expense</t>
-        </is>
-      </c>
+          <t>Workmen's compensation</t>
+        </is>
+      </c>
+      <c r="C339" s="5" t="n"/>
     </row>
     <row r="340">
       <c r="A340" s="4" t="inlineStr">
         <is>
-          <t>sanitation</t>
+          <t>s compensation</t>
         </is>
       </c>
       <c r="B340" s="4" t="inlineStr">
         <is>
-          <t>Cleaning Expense</t>
-        </is>
-      </c>
+          <t>Workmen's compensation</t>
+        </is>
+      </c>
+      <c r="C340" s="5" t="n"/>
     </row>
     <row r="341">
       <c r="A341" s="4" t="inlineStr">
         <is>
-          <t>ค่าทำความสะอาด</t>
+          <t>scompensation</t>
         </is>
       </c>
       <c r="B341" s="4" t="inlineStr">
         <is>
-          <t>Cleaning Expense</t>
-        </is>
-      </c>
+          <t>Workmen's compensation</t>
+        </is>
+      </c>
+      <c r="C341" s="5" t="n"/>
     </row>
     <row r="342">
-      <c r="A342" s="3" t="inlineStr">
-        <is>
-          <t>── Signboard Tax ──</t>
-        </is>
-      </c>
-      <c r="B342" s="3" t="inlineStr"/>
-      <c r="C342" s="3" t="inlineStr"/>
+      <c r="A342" s="6" t="inlineStr">
+        <is>
+          <t>workmen s</t>
+        </is>
+      </c>
+      <c r="B342" s="6" t="inlineStr">
+        <is>
+          <t>Workmen's compensation</t>
+        </is>
+      </c>
+      <c r="C342" s="3" t="n"/>
     </row>
     <row r="343">
       <c r="A343" s="4" t="inlineStr">
         <is>
-          <t>signboard</t>
+          <t>workmen s compensation</t>
         </is>
       </c>
       <c r="B343" s="4" t="inlineStr">
         <is>
-          <t>Signboard Tax</t>
-        </is>
-      </c>
+          <t>Workmen's compensation</t>
+        </is>
+      </c>
+      <c r="C343" s="5" t="n"/>
     </row>
     <row r="344">
       <c r="A344" s="4" t="inlineStr">
         <is>
-          <t>signboard tax</t>
+          <t>workmen's compensation</t>
         </is>
       </c>
       <c r="B344" s="4" t="inlineStr">
         <is>
-          <t>Signboard Tax</t>
-        </is>
-      </c>
+          <t>Workmen's compensation</t>
+        </is>
+      </c>
+      <c r="C344" s="5" t="n"/>
     </row>
     <row r="345">
       <c r="A345" s="4" t="inlineStr">
         <is>
-          <t>sign tax</t>
+          <t>workmens</t>
         </is>
       </c>
       <c r="B345" s="4" t="inlineStr">
         <is>
-          <t>Signboard Tax</t>
-        </is>
-      </c>
+          <t>Workmen's compensation</t>
+        </is>
+      </c>
+      <c r="C345" s="5" t="n"/>
     </row>
     <row r="346">
-      <c r="A346" s="3" t="inlineStr">
-        <is>
-          <t>── Land &amp; Building TAX ──</t>
-        </is>
-      </c>
-      <c r="B346" s="3" t="inlineStr"/>
-      <c r="C346" s="3" t="inlineStr"/>
+      <c r="A346" s="6" t="inlineStr">
+        <is>
+          <t>workmenscompensation</t>
+        </is>
+      </c>
+      <c r="B346" s="6" t="inlineStr">
+        <is>
+          <t>Workmen's compensation</t>
+        </is>
+      </c>
+      <c r="C346" s="3" t="n"/>
     </row>
     <row r="347">
-      <c r="A347" s="4" t="inlineStr">
-        <is>
-          <t>land tax</t>
-        </is>
-      </c>
-      <c r="B347" s="4" t="inlineStr">
-        <is>
-          <t>Land &amp; Building TAX</t>
-        </is>
-      </c>
+      <c r="A347" s="3" t="n"/>
+      <c r="B347" s="4" t="n"/>
+      <c r="C347" s="5" t="n"/>
     </row>
     <row r="348">
-      <c r="A348" s="4" t="inlineStr">
-        <is>
-          <t>building tax</t>
-        </is>
-      </c>
-      <c r="B348" s="4" t="inlineStr">
-        <is>
-          <t>Land &amp; Building TAX</t>
-        </is>
-      </c>
+      <c r="A348" s="4" t="n"/>
+      <c r="B348" s="4" t="n"/>
+      <c r="C348" s="5" t="n"/>
     </row>
     <row r="349">
-      <c r="A349" s="4" t="inlineStr">
-        <is>
-          <t>property tax</t>
-        </is>
-      </c>
-      <c r="B349" s="4" t="inlineStr">
-        <is>
-          <t>Land &amp; Building TAX</t>
-        </is>
-      </c>
+      <c r="A349" s="4" t="n"/>
+      <c r="B349" s="4" t="n"/>
+      <c r="C349" s="5" t="n"/>
     </row>
     <row r="350">
-      <c r="A350" s="4" t="inlineStr">
-        <is>
-          <t>land &amp; building</t>
-        </is>
-      </c>
-      <c r="B350" s="4" t="inlineStr">
-        <is>
-          <t>Land &amp; Building TAX</t>
-        </is>
-      </c>
+      <c r="A350" s="4" t="n"/>
+      <c r="B350" s="4" t="n"/>
+      <c r="C350" s="5" t="n"/>
     </row>
     <row r="351">
-      <c r="A351" s="4" t="inlineStr">
-        <is>
-          <t>ภาษีที่ดิน</t>
-        </is>
-      </c>
-      <c r="B351" s="4" t="inlineStr">
-        <is>
-          <t>Land &amp; Building TAX</t>
-        </is>
-      </c>
+      <c r="A351" s="4" t="n"/>
+      <c r="B351" s="4" t="n"/>
+      <c r="C351" s="5" t="n"/>
     </row>
     <row r="352">
-      <c r="A352" s="3" t="inlineStr">
-        <is>
-          <t>── Common expense ──</t>
-        </is>
-      </c>
-      <c r="B352" s="3" t="inlineStr"/>
-      <c r="C352" s="3" t="inlineStr"/>
+      <c r="A352" s="6" t="n"/>
+      <c r="B352" s="6" t="n"/>
+      <c r="C352" s="3" t="n"/>
     </row>
     <row r="353">
-      <c r="A353" s="4" t="inlineStr">
-        <is>
-          <t>common expense</t>
-        </is>
-      </c>
-      <c r="B353" s="4" t="inlineStr">
-        <is>
-          <t>Common expense</t>
-        </is>
-      </c>
+      <c r="A353" s="4" t="n"/>
+      <c r="B353" s="4" t="n"/>
+      <c r="C353" s="5" t="n"/>
     </row>
     <row r="354">
-      <c r="A354" s="4" t="inlineStr">
-        <is>
-          <t>common area</t>
-        </is>
-      </c>
-      <c r="B354" s="4" t="inlineStr">
-        <is>
-          <t>Common expense</t>
-        </is>
-      </c>
+      <c r="A354" s="4" t="n"/>
+      <c r="B354" s="4" t="n"/>
+      <c r="C354" s="5" t="n"/>
     </row>
     <row r="355">
-      <c r="A355" s="4" t="inlineStr">
-        <is>
-          <t>common fee</t>
-        </is>
-      </c>
-      <c r="B355" s="4" t="inlineStr">
-        <is>
-          <t>Common expense</t>
-        </is>
-      </c>
+      <c r="A355" s="3" t="n"/>
+      <c r="B355" s="4" t="n"/>
+      <c r="C355" s="5" t="n"/>
     </row>
     <row r="356">
-      <c r="A356" s="4" t="inlineStr">
-        <is>
-          <t>condo fee</t>
-        </is>
-      </c>
-      <c r="B356" s="4" t="inlineStr">
-        <is>
-          <t>Common expense</t>
-        </is>
-      </c>
+      <c r="A356" s="4" t="n"/>
+      <c r="B356" s="4" t="n"/>
+      <c r="C356" s="5" t="n"/>
     </row>
     <row r="357">
-      <c r="A357" s="3" t="inlineStr">
-        <is>
-          <t>── Service Office ──</t>
-        </is>
-      </c>
-      <c r="B357" s="3" t="inlineStr"/>
-      <c r="C357" s="3" t="inlineStr"/>
+      <c r="A357" s="3" t="n"/>
+      <c r="B357" s="3" t="n"/>
+      <c r="C357" s="3" t="n"/>
     </row>
     <row r="358">
-      <c r="A358" s="4" t="inlineStr">
-        <is>
-          <t>service office</t>
-        </is>
-      </c>
-      <c r="B358" s="4" t="inlineStr">
-        <is>
-          <t>Service Office</t>
-        </is>
-      </c>
+      <c r="A358" s="4" t="n"/>
+      <c r="B358" s="4" t="n"/>
+      <c r="C358" s="5" t="n"/>
     </row>
     <row r="359">
-      <c r="A359" s="4" t="inlineStr">
-        <is>
-          <t>serviced office</t>
-        </is>
-      </c>
-      <c r="B359" s="4" t="inlineStr">
-        <is>
-          <t>Service Office</t>
-        </is>
-      </c>
+      <c r="A359" s="4" t="n"/>
+      <c r="B359" s="4" t="n"/>
+      <c r="C359" s="5" t="n"/>
     </row>
     <row r="360">
-      <c r="A360" s="4" t="inlineStr">
-        <is>
-          <t>co-working</t>
-        </is>
-      </c>
-      <c r="B360" s="4" t="inlineStr">
-        <is>
-          <t>Service Office</t>
-        </is>
-      </c>
+      <c r="A360" s="4" t="n"/>
+      <c r="B360" s="4" t="n"/>
+      <c r="C360" s="5" t="n"/>
     </row>
     <row r="361">
-      <c r="A361" s="3" t="inlineStr">
-        <is>
-          <t>── Office Equipment ──</t>
-        </is>
-      </c>
-      <c r="B361" s="3" t="inlineStr"/>
-      <c r="C361" s="3" t="inlineStr"/>
+      <c r="A361" s="6" t="n"/>
+      <c r="B361" s="6" t="n"/>
+      <c r="C361" s="3" t="n"/>
     </row>
     <row r="362">
-      <c r="A362" s="4" t="inlineStr">
-        <is>
-          <t>office equipment</t>
-        </is>
-      </c>
-      <c r="B362" s="4" t="inlineStr">
-        <is>
-          <t>Office Equipment</t>
-        </is>
-      </c>
+      <c r="A362" s="4" t="n"/>
+      <c r="B362" s="4" t="n"/>
+      <c r="C362" s="5" t="n"/>
     </row>
     <row r="363">
-      <c r="A363" s="4" t="inlineStr">
-        <is>
-          <t>equipment</t>
-        </is>
-      </c>
-      <c r="B363" s="4" t="inlineStr">
-        <is>
-          <t>Office Equipment</t>
-        </is>
-      </c>
+      <c r="A363" s="4" t="n"/>
+      <c r="B363" s="4" t="n"/>
+      <c r="C363" s="5" t="n"/>
     </row>
     <row r="364">
-      <c r="A364" s="4" t="inlineStr">
-        <is>
-          <t>furniture</t>
-        </is>
-      </c>
-      <c r="B364" s="4" t="inlineStr">
-        <is>
-          <t>Office Equipment</t>
-        </is>
-      </c>
+      <c r="A364" s="4" t="n"/>
+      <c r="B364" s="4" t="n"/>
+      <c r="C364" s="5" t="n"/>
     </row>
     <row r="365">
-      <c r="A365" s="4" t="inlineStr">
-        <is>
-          <t>fixture</t>
-        </is>
-      </c>
-      <c r="B365" s="4" t="inlineStr">
-        <is>
-          <t>Office Equipment</t>
-        </is>
-      </c>
+      <c r="A365" s="4" t="n"/>
+      <c r="B365" s="4" t="n"/>
+      <c r="C365" s="5" t="n"/>
     </row>
     <row r="366">
-      <c r="A366" s="3" t="inlineStr">
-        <is>
-          <t>── Facility Expense ──</t>
-        </is>
-      </c>
-      <c r="B366" s="3" t="inlineStr"/>
-      <c r="C366" s="3" t="inlineStr"/>
+      <c r="A366" s="6" t="n"/>
+      <c r="B366" s="6" t="n"/>
+      <c r="C366" s="3" t="n"/>
     </row>
     <row r="367">
-      <c r="A367" s="4" t="inlineStr">
-        <is>
-          <t>facility</t>
-        </is>
-      </c>
-      <c r="B367" s="4" t="inlineStr">
-        <is>
-          <t>Facility Expense</t>
-        </is>
-      </c>
+      <c r="A367" s="4" t="n"/>
+      <c r="B367" s="4" t="n"/>
     </row>
     <row r="368">
-      <c r="A368" s="4" t="inlineStr">
-        <is>
-          <t>facility expense</t>
-        </is>
-      </c>
-      <c r="B368" s="4" t="inlineStr">
-        <is>
-          <t>Facility Expense</t>
-        </is>
-      </c>
+      <c r="A368" s="4" t="n"/>
+      <c r="B368" s="4" t="n"/>
     </row>
     <row r="369">
-      <c r="A369" s="4" t="inlineStr">
-        <is>
-          <t>facility cost</t>
-        </is>
-      </c>
-      <c r="B369" s="4" t="inlineStr">
-        <is>
-          <t>Facility Expense</t>
-        </is>
-      </c>
+      <c r="A369" s="4" t="n"/>
+      <c r="B369" s="4" t="n"/>
     </row>
     <row r="370">
-      <c r="A370" s="4" t="inlineStr">
-        <is>
-          <t>ค่าสาธารณูปโภค</t>
-        </is>
-      </c>
-      <c r="B370" s="4" t="inlineStr">
-        <is>
-          <t>Facility Expense</t>
-        </is>
-      </c>
+      <c r="A370" s="4" t="n"/>
+      <c r="B370" s="4" t="n"/>
     </row>
     <row r="371">
-      <c r="A371" s="3" t="inlineStr">
-        <is>
-          <t>── Staff Amenity ──</t>
-        </is>
-      </c>
-      <c r="B371" s="3" t="inlineStr"/>
-      <c r="C371" s="3" t="inlineStr"/>
+      <c r="A371" s="3" t="n"/>
+      <c r="B371" s="3" t="n"/>
+      <c r="C371" s="3" t="n"/>
     </row>
     <row r="372">
-      <c r="A372" s="4" t="inlineStr">
-        <is>
-          <t>staff amenity</t>
-        </is>
-      </c>
-      <c r="B372" s="4" t="inlineStr">
-        <is>
-          <t>Staff Amenity</t>
-        </is>
-      </c>
+      <c r="A372" s="4" t="n"/>
+      <c r="B372" s="4" t="n"/>
     </row>
     <row r="373">
-      <c r="A373" s="4" t="inlineStr">
-        <is>
-          <t>amenity</t>
-        </is>
-      </c>
-      <c r="B373" s="4" t="inlineStr">
-        <is>
-          <t>Staff Amenity</t>
-        </is>
-      </c>
+      <c r="A373" s="4" t="n"/>
+      <c r="B373" s="4" t="n"/>
     </row>
     <row r="374">
-      <c r="A374" s="4" t="inlineStr">
-        <is>
-          <t>amenities</t>
-        </is>
-      </c>
-      <c r="B374" s="4" t="inlineStr">
-        <is>
-          <t>Staff Amenity</t>
-        </is>
-      </c>
+      <c r="A374" s="4" t="n"/>
+      <c r="B374" s="4" t="n"/>
     </row>
     <row r="375">
-      <c r="A375" s="4" t="inlineStr">
-        <is>
-          <t>staff meal</t>
-        </is>
-      </c>
-      <c r="B375" s="4" t="inlineStr">
-        <is>
-          <t>Staff Amenity</t>
-        </is>
-      </c>
+      <c r="A375" s="4" t="n"/>
+      <c r="B375" s="4" t="n"/>
     </row>
     <row r="376">
-      <c r="A376" s="4" t="inlineStr">
-        <is>
-          <t>canteen</t>
-        </is>
-      </c>
-      <c r="B376" s="4" t="inlineStr">
-        <is>
-          <t>Staff Amenity</t>
-        </is>
-      </c>
+      <c r="A376" s="4" t="n"/>
+      <c r="B376" s="4" t="n"/>
     </row>
     <row r="377">
-      <c r="A377" s="3" t="inlineStr">
-        <is>
-          <t>── Personnel Expense ──</t>
-        </is>
-      </c>
-      <c r="B377" s="3" t="inlineStr"/>
-      <c r="C377" s="3" t="inlineStr"/>
+      <c r="A377" s="3" t="n"/>
+      <c r="B377" s="3" t="n"/>
+      <c r="C377" s="3" t="n"/>
     </row>
     <row r="378">
-      <c r="A378" s="4" t="inlineStr">
-        <is>
-          <t>personnel</t>
-        </is>
-      </c>
-      <c r="B378" s="4" t="inlineStr">
-        <is>
-          <t>Personnel Expense</t>
-        </is>
-      </c>
+      <c r="A378" s="4" t="n"/>
+      <c r="B378" s="4" t="n"/>
     </row>
     <row r="379">
-      <c r="A379" s="4" t="inlineStr">
-        <is>
-          <t>personnel expense</t>
-        </is>
-      </c>
-      <c r="B379" s="4" t="inlineStr">
-        <is>
-          <t>Personnel Expense</t>
-        </is>
-      </c>
+      <c r="A379" s="4" t="n"/>
+      <c r="B379" s="4" t="n"/>
     </row>
     <row r="380">
-      <c r="A380" s="4" t="inlineStr">
-        <is>
-          <t>hr cost</t>
-        </is>
-      </c>
-      <c r="B380" s="4" t="inlineStr">
-        <is>
-          <t>Personnel Expense</t>
-        </is>
-      </c>
+      <c r="A380" s="4" t="n"/>
+      <c r="B380" s="4" t="n"/>
     </row>
     <row r="381">
-      <c r="A381" s="4" t="inlineStr">
-        <is>
-          <t>hr expense</t>
-        </is>
-      </c>
-      <c r="B381" s="4" t="inlineStr">
-        <is>
-          <t>Personnel Expense</t>
-        </is>
-      </c>
+      <c r="A381" s="4" t="n"/>
+      <c r="B381" s="4" t="n"/>
     </row>
     <row r="382">
-      <c r="A382" s="4" t="inlineStr">
-        <is>
-          <t>recruitment</t>
-        </is>
-      </c>
-      <c r="B382" s="4" t="inlineStr">
-        <is>
-          <t>Personnel Expense</t>
-        </is>
-      </c>
+      <c r="A382" s="4" t="n"/>
+      <c r="B382" s="4" t="n"/>
     </row>
     <row r="383">
-      <c r="A383" s="4" t="inlineStr">
-        <is>
-          <t>hiring cost</t>
-        </is>
-      </c>
-      <c r="B383" s="4" t="inlineStr">
-        <is>
-          <t>Personnel Expense</t>
-        </is>
-      </c>
+      <c r="A383" s="4" t="n"/>
+      <c r="B383" s="4" t="n"/>
     </row>
     <row r="384">
-      <c r="A384" s="3" t="inlineStr">
-        <is>
-          <t>── CLAIM FROM CUSTOMER ──</t>
-        </is>
-      </c>
-      <c r="B384" s="3" t="inlineStr"/>
-      <c r="C384" s="3" t="inlineStr"/>
+      <c r="A384" s="3" t="n"/>
+      <c r="B384" s="3" t="n"/>
+      <c r="C384" s="3" t="n"/>
     </row>
     <row r="385">
-      <c r="A385" s="4" t="inlineStr">
-        <is>
-          <t>claim</t>
-        </is>
-      </c>
-      <c r="B385" s="4" t="inlineStr">
-        <is>
-          <t>CLAIM FROM CUSTOMER</t>
-        </is>
-      </c>
+      <c r="A385" s="4" t="n"/>
+      <c r="B385" s="4" t="n"/>
     </row>
     <row r="386">
-      <c r="A386" s="4" t="inlineStr">
-        <is>
-          <t>customer claim</t>
-        </is>
-      </c>
-      <c r="B386" s="4" t="inlineStr">
-        <is>
-          <t>CLAIM FROM CUSTOMER</t>
-        </is>
-      </c>
+      <c r="A386" s="4" t="n"/>
+      <c r="B386" s="4" t="n"/>
     </row>
     <row r="387">
-      <c r="A387" s="4" t="inlineStr">
-        <is>
-          <t>claim from customer</t>
-        </is>
-      </c>
-      <c r="B387" s="4" t="inlineStr">
-        <is>
-          <t>CLAIM FROM CUSTOMER</t>
-        </is>
-      </c>
+      <c r="A387" s="4" t="n"/>
+      <c r="B387" s="4" t="n"/>
     </row>
     <row r="388">
-      <c r="A388" s="4" t="inlineStr">
-        <is>
-          <t>damage claim</t>
-        </is>
-      </c>
-      <c r="B388" s="4" t="inlineStr">
-        <is>
-          <t>CLAIM FROM CUSTOMER</t>
-        </is>
-      </c>
+      <c r="A388" s="4" t="n"/>
+      <c r="B388" s="4" t="n"/>
     </row>
     <row r="389">
-      <c r="A389" s="4" t="inlineStr">
-        <is>
-          <t>penalty</t>
-        </is>
-      </c>
-      <c r="B389" s="4" t="inlineStr">
-        <is>
-          <t>CLAIM FROM CUSTOMER</t>
-        </is>
-      </c>
+      <c r="A389" s="4" t="n"/>
+      <c r="B389" s="4" t="n"/>
     </row>
     <row r="390">
-      <c r="A390" s="4" t="inlineStr">
-        <is>
-          <t>deduction</t>
-        </is>
-      </c>
-      <c r="B390" s="4" t="inlineStr">
-        <is>
-          <t>CLAIM FROM CUSTOMER</t>
-        </is>
-      </c>
+      <c r="A390" s="4" t="n"/>
+      <c r="B390" s="4" t="n"/>
     </row>
     <row r="391">
-      <c r="A391" s="3" t="inlineStr">
-        <is>
-          <t>── Number of staff ──</t>
-        </is>
-      </c>
-      <c r="B391" s="3" t="inlineStr"/>
-      <c r="C391" s="3" t="inlineStr"/>
+      <c r="A391" s="3" t="n"/>
+      <c r="B391" s="3" t="n"/>
+      <c r="C391" s="3" t="n"/>
     </row>
     <row r="392">
-      <c r="A392" s="4" t="inlineStr">
-        <is>
-          <t>staff</t>
-        </is>
-      </c>
-      <c r="B392" s="4" t="inlineStr">
-        <is>
-          <t>Number of staff</t>
-        </is>
-      </c>
+      <c r="A392" s="4" t="n"/>
+      <c r="B392" s="4" t="n"/>
     </row>
     <row r="393">
-      <c r="A393" s="4" t="inlineStr">
-        <is>
-          <t>headcount</t>
-        </is>
-      </c>
-      <c r="B393" s="4" t="inlineStr">
-        <is>
-          <t>Number of staff</t>
-        </is>
-      </c>
+      <c r="A393" s="4" t="n"/>
+      <c r="B393" s="4" t="n"/>
     </row>
     <row r="394">
-      <c r="A394" s="4" t="inlineStr">
-        <is>
-          <t>employee</t>
-        </is>
-      </c>
-      <c r="B394" s="4" t="inlineStr">
-        <is>
-          <t>Number of staff</t>
-        </is>
-      </c>
+      <c r="A394" s="4" t="n"/>
+      <c r="B394" s="4" t="n"/>
     </row>
     <row r="395">
-      <c r="A395" s="4" t="inlineStr">
-        <is>
-          <t>employees</t>
-        </is>
-      </c>
-      <c r="B395" s="4" t="inlineStr">
-        <is>
-          <t>Number of staff</t>
-        </is>
-      </c>
+      <c r="A395" s="4" t="n"/>
+      <c r="B395" s="4" t="n"/>
     </row>
     <row r="396">
-      <c r="A396" s="4" t="inlineStr">
-        <is>
-          <t>hc</t>
-        </is>
-      </c>
-      <c r="B396" s="4" t="inlineStr">
-        <is>
-          <t>Number of staff</t>
-        </is>
-      </c>
+      <c r="A396" s="4" t="n"/>
+      <c r="B396" s="4" t="n"/>
     </row>
     <row r="397">
-      <c r="A397" s="4" t="inlineStr">
-        <is>
-          <t>head count</t>
-        </is>
-      </c>
-      <c r="B397" s="4" t="inlineStr">
-        <is>
-          <t>Number of staff</t>
-        </is>
-      </c>
+      <c r="A397" s="4" t="n"/>
+      <c r="B397" s="4" t="n"/>
     </row>
     <row r="398">
-      <c r="A398" s="4" t="inlineStr">
-        <is>
-          <t>number of staff</t>
-        </is>
-      </c>
-      <c r="B398" s="4" t="inlineStr">
-        <is>
-          <t>Number of staff</t>
-        </is>
-      </c>
+      <c r="A398" s="4" t="n"/>
+      <c r="B398" s="4" t="n"/>
     </row>
     <row r="399">
-      <c r="A399" s="4" t="inlineStr">
-        <is>
-          <t>workforce</t>
-        </is>
-      </c>
-      <c r="B399" s="4" t="inlineStr">
-        <is>
-          <t>Number of staff</t>
-        </is>
-      </c>
+      <c r="A399" s="4" t="n"/>
+      <c r="B399" s="4" t="n"/>
     </row>
     <row r="400">
-      <c r="A400" s="4" t="inlineStr">
-        <is>
-          <t>manpower count</t>
-        </is>
-      </c>
-      <c r="B400" s="4" t="inlineStr">
-        <is>
-          <t>Number of staff</t>
-        </is>
-      </c>
+      <c r="A400" s="4" t="n"/>
+      <c r="B400" s="4" t="n"/>
     </row>
     <row r="401">
-      <c r="A401" s="4" t="inlineStr">
-        <is>
-          <t>team size</t>
-        </is>
-      </c>
-      <c r="B401" s="4" t="inlineStr">
-        <is>
-          <t>Number of staff</t>
-        </is>
-      </c>
+      <c r="A401" s="4" t="n"/>
+      <c r="B401" s="4" t="n"/>
     </row>
     <row r="402">
-      <c r="A402" s="4" t="inlineStr">
-        <is>
-          <t>how many people</t>
-        </is>
-      </c>
-      <c r="B402" s="4" t="inlineStr">
-        <is>
-          <t>Number of staff</t>
-        </is>
-      </c>
+      <c r="A402" s="4" t="n"/>
+      <c r="B402" s="4" t="n"/>
     </row>
     <row r="403">
-      <c r="A403" s="4" t="inlineStr">
-        <is>
-          <t>how many staff</t>
-        </is>
-      </c>
-      <c r="B403" s="4" t="inlineStr">
-        <is>
-          <t>Number of staff</t>
-        </is>
-      </c>
+      <c r="A403" s="4" t="n"/>
+      <c r="B403" s="4" t="n"/>
     </row>
     <row r="404">
-      <c r="A404" s="4" t="inlineStr">
-        <is>
-          <t>how many employee</t>
-        </is>
-      </c>
-      <c r="B404" s="4" t="inlineStr">
-        <is>
-          <t>Number of staff</t>
-        </is>
-      </c>
+      <c r="A404" s="4" t="n"/>
+      <c r="B404" s="4" t="n"/>
     </row>
     <row r="405">
-      <c r="A405" s="4" t="inlineStr">
-        <is>
-          <t>จำนวนพนักงาน</t>
-        </is>
-      </c>
-      <c r="B405" s="4" t="inlineStr">
-        <is>
-          <t>Number of staff</t>
-        </is>
-      </c>
+      <c r="A405" s="4" t="n"/>
+      <c r="B405" s="4" t="n"/>
     </row>
     <row r="406">
-      <c r="A406" s="3" t="inlineStr">
-        <is>
-          <t>── Software License ──</t>
-        </is>
-      </c>
-      <c r="B406" s="3" t="inlineStr"/>
-      <c r="C406" s="3" t="inlineStr"/>
+      <c r="A406" s="3" t="n"/>
+      <c r="B406" s="3" t="n"/>
+      <c r="C406" s="3" t="n"/>
     </row>
     <row r="407">
-      <c r="A407" s="4" t="inlineStr">
-        <is>
-          <t>software</t>
-        </is>
-      </c>
-      <c r="B407" s="4" t="inlineStr">
-        <is>
-          <t>Software License</t>
-        </is>
-      </c>
+      <c r="A407" s="4" t="n"/>
+      <c r="B407" s="4" t="n"/>
     </row>
     <row r="408">
-      <c r="A408" s="4" t="inlineStr">
-        <is>
-          <t>license</t>
-        </is>
-      </c>
-      <c r="B408" s="4" t="inlineStr">
-        <is>
-          <t>Software License</t>
-        </is>
-      </c>
+      <c r="A408" s="4" t="n"/>
+      <c r="B408" s="4" t="n"/>
     </row>
     <row r="409">
-      <c r="A409" s="4" t="inlineStr">
-        <is>
-          <t>software license</t>
-        </is>
-      </c>
-      <c r="B409" s="4" t="inlineStr">
-        <is>
-          <t>Software License</t>
-        </is>
-      </c>
+      <c r="A409" s="4" t="n"/>
+      <c r="B409" s="4" t="n"/>
     </row>
     <row r="410">
-      <c r="A410" s="4" t="inlineStr">
-        <is>
-          <t>software cost</t>
-        </is>
-      </c>
-      <c r="B410" s="4" t="inlineStr">
-        <is>
-          <t>Software License</t>
-        </is>
-      </c>
+      <c r="A410" s="4" t="n"/>
+      <c r="B410" s="4" t="n"/>
     </row>
     <row r="411">
-      <c r="A411" s="4" t="inlineStr">
-        <is>
-          <t>it cost</t>
-        </is>
-      </c>
-      <c r="B411" s="4" t="inlineStr">
-        <is>
-          <t>Software License</t>
-        </is>
-      </c>
+      <c r="A411" s="4" t="n"/>
+      <c r="B411" s="4" t="n"/>
     </row>
     <row r="412">
-      <c r="A412" s="4" t="inlineStr">
-        <is>
-          <t>system cost</t>
-        </is>
-      </c>
-      <c r="B412" s="4" t="inlineStr">
-        <is>
-          <t>Software License</t>
-        </is>
-      </c>
+      <c r="A412" s="4" t="n"/>
+      <c r="B412" s="4" t="n"/>
     </row>
     <row r="413">
-      <c r="A413" s="4" t="inlineStr">
-        <is>
-          <t>subscription</t>
-        </is>
-      </c>
-      <c r="B413" s="4" t="inlineStr">
-        <is>
-          <t>Software License</t>
-        </is>
-      </c>
+      <c r="A413" s="4" t="n"/>
+      <c r="B413" s="4" t="n"/>
     </row>
     <row r="414">
-      <c r="A414" s="3" t="inlineStr">
-        <is>
-          <t>── Revenue per Head ──</t>
-        </is>
-      </c>
-      <c r="B414" s="3" t="inlineStr"/>
-      <c r="C414" s="3" t="inlineStr"/>
+      <c r="A414" s="3" t="n"/>
+      <c r="B414" s="3" t="n"/>
+      <c r="C414" s="3" t="n"/>
     </row>
     <row r="415">
-      <c r="A415" s="4" t="inlineStr">
-        <is>
-          <t>revenue per head</t>
-        </is>
-      </c>
-      <c r="B415" s="4" t="inlineStr">
-        <is>
-          <t>Revenue per Head</t>
-        </is>
-      </c>
+      <c r="A415" s="4" t="n"/>
+      <c r="B415" s="4" t="n"/>
     </row>
     <row r="416">
-      <c r="A416" s="4" t="inlineStr">
-        <is>
-          <t>rev per head</t>
-        </is>
-      </c>
-      <c r="B416" s="4" t="inlineStr">
-        <is>
-          <t>Revenue per Head</t>
-        </is>
-      </c>
+      <c r="A416" s="4" t="n"/>
+      <c r="B416" s="4" t="n"/>
     </row>
     <row r="417">
-      <c r="A417" s="4" t="inlineStr">
-        <is>
-          <t>revenue per employee</t>
-        </is>
-      </c>
-      <c r="B417" s="4" t="inlineStr">
-        <is>
-          <t>Revenue per Head</t>
-        </is>
-      </c>
+      <c r="A417" s="4" t="n"/>
+      <c r="B417" s="4" t="n"/>
     </row>
     <row r="418">
-      <c r="A418" s="4" t="inlineStr">
-        <is>
-          <t>productivity</t>
-        </is>
-      </c>
-      <c r="B418" s="4" t="inlineStr">
-        <is>
-          <t>Revenue per Head</t>
-        </is>
-      </c>
+      <c r="A418" s="4" t="n"/>
+      <c r="B418" s="4" t="n"/>
     </row>
     <row r="419">
-      <c r="A419" s="4" t="inlineStr">
-        <is>
-          <t>revenue per staff</t>
-        </is>
-      </c>
-      <c r="B419" s="4" t="inlineStr">
-        <is>
-          <t>Revenue per Head</t>
-        </is>
-      </c>
+      <c r="A419" s="4" t="n"/>
+      <c r="B419" s="4" t="n"/>
     </row>
     <row r="420">
-      <c r="A420" s="3" t="inlineStr">
-        <is>
-          <t>── Gross Profit Ratio ──</t>
-        </is>
-      </c>
-      <c r="B420" s="3" t="inlineStr"/>
-      <c r="C420" s="3" t="inlineStr"/>
+      <c r="A420" s="3" t="n"/>
+      <c r="B420" s="3" t="n"/>
+      <c r="C420" s="3" t="n"/>
     </row>
     <row r="421">
-      <c r="A421" s="4" t="inlineStr">
-        <is>
-          <t>gp ratio</t>
-        </is>
-      </c>
-      <c r="B421" s="4" t="inlineStr">
-        <is>
-          <t>Gross Profit Ratio</t>
-        </is>
-      </c>
+      <c r="A421" s="4" t="n"/>
+      <c r="B421" s="4" t="n"/>
     </row>
     <row r="422">
-      <c r="A422" s="4" t="inlineStr">
-        <is>
-          <t>gross profit ratio</t>
-        </is>
-      </c>
-      <c r="B422" s="4" t="inlineStr">
-        <is>
-          <t>Gross Profit Ratio</t>
-        </is>
-      </c>
+      <c r="A422" s="4" t="n"/>
+      <c r="B422" s="4" t="n"/>
     </row>
     <row r="423">
-      <c r="A423" s="4" t="inlineStr">
-        <is>
-          <t>gp%</t>
-        </is>
-      </c>
-      <c r="B423" s="4" t="inlineStr">
-        <is>
-          <t>Gross Profit Ratio</t>
-        </is>
-      </c>
+      <c r="A423" s="4" t="n"/>
+      <c r="B423" s="4" t="n"/>
     </row>
     <row r="424">
-      <c r="A424" s="4" t="inlineStr">
-        <is>
-          <t>gross margin %</t>
-        </is>
-      </c>
-      <c r="B424" s="4" t="inlineStr">
-        <is>
-          <t>Gross Profit Ratio</t>
-        </is>
-      </c>
+      <c r="A424" s="4" t="n"/>
+      <c r="B424" s="4" t="n"/>
     </row>
     <row r="425">
-      <c r="A425" s="4" t="inlineStr">
-        <is>
-          <t>gross profit percentage</t>
-        </is>
-      </c>
-      <c r="B425" s="4" t="inlineStr">
-        <is>
-          <t>Gross Profit Ratio</t>
-        </is>
-      </c>
+      <c r="A425" s="4" t="n"/>
+      <c r="B425" s="4" t="n"/>
     </row>
     <row r="426">
-      <c r="A426" s="4" t="inlineStr">
-        <is>
-          <t>profit margin</t>
-        </is>
-      </c>
-      <c r="B426" s="4" t="inlineStr">
-        <is>
-          <t>Gross Profit Ratio</t>
-        </is>
-      </c>
+      <c r="A426" s="4" t="n"/>
+      <c r="B426" s="4" t="n"/>
     </row>
     <row r="427">
-      <c r="A427" s="3" t="inlineStr">
-        <is>
-          <t>── Operating Profit Ratio ──</t>
-        </is>
-      </c>
-      <c r="B427" s="3" t="inlineStr"/>
-      <c r="C427" s="3" t="inlineStr"/>
+      <c r="A427" s="3" t="n"/>
+      <c r="B427" s="3" t="n"/>
+      <c r="C427" s="3" t="n"/>
     </row>
     <row r="428">
-      <c r="A428" s="4" t="inlineStr">
-        <is>
-          <t>op ratio</t>
-        </is>
-      </c>
-      <c r="B428" s="4" t="inlineStr">
-        <is>
-          <t>Operating Profit Ratio</t>
-        </is>
-      </c>
+      <c r="A428" s="4" t="n"/>
+      <c r="B428" s="4" t="n"/>
     </row>
     <row r="429">
-      <c r="A429" s="4" t="inlineStr">
-        <is>
-          <t>operating profit ratio</t>
-        </is>
-      </c>
-      <c r="B429" s="4" t="inlineStr">
-        <is>
-          <t>Operating Profit Ratio</t>
-        </is>
-      </c>
+      <c r="A429" s="4" t="n"/>
+      <c r="B429" s="4" t="n"/>
     </row>
     <row r="430">
-      <c r="A430" s="4" t="inlineStr">
-        <is>
-          <t>op%</t>
-        </is>
-      </c>
-      <c r="B430" s="4" t="inlineStr">
-        <is>
-          <t>Operating Profit Ratio</t>
-        </is>
-      </c>
+      <c r="A430" s="4" t="n"/>
+      <c r="B430" s="4" t="n"/>
     </row>
     <row r="431">
-      <c r="A431" s="4" t="inlineStr">
-        <is>
-          <t>net margin</t>
-        </is>
-      </c>
-      <c r="B431" s="4" t="inlineStr">
-        <is>
-          <t>Operating Profit Ratio</t>
-        </is>
-      </c>
+      <c r="A431" s="4" t="n"/>
+      <c r="B431" s="4" t="n"/>
     </row>
     <row r="432">
-      <c r="A432" s="4" t="inlineStr">
-        <is>
-          <t>operating margin</t>
-        </is>
-      </c>
-      <c r="B432" s="4" t="inlineStr">
-        <is>
-          <t>Operating Profit Ratio</t>
-        </is>
-      </c>
+      <c r="A432" s="4" t="n"/>
+      <c r="B432" s="4" t="n"/>
     </row>
     <row r="433">
-      <c r="A433" s="4" t="inlineStr">
-        <is>
-          <t>net profit ratio</t>
-        </is>
-      </c>
-      <c r="B433" s="4" t="inlineStr">
-        <is>
-          <t>Operating Profit Ratio</t>
-        </is>
-      </c>
+      <c r="A433" s="4" t="n"/>
+      <c r="B433" s="4" t="n"/>
     </row>
     <row r="434">
-      <c r="A434" s="3" t="inlineStr">
-        <is>
-          <t>── Variable Cost Ratio ──</t>
-        </is>
-      </c>
-      <c r="B434" s="3" t="inlineStr"/>
-      <c r="C434" s="3" t="inlineStr"/>
+      <c r="A434" s="3" t="n"/>
+      <c r="B434" s="3" t="n"/>
+      <c r="C434" s="3" t="n"/>
     </row>
     <row r="435">
-      <c r="A435" s="4" t="inlineStr">
-        <is>
-          <t>variable cost ratio</t>
-        </is>
-      </c>
-      <c r="B435" s="4" t="inlineStr">
-        <is>
-          <t>Variable Cost Ratio</t>
-        </is>
-      </c>
+      <c r="A435" s="4" t="n"/>
+      <c r="B435" s="4" t="n"/>
     </row>
     <row r="436">
-      <c r="A436" s="4" t="inlineStr">
-        <is>
-          <t>variable ratio</t>
-        </is>
-      </c>
-      <c r="B436" s="4" t="inlineStr">
-        <is>
-          <t>Variable Cost Ratio</t>
-        </is>
-      </c>
+      <c r="A436" s="4" t="n"/>
+      <c r="B436" s="4" t="n"/>
     </row>
     <row r="437">
-      <c r="A437" s="4" t="inlineStr">
-        <is>
-          <t>vcr</t>
-        </is>
-      </c>
-      <c r="B437" s="4" t="inlineStr">
-        <is>
-          <t>Variable Cost Ratio</t>
-        </is>
-      </c>
+      <c r="A437" s="4" t="n"/>
+      <c r="B437" s="4" t="n"/>
     </row>
     <row r="438">
-      <c r="A438" s="3" t="inlineStr">
-        <is>
-          <t>── Fixed Cost Ratio ──</t>
-        </is>
-      </c>
-      <c r="B438" s="3" t="inlineStr"/>
-      <c r="C438" s="3" t="inlineStr"/>
+      <c r="A438" s="3" t="n"/>
+      <c r="B438" s="3" t="n"/>
+      <c r="C438" s="3" t="n"/>
     </row>
     <row r="439">
-      <c r="A439" s="4" t="inlineStr">
-        <is>
-          <t>fixed cost ratio</t>
-        </is>
-      </c>
-      <c r="B439" s="4" t="inlineStr">
-        <is>
-          <t>Fixed Cost Ratio</t>
-        </is>
-      </c>
+      <c r="A439" s="4" t="n"/>
+      <c r="B439" s="4" t="n"/>
     </row>
     <row r="440">
-      <c r="A440" s="4" t="inlineStr">
-        <is>
-          <t>fixed ratio</t>
-        </is>
-      </c>
-      <c r="B440" s="4" t="inlineStr">
-        <is>
-          <t>Fixed Cost Ratio</t>
-        </is>
-      </c>
+      <c r="A440" s="4" t="n"/>
+      <c r="B440" s="4" t="n"/>
     </row>
     <row r="441">
-      <c r="A441" s="4" t="inlineStr">
-        <is>
-          <t>fcr</t>
-        </is>
-      </c>
-      <c r="B441" s="4" t="inlineStr">
-        <is>
-          <t>Fixed Cost Ratio</t>
-        </is>
-      </c>
+      <c r="A441" s="4" t="n"/>
+      <c r="B441" s="4" t="n"/>
     </row>
     <row r="442">
-      <c r="A442" s="3" t="inlineStr">
-        <is>
-          <t>── Fixed Cost Efficiency ──</t>
-        </is>
-      </c>
-      <c r="B442" s="3" t="inlineStr"/>
-      <c r="C442" s="3" t="inlineStr"/>
+      <c r="A442" s="3" t="n"/>
+      <c r="B442" s="3" t="n"/>
+      <c r="C442" s="3" t="n"/>
     </row>
     <row r="443">
-      <c r="A443" s="4" t="inlineStr">
-        <is>
-          <t>fixed cost efficiency</t>
-        </is>
-      </c>
-      <c r="B443" s="4" t="inlineStr">
-        <is>
-          <t>Fixed Cost Efficiency</t>
-        </is>
-      </c>
+      <c r="A443" s="4" t="n"/>
+      <c r="B443" s="4" t="n"/>
     </row>
     <row r="444">
-      <c r="A444" s="4" t="inlineStr">
-        <is>
-          <t>efficiency</t>
-        </is>
-      </c>
-      <c r="B444" s="4" t="inlineStr">
-        <is>
-          <t>Fixed Cost Efficiency</t>
-        </is>
-      </c>
+      <c r="A444" s="4" t="n"/>
+      <c r="B444" s="4" t="n"/>
     </row>
     <row r="445">
-      <c r="A445" s="4" t="inlineStr">
-        <is>
-          <t>fce</t>
-        </is>
-      </c>
-      <c r="B445" s="4" t="inlineStr">
-        <is>
-          <t>Fixed Cost Efficiency</t>
-        </is>
-      </c>
+      <c r="A445" s="4" t="n"/>
+      <c r="B445" s="4" t="n"/>
     </row>
     <row r="446">
-      <c r="A446" s="3" t="inlineStr">
-        <is>
-          <t>── Direct Labor Ratio ──</t>
-        </is>
-      </c>
-      <c r="B446" s="3" t="inlineStr"/>
-      <c r="C446" s="3" t="inlineStr"/>
+      <c r="A446" s="3" t="n"/>
+      <c r="B446" s="3" t="n"/>
+      <c r="C446" s="3" t="n"/>
     </row>
     <row r="447">
-      <c r="A447" s="4" t="inlineStr">
-        <is>
-          <t>labor ratio</t>
-        </is>
-      </c>
-      <c r="B447" s="4" t="inlineStr">
-        <is>
-          <t>Direct Labor Ratio</t>
-        </is>
-      </c>
+      <c r="A447" s="4" t="n"/>
+      <c r="B447" s="4" t="n"/>
     </row>
     <row r="448">
-      <c r="A448" s="4" t="inlineStr">
-        <is>
-          <t>direct labor ratio</t>
-        </is>
-      </c>
-      <c r="B448" s="4" t="inlineStr">
-        <is>
-          <t>Direct Labor Ratio</t>
-        </is>
-      </c>
+      <c r="A448" s="4" t="n"/>
+      <c r="B448" s="4" t="n"/>
     </row>
     <row r="449">
-      <c r="A449" s="4" t="inlineStr">
-        <is>
-          <t>dlr</t>
-        </is>
-      </c>
-      <c r="B449" s="4" t="inlineStr">
-        <is>
-          <t>Direct Labor Ratio</t>
-        </is>
-      </c>
+      <c r="A449" s="4" t="n"/>
+      <c r="B449" s="4" t="n"/>
     </row>
     <row r="450">
-      <c r="A450" s="4" t="inlineStr">
-        <is>
-          <t>labor %</t>
-        </is>
-      </c>
-      <c r="B450" s="4" t="inlineStr">
-        <is>
-          <t>Direct Labor Ratio</t>
-        </is>
-      </c>
+      <c r="A450" s="4" t="n"/>
+      <c r="B450" s="4" t="n"/>
     </row>
     <row r="451">
-      <c r="A451" s="3" t="inlineStr">
-        <is>
-          <t>── Direct Material Ratio ──</t>
-        </is>
-      </c>
-      <c r="B451" s="3" t="inlineStr"/>
-      <c r="C451" s="3" t="inlineStr"/>
+      <c r="A451" s="3" t="n"/>
+      <c r="B451" s="3" t="n"/>
+      <c r="C451" s="3" t="n"/>
     </row>
     <row r="452">
-      <c r="A452" s="4" t="inlineStr">
-        <is>
-          <t>material ratio</t>
-        </is>
-      </c>
-      <c r="B452" s="4" t="inlineStr">
-        <is>
-          <t>Direct Material Ratio</t>
-        </is>
-      </c>
+      <c r="A452" s="4" t="n"/>
+      <c r="B452" s="4" t="n"/>
     </row>
     <row r="453">
-      <c r="A453" s="4" t="inlineStr">
-        <is>
-          <t>direct material ratio</t>
-        </is>
-      </c>
-      <c r="B453" s="4" t="inlineStr">
-        <is>
-          <t>Direct Material Ratio</t>
-        </is>
-      </c>
+      <c r="A453" s="4" t="n"/>
+      <c r="B453" s="4" t="n"/>
     </row>
     <row r="454">
-      <c r="A454" s="4" t="inlineStr">
-        <is>
-          <t>dmr</t>
-        </is>
-      </c>
-      <c r="B454" s="4" t="inlineStr">
-        <is>
-          <t>Direct Material Ratio</t>
-        </is>
-      </c>
+      <c r="A454" s="4" t="n"/>
+      <c r="B454" s="4" t="n"/>
     </row>
     <row r="455">
-      <c r="A455" s="4" t="inlineStr">
-        <is>
-          <t>material %</t>
-        </is>
-      </c>
-      <c r="B455" s="4" t="inlineStr">
-        <is>
-          <t>Direct Material Ratio</t>
-        </is>
-      </c>
+      <c r="A455" s="4" t="n"/>
+      <c r="B455" s="4" t="n"/>
     </row>
     <row r="456">
-      <c r="A456" s="3" t="inlineStr">
-        <is>
-          <t>── Outsource Labor Ratio ──</t>
-        </is>
-      </c>
-      <c r="B456" s="3" t="inlineStr"/>
-      <c r="C456" s="3" t="inlineStr"/>
+      <c r="A456" s="3" t="n"/>
+      <c r="B456" s="3" t="n"/>
+      <c r="C456" s="3" t="n"/>
     </row>
     <row r="457">
-      <c r="A457" s="4" t="inlineStr">
-        <is>
-          <t>outsource ratio</t>
-        </is>
-      </c>
-      <c r="B457" s="4" t="inlineStr">
-        <is>
-          <t>Outsource Labor Ratio</t>
-        </is>
-      </c>
+      <c r="A457" s="4" t="n"/>
+      <c r="B457" s="4" t="n"/>
     </row>
     <row r="458">
-      <c r="A458" s="4" t="inlineStr">
-        <is>
-          <t>outsource labor ratio</t>
-        </is>
-      </c>
-      <c r="B458" s="4" t="inlineStr">
-        <is>
-          <t>Outsource Labor Ratio</t>
-        </is>
-      </c>
+      <c r="A458" s="4" t="n"/>
+      <c r="B458" s="4" t="n"/>
     </row>
     <row r="459">
-      <c r="A459" s="4" t="inlineStr">
-        <is>
-          <t>olr</t>
-        </is>
-      </c>
-      <c r="B459" s="4" t="inlineStr">
-        <is>
-          <t>Outsource Labor Ratio</t>
-        </is>
-      </c>
+      <c r="A459" s="4" t="n"/>
+      <c r="B459" s="4" t="n"/>
     </row>
     <row r="460">
-      <c r="A460" s="3" t="inlineStr">
-        <is>
-          <t>── Marginal Profit Ratio ──</t>
-        </is>
-      </c>
-      <c r="B460" s="3" t="inlineStr"/>
-      <c r="C460" s="3" t="inlineStr"/>
+      <c r="A460" s="3" t="n"/>
+      <c r="B460" s="3" t="n"/>
+      <c r="C460" s="3" t="n"/>
     </row>
     <row r="461">
-      <c r="A461" s="4" t="inlineStr">
-        <is>
-          <t>marginal profit ratio</t>
-        </is>
-      </c>
-      <c r="B461" s="4" t="inlineStr">
-        <is>
-          <t>Marginal Profit Ratio</t>
-        </is>
-      </c>
+      <c r="A461" s="4" t="n"/>
+      <c r="B461" s="4" t="n"/>
     </row>
     <row r="462">
-      <c r="A462" s="4" t="inlineStr">
-        <is>
-          <t>marginal ratio</t>
-        </is>
-      </c>
-      <c r="B462" s="4" t="inlineStr">
-        <is>
-          <t>Marginal Profit Ratio</t>
-        </is>
-      </c>
+      <c r="A462" s="4" t="n"/>
+      <c r="B462" s="4" t="n"/>
     </row>
     <row r="463">
-      <c r="A463" s="4" t="inlineStr">
-        <is>
-          <t>mpr</t>
-        </is>
-      </c>
-      <c r="B463" s="4" t="inlineStr">
-        <is>
-          <t>Marginal Profit Ratio</t>
-        </is>
-      </c>
+      <c r="A463" s="4" t="n"/>
+      <c r="B463" s="4" t="n"/>
     </row>
     <row r="464">
-      <c r="A464" s="4" t="inlineStr">
-        <is>
-          <t>contribution ratio</t>
-        </is>
-      </c>
-      <c r="B464" s="4" t="inlineStr">
-        <is>
-          <t>Marginal Profit Ratio</t>
-        </is>
-      </c>
+      <c r="A464" s="4" t="n"/>
+      <c r="B464" s="4" t="n"/>
     </row>
     <row r="465">
-      <c r="A465" s="4" t="inlineStr">
-        <is>
-          <t>contribution %</t>
-        </is>
-      </c>
-      <c r="B465" s="4" t="inlineStr">
-        <is>
-          <t>Marginal Profit Ratio</t>
-        </is>
-      </c>
+      <c r="A465" s="4" t="n"/>
+      <c r="B465" s="4" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/keyword.xlsx
+++ b/keyword.xlsx
@@ -6387,638 +6387,475 @@
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>acw</t>
+          <t>all site</t>
         </is>
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>ACW</t>
-        </is>
-      </c>
+          <t>All Site</t>
+        </is>
+      </c>
+      <c r="C3" s="5" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="4" t="inlineStr">
         <is>
-          <t>all site</t>
+          <t>cbr01</t>
         </is>
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>All Site</t>
-        </is>
-      </c>
+          <t>CBR01</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>bn20</t>
+          <t>cbr02</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>BN20</t>
-        </is>
-      </c>
+          <t>CBR02</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>bp1</t>
+          <t>cbr03</t>
         </is>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>BP1</t>
-        </is>
-      </c>
+          <t>CBR03</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>bpa</t>
+          <t>cbr04</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>BPA</t>
-        </is>
-      </c>
+          <t>CBR04</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>bpb</t>
+          <t>cbr05</t>
         </is>
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>BPB</t>
-        </is>
-      </c>
+          <t>CBR05</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>bpc</t>
+          <t>ccs01</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>BPC</t>
-        </is>
-      </c>
+          <t>CCS01</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>bpd</t>
+          <t>ccs02</t>
         </is>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>BPD</t>
-        </is>
-      </c>
+          <t>CCS02</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>cbr01</t>
+          <t>ccs03</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>CBR01</t>
-        </is>
-      </c>
+          <t>CCS03</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t>cbr02</t>
+          <t>otr01</t>
         </is>
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>CBR02</t>
-        </is>
-      </c>
+          <t>OTR01</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>cbr03</t>
+          <t>otr02</t>
         </is>
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>CBR03</t>
-        </is>
-      </c>
+          <t>OTR02</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
         <is>
-          <t>cbr04</t>
+          <t>pjr01</t>
         </is>
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>CBR04</t>
-        </is>
-      </c>
+          <t>PJR01</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>cbr05</t>
+          <t>ryn01</t>
         </is>
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>CBR05</t>
-        </is>
-      </c>
+          <t>RYN01</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
         <is>
-          <t>ccs01</t>
+          <t>ryn02</t>
         </is>
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>CCS01</t>
-        </is>
-      </c>
+          <t>RYN02</t>
+        </is>
+      </c>
+      <c r="C16" s="5" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>ccs02</t>
+          <t>ryn03</t>
         </is>
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>CCS02</t>
-        </is>
-      </c>
+          <t>RYN03</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
         <is>
-          <t>ccs03</t>
+          <t>ryn04</t>
         </is>
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>CCS03</t>
-        </is>
-      </c>
+          <t>RYN04</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>hmw</t>
+          <t>smk01</t>
         </is>
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>HMW</t>
-        </is>
-      </c>
+          <t>SMK01</t>
+        </is>
+      </c>
+      <c r="C19" s="5" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
         <is>
-          <t>neg</t>
+          <t>smk02</t>
         </is>
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>NeG</t>
-        </is>
-      </c>
+          <t>SMK02</t>
+        </is>
+      </c>
+      <c r="C20" s="5" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>smk03</t>
         </is>
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>OTHER</t>
-        </is>
-      </c>
+          <t>SMK03</t>
+        </is>
+      </c>
+      <c r="C21" s="5" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="4" t="inlineStr">
         <is>
-          <t>otr01</t>
+          <t>smk04</t>
         </is>
       </c>
       <c r="B22" s="4" t="inlineStr">
         <is>
-          <t>OTR01</t>
-        </is>
-      </c>
+          <t>SMK04</t>
+        </is>
+      </c>
+      <c r="C22" s="5" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="4" t="inlineStr">
         <is>
-          <t>otr02</t>
+          <t>smk05</t>
         </is>
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>OTR02</t>
-        </is>
-      </c>
+          <t>SMK05</t>
+        </is>
+      </c>
+      <c r="C23" s="5" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="4" t="inlineStr">
         <is>
-          <t>p304</t>
+          <t>smk06</t>
         </is>
       </c>
       <c r="B24" s="4" t="inlineStr">
         <is>
-          <t>P304</t>
-        </is>
-      </c>
+          <t>SMK06</t>
+        </is>
+      </c>
+      <c r="C24" s="5" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="4" t="inlineStr">
         <is>
-          <t>pjr01</t>
+          <t>smk07</t>
         </is>
       </c>
       <c r="B25" s="4" t="inlineStr">
         <is>
-          <t>PJR01</t>
-        </is>
-      </c>
+          <t>SMK07</t>
+        </is>
+      </c>
+      <c r="C25" s="5" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="4" t="inlineStr">
         <is>
-          <t>ppd</t>
+          <t>all site</t>
         </is>
       </c>
       <c r="B26" s="4" t="inlineStr">
         <is>
-          <t>PPD</t>
-        </is>
-      </c>
+          <t>All Site</t>
+        </is>
+      </c>
+      <c r="C26" s="5" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="4" t="inlineStr">
         <is>
-          <t>ryn01</t>
+          <t>all sites</t>
         </is>
       </c>
       <c r="B27" s="4" t="inlineStr">
         <is>
-          <t>RYN01</t>
-        </is>
-      </c>
+          <t>All Site</t>
+        </is>
+      </c>
+      <c r="C27" s="5" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="4" t="inlineStr">
         <is>
-          <t>ryn02</t>
+          <t>all</t>
         </is>
       </c>
       <c r="B28" s="4" t="inlineStr">
         <is>
-          <t>RYN02</t>
-        </is>
-      </c>
+          <t>All Site</t>
+        </is>
+      </c>
+      <c r="C28" s="5" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="4" t="inlineStr">
         <is>
-          <t>ryn03</t>
+          <t>company</t>
         </is>
       </c>
       <c r="B29" s="4" t="inlineStr">
         <is>
-          <t>RYN03</t>
-        </is>
-      </c>
+          <t>All Site</t>
+        </is>
+      </c>
+      <c r="C29" s="5" t="n"/>
     </row>
     <row r="30">
       <c r="A30" s="4" t="inlineStr">
         <is>
-          <t>ryn04</t>
+          <t>companywide</t>
         </is>
       </c>
       <c r="B30" s="4" t="inlineStr">
         <is>
-          <t>RYN04</t>
-        </is>
-      </c>
+          <t>All Site</t>
+        </is>
+      </c>
+      <c r="C30" s="5" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="4" t="inlineStr">
         <is>
-          <t>sdct</t>
+          <t>company wide</t>
         </is>
       </c>
       <c r="B31" s="4" t="inlineStr">
         <is>
-          <t>SDCT</t>
-        </is>
-      </c>
+          <t>All Site</t>
+        </is>
+      </c>
+      <c r="C31" s="5" t="n"/>
     </row>
     <row r="32">
-      <c r="A32" s="4" t="inlineStr">
-        <is>
-          <t>smk01</t>
-        </is>
-      </c>
-      <c r="B32" s="4" t="inlineStr">
-        <is>
-          <t>SMK01</t>
-        </is>
-      </c>
+      <c r="A32" s="4" t="n"/>
+      <c r="B32" s="4" t="n"/>
     </row>
     <row r="33">
-      <c r="A33" s="4" t="inlineStr">
-        <is>
-          <t>smk02</t>
-        </is>
-      </c>
-      <c r="B33" s="4" t="inlineStr">
-        <is>
-          <t>SMK02</t>
-        </is>
-      </c>
+      <c r="A33" s="4" t="n"/>
+      <c r="B33" s="4" t="n"/>
     </row>
     <row r="34">
-      <c r="A34" s="4" t="inlineStr">
-        <is>
-          <t>smk03</t>
-        </is>
-      </c>
-      <c r="B34" s="4" t="inlineStr">
-        <is>
-          <t>SMK03</t>
-        </is>
-      </c>
+      <c r="A34" s="4" t="n"/>
+      <c r="B34" s="4" t="n"/>
     </row>
     <row r="35">
-      <c r="A35" s="4" t="inlineStr">
-        <is>
-          <t>smk04</t>
-        </is>
-      </c>
-      <c r="B35" s="4" t="inlineStr">
-        <is>
-          <t>SMK04</t>
-        </is>
-      </c>
+      <c r="A35" s="4" t="n"/>
+      <c r="B35" s="4" t="n"/>
     </row>
     <row r="36">
-      <c r="A36" s="4" t="inlineStr">
-        <is>
-          <t>smk05</t>
-        </is>
-      </c>
-      <c r="B36" s="4" t="inlineStr">
-        <is>
-          <t>SMK05</t>
-        </is>
-      </c>
+      <c r="A36" s="4" t="n"/>
+      <c r="B36" s="4" t="n"/>
     </row>
     <row r="37">
-      <c r="A37" s="4" t="inlineStr">
-        <is>
-          <t>smk06</t>
-        </is>
-      </c>
-      <c r="B37" s="4" t="inlineStr">
-        <is>
-          <t>SMK06</t>
-        </is>
-      </c>
+      <c r="A37" s="4" t="n"/>
+      <c r="B37" s="4" t="n"/>
     </row>
     <row r="38">
-      <c r="A38" s="4" t="inlineStr">
-        <is>
-          <t>smk07</t>
-        </is>
-      </c>
-      <c r="B38" s="4" t="inlineStr">
-        <is>
-          <t>SMK07</t>
-        </is>
-      </c>
+      <c r="A38" s="4" t="n"/>
+      <c r="B38" s="4" t="n"/>
     </row>
     <row r="39">
-      <c r="A39" s="4" t="inlineStr">
-        <is>
-          <t>ssw</t>
-        </is>
-      </c>
-      <c r="B39" s="4" t="inlineStr">
-        <is>
-          <t>SSW</t>
-        </is>
-      </c>
+      <c r="A39" s="4" t="n"/>
+      <c r="B39" s="4" t="n"/>
     </row>
     <row r="40">
-      <c r="A40" s="4" t="inlineStr">
-        <is>
-          <t>st11</t>
-        </is>
-      </c>
-      <c r="B40" s="4" t="inlineStr">
-        <is>
-          <t>ST11</t>
-        </is>
-      </c>
+      <c r="A40" s="4" t="n"/>
+      <c r="B40" s="4" t="n"/>
     </row>
     <row r="41">
-      <c r="A41" s="4" t="inlineStr">
-        <is>
-          <t>st9</t>
-        </is>
-      </c>
-      <c r="B41" s="4" t="inlineStr">
-        <is>
-          <t>ST9</t>
-        </is>
-      </c>
+      <c r="A41" s="4" t="n"/>
+      <c r="B41" s="4" t="n"/>
     </row>
     <row r="42">
-      <c r="A42" s="4" t="inlineStr">
-        <is>
-          <t>stf</t>
-        </is>
-      </c>
-      <c r="B42" s="4" t="inlineStr">
-        <is>
-          <t>STF</t>
-        </is>
-      </c>
+      <c r="A42" s="4" t="n"/>
+      <c r="B42" s="4" t="n"/>
     </row>
     <row r="43">
-      <c r="A43" s="4" t="inlineStr">
-        <is>
-          <t>tac</t>
-        </is>
-      </c>
-      <c r="B43" s="4" t="inlineStr">
-        <is>
-          <t>TAC</t>
-        </is>
-      </c>
+      <c r="A43" s="4" t="n"/>
+      <c r="B43" s="4" t="n"/>
     </row>
     <row r="44">
-      <c r="A44" s="4" t="inlineStr">
-        <is>
-          <t>tbn1</t>
-        </is>
-      </c>
-      <c r="B44" s="4" t="inlineStr">
-        <is>
-          <t>TBN1</t>
-        </is>
-      </c>
+      <c r="A44" s="4" t="n"/>
+      <c r="B44" s="4" t="n"/>
     </row>
     <row r="45">
-      <c r="A45" s="4" t="inlineStr">
-        <is>
-          <t>tbn2</t>
-        </is>
-      </c>
-      <c r="B45" s="4" t="inlineStr">
-        <is>
-          <t>TBN2</t>
-        </is>
-      </c>
+      <c r="A45" s="4" t="n"/>
+      <c r="B45" s="4" t="n"/>
     </row>
     <row r="46">
-      <c r="A46" s="4" t="inlineStr">
-        <is>
-          <t>uaf</t>
-        </is>
-      </c>
-      <c r="B46" s="4" t="inlineStr">
-        <is>
-          <t>UAF</t>
-        </is>
-      </c>
+      <c r="A46" s="4" t="n"/>
+      <c r="B46" s="4" t="n"/>
     </row>
     <row r="47">
-      <c r="A47" s="4" t="inlineStr">
-        <is>
-          <t>wgr</t>
-        </is>
-      </c>
-      <c r="B47" s="4" t="inlineStr">
-        <is>
-          <t>WGR</t>
-        </is>
-      </c>
+      <c r="A47" s="4" t="n"/>
+      <c r="B47" s="4" t="n"/>
     </row>
     <row r="48">
-      <c r="A48" s="4" t="inlineStr">
-        <is>
-          <t>zc</t>
-        </is>
-      </c>
-      <c r="B48" s="4" t="inlineStr">
-        <is>
-          <t>ZC</t>
-        </is>
-      </c>
+      <c r="A48" s="4" t="n"/>
+      <c r="B48" s="4" t="n"/>
     </row>
     <row r="49">
-      <c r="A49" s="4" t="inlineStr">
-        <is>
-          <t>all site</t>
-        </is>
-      </c>
-      <c r="B49" s="4" t="inlineStr">
-        <is>
-          <t>All Site</t>
-        </is>
-      </c>
+      <c r="A49" s="4" t="n"/>
+      <c r="B49" s="4" t="n"/>
     </row>
     <row r="50">
-      <c r="A50" s="4" t="inlineStr">
-        <is>
-          <t>all sites</t>
-        </is>
-      </c>
-      <c r="B50" s="4" t="inlineStr">
-        <is>
-          <t>All Site</t>
-        </is>
-      </c>
+      <c r="A50" s="4" t="n"/>
+      <c r="B50" s="4" t="n"/>
     </row>
     <row r="51">
-      <c r="A51" s="4" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="B51" s="4" t="inlineStr">
-        <is>
-          <t>All Site</t>
-        </is>
-      </c>
+      <c r="A51" s="4" t="n"/>
+      <c r="B51" s="4" t="n"/>
     </row>
     <row r="52">
-      <c r="A52" s="4" t="inlineStr">
-        <is>
-          <t>company</t>
-        </is>
-      </c>
-      <c r="B52" s="4" t="inlineStr">
-        <is>
-          <t>All Site</t>
-        </is>
-      </c>
+      <c r="A52" s="4" t="n"/>
+      <c r="B52" s="4" t="n"/>
     </row>
     <row r="53">
-      <c r="A53" s="4" t="inlineStr">
-        <is>
-          <t>companywide</t>
-        </is>
-      </c>
-      <c r="B53" s="4" t="inlineStr">
-        <is>
-          <t>All Site</t>
-        </is>
-      </c>
+      <c r="A53" s="4" t="n"/>
+      <c r="B53" s="4" t="n"/>
     </row>
     <row r="54">
-      <c r="A54" s="4" t="inlineStr">
-        <is>
-          <t>company wide</t>
-        </is>
-      </c>
-      <c r="B54" s="4" t="inlineStr">
-        <is>
-          <t>All Site</t>
-        </is>
-      </c>
+      <c r="A54" s="4" t="n"/>
+      <c r="B54" s="4" t="n"/>
     </row>
     <row r="55">
-      <c r="A55" s="4" t="inlineStr">
-        <is>
-          <t>ทั้งหมด</t>
-        </is>
-      </c>
-      <c r="B55" s="4" t="inlineStr">
-        <is>
-          <t>All Site</t>
-        </is>
-      </c>
+      <c r="A55" s="4" t="n"/>
+      <c r="B55" s="4" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
